--- a/artfynd/A 5994-2026 artfynd.xlsx
+++ b/artfynd/A 5994-2026 artfynd.xlsx
@@ -2947,50 +2947,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131195643</v>
+        <v>131195654</v>
       </c>
       <c r="B23" t="n">
-        <v>57881</v>
+        <v>92269</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440858</v>
+        <v>440686</v>
       </c>
       <c r="R23" t="n">
-        <v>6815063</v>
+        <v>6815080</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3022,7 +3017,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3032,7 +3027,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3059,32 +3054,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131195654</v>
+        <v>131195670</v>
       </c>
       <c r="B24" t="n">
-        <v>92269</v>
+        <v>81230</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>1049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3094,10 +3089,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440686</v>
+        <v>440868</v>
       </c>
       <c r="R24" t="n">
-        <v>6815080</v>
+        <v>6814651</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3129,7 +3124,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3139,7 +3134,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3166,10 +3161,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131195670</v>
+        <v>131195762</v>
       </c>
       <c r="B25" t="n">
-        <v>81230</v>
+        <v>79245</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3177,21 +3172,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3201,10 +3196,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440868</v>
+        <v>440958</v>
       </c>
       <c r="R25" t="n">
-        <v>6814651</v>
+        <v>6814746</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3236,7 +3231,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3246,7 +3241,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3273,7 +3268,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131195762</v>
+        <v>131195886</v>
       </c>
       <c r="B26" t="n">
         <v>79245</v>
@@ -3308,10 +3303,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>440958</v>
+        <v>440835</v>
       </c>
       <c r="R26" t="n">
-        <v>6814746</v>
+        <v>6814572</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3343,7 +3338,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3353,7 +3348,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3380,7 +3375,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131195886</v>
+        <v>131195873</v>
       </c>
       <c r="B27" t="n">
         <v>79245</v>
@@ -3415,10 +3410,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>440835</v>
+        <v>440848</v>
       </c>
       <c r="R27" t="n">
-        <v>6814572</v>
+        <v>6814711</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3450,7 +3445,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3460,7 +3455,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3487,7 +3482,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131195873</v>
+        <v>131195904</v>
       </c>
       <c r="B28" t="n">
         <v>79245</v>
@@ -3522,10 +3517,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>440848</v>
+        <v>440820</v>
       </c>
       <c r="R28" t="n">
-        <v>6814711</v>
+        <v>6814384</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3557,7 +3552,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3567,7 +3562,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3594,7 +3589,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131195904</v>
+        <v>131195758</v>
       </c>
       <c r="B29" t="n">
         <v>79245</v>
@@ -3629,10 +3624,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>440820</v>
+        <v>441015</v>
       </c>
       <c r="R29" t="n">
-        <v>6814384</v>
+        <v>6814688</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3664,7 +3659,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3674,7 +3669,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3701,7 +3696,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131195758</v>
+        <v>131195751</v>
       </c>
       <c r="B30" t="n">
         <v>79245</v>
@@ -3736,10 +3731,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>441015</v>
+        <v>441102</v>
       </c>
       <c r="R30" t="n">
-        <v>6814688</v>
+        <v>6814644</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3771,7 +3766,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3781,7 +3776,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3808,7 +3803,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131195751</v>
+        <v>131195874</v>
       </c>
       <c r="B31" t="n">
         <v>79245</v>
@@ -3843,10 +3838,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>441102</v>
+        <v>440845</v>
       </c>
       <c r="R31" t="n">
-        <v>6814644</v>
+        <v>6814694</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3878,7 +3873,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3888,7 +3883,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3915,7 +3910,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131195874</v>
+        <v>131195821</v>
       </c>
       <c r="B32" t="n">
         <v>79245</v>
@@ -3950,10 +3945,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440845</v>
+        <v>440732</v>
       </c>
       <c r="R32" t="n">
-        <v>6814694</v>
+        <v>6815137</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3985,7 +3980,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3995,7 +3990,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4022,10 +4017,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131195821</v>
+        <v>131195564</v>
       </c>
       <c r="B33" t="n">
-        <v>79245</v>
+        <v>83225</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4033,21 +4028,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4057,10 +4052,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440732</v>
+        <v>440439</v>
       </c>
       <c r="R33" t="n">
-        <v>6815137</v>
+        <v>6815121</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4092,7 +4087,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4102,7 +4097,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4129,10 +4124,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131195564</v>
+        <v>131195774</v>
       </c>
       <c r="B34" t="n">
-        <v>83225</v>
+        <v>79245</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4140,21 +4135,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4164,10 +4159,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440439</v>
+        <v>440927</v>
       </c>
       <c r="R34" t="n">
-        <v>6815121</v>
+        <v>6814891</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4199,7 +4194,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4209,7 +4204,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4236,7 +4231,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131195774</v>
+        <v>131195851</v>
       </c>
       <c r="B35" t="n">
         <v>79245</v>
@@ -4271,10 +4266,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440927</v>
+        <v>440426</v>
       </c>
       <c r="R35" t="n">
-        <v>6814891</v>
+        <v>6815128</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4306,7 +4301,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4316,7 +4311,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4343,10 +4338,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131195851</v>
+        <v>131195614</v>
       </c>
       <c r="B36" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4354,34 +4349,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440426</v>
+        <v>440798</v>
       </c>
       <c r="R36" t="n">
-        <v>6815128</v>
+        <v>6815081</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4413,7 +4413,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4450,7 +4450,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131195614</v>
+        <v>131195601</v>
       </c>
       <c r="B37" t="n">
         <v>57884</v>
@@ -4490,10 +4490,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440798</v>
+        <v>440519</v>
       </c>
       <c r="R37" t="n">
-        <v>6815081</v>
+        <v>6815131</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4525,7 +4525,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4535,7 +4535,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Dagsfärska spår efter födosök (små barkbitar på nysnö)</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4562,27 +4567,27 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131195601</v>
+        <v>131195551</v>
       </c>
       <c r="B38" t="n">
-        <v>57884</v>
+        <v>5197</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>105930</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4593,7 +4598,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4602,10 +4607,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440519</v>
+        <v>440944</v>
       </c>
       <c r="R38" t="n">
-        <v>6815131</v>
+        <v>6814700</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4637,7 +4642,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4647,12 +4652,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:56</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Dagsfärska spår efter födosök (små barkbitar på nysnö)</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4679,27 +4679,27 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131195551</v>
+        <v>131195643</v>
       </c>
       <c r="B39" t="n">
-        <v>5197</v>
+        <v>57881</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4710,7 +4710,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4719,10 +4719,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440944</v>
+        <v>440858</v>
       </c>
       <c r="R39" t="n">
-        <v>6814700</v>
+        <v>6815063</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4754,7 +4754,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4791,32 +4791,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131195579</v>
+        <v>131195570</v>
       </c>
       <c r="B40" t="n">
-        <v>91810</v>
+        <v>91773</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4826,10 +4826,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440686</v>
+        <v>441037</v>
       </c>
       <c r="R40" t="n">
-        <v>6815080</v>
+        <v>6815351</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4861,7 +4861,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5545,32 +5545,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131195570</v>
+        <v>131195579</v>
       </c>
       <c r="B47" t="n">
-        <v>91773</v>
+        <v>91810</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5580,10 +5580,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>441037</v>
+        <v>440686</v>
       </c>
       <c r="R47" t="n">
-        <v>6815351</v>
+        <v>6815080</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -14105,10 +14105,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>131195624</v>
+        <v>131195796</v>
       </c>
       <c r="B126" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14116,39 +14116,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>440693</v>
+        <v>440887</v>
       </c>
       <c r="R126" t="n">
-        <v>6815072</v>
+        <v>6815322</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14180,7 +14175,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14190,7 +14185,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14217,10 +14212,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>131195630</v>
+        <v>131195785</v>
       </c>
       <c r="B127" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14228,39 +14223,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>440458</v>
+        <v>440835</v>
       </c>
       <c r="R127" t="n">
-        <v>6815199</v>
+        <v>6815088</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14292,7 +14282,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14302,7 +14292,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14329,7 +14319,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>131195796</v>
+        <v>131195700</v>
       </c>
       <c r="B128" t="n">
         <v>79245</v>
@@ -14358,16 +14348,21 @@
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>440887</v>
+        <v>440915</v>
       </c>
       <c r="R128" t="n">
-        <v>6815322</v>
+        <v>6815308</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14399,7 +14394,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14409,7 +14404,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14436,7 +14431,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>131195785</v>
+        <v>131195892</v>
       </c>
       <c r="B129" t="n">
         <v>79245</v>
@@ -14471,10 +14466,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>440835</v>
+        <v>440901</v>
       </c>
       <c r="R129" t="n">
-        <v>6815088</v>
+        <v>6814603</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14506,7 +14501,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14516,7 +14511,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14543,10 +14538,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>131195700</v>
+        <v>131195650</v>
       </c>
       <c r="B130" t="n">
-        <v>79245</v>
+        <v>57881</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14554,27 +14549,27 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
@@ -14583,10 +14578,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>440915</v>
+        <v>441062</v>
       </c>
       <c r="R130" t="n">
-        <v>6815308</v>
+        <v>6815341</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14618,7 +14613,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14628,7 +14623,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14655,10 +14650,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>131195892</v>
+        <v>131195624</v>
       </c>
       <c r="B131" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14666,34 +14661,39 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>440901</v>
+        <v>440693</v>
       </c>
       <c r="R131" t="n">
-        <v>6814603</v>
+        <v>6815072</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14725,7 +14725,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14735,7 +14735,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14762,10 +14762,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>131195650</v>
+        <v>131195630</v>
       </c>
       <c r="B132" t="n">
-        <v>57881</v>
+        <v>57884</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14773,16 +14773,16 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -14802,10 +14802,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>441062</v>
+        <v>440458</v>
       </c>
       <c r="R132" t="n">
-        <v>6815341</v>
+        <v>6815199</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14837,7 +14837,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14847,7 +14847,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -20314,10 +20314,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>131195888</v>
+        <v>131195622</v>
       </c>
       <c r="B183" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20325,34 +20325,39 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P183" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>440842</v>
+        <v>440736</v>
       </c>
       <c r="R183" t="n">
-        <v>6814583</v>
+        <v>6815133</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20384,7 +20389,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -20394,7 +20399,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -20421,10 +20426,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>131195563</v>
+        <v>131195598</v>
       </c>
       <c r="B184" t="n">
-        <v>83225</v>
+        <v>57884</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20432,34 +20437,39 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P184" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>440440</v>
+        <v>440953</v>
       </c>
       <c r="R184" t="n">
-        <v>6815105</v>
+        <v>6815353</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20491,7 +20501,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -20501,7 +20511,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -20528,10 +20538,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>131195866</v>
+        <v>131195611</v>
       </c>
       <c r="B185" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20539,34 +20549,39 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P185" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>440817</v>
+        <v>441058</v>
       </c>
       <c r="R185" t="n">
-        <v>6814896</v>
+        <v>6814648</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20598,7 +20613,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -20608,7 +20623,7 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -20635,10 +20650,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>131195905</v>
+        <v>131195631</v>
       </c>
       <c r="B186" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -20646,34 +20661,39 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P186" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>440845</v>
+        <v>440506</v>
       </c>
       <c r="R186" t="n">
-        <v>6814361</v>
+        <v>6815165</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20705,7 +20725,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -20715,7 +20735,7 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20742,7 +20762,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>131195741</v>
+        <v>131195888</v>
       </c>
       <c r="B187" t="n">
         <v>79245</v>
@@ -20777,10 +20797,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>441179</v>
+        <v>440842</v>
       </c>
       <c r="R187" t="n">
-        <v>6814662</v>
+        <v>6814583</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20812,7 +20832,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -20822,7 +20842,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20849,10 +20869,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>131195850</v>
+        <v>131195563</v>
       </c>
       <c r="B188" t="n">
-        <v>79245</v>
+        <v>83225</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20860,21 +20880,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -20884,10 +20904,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>440439</v>
+        <v>440440</v>
       </c>
       <c r="R188" t="n">
-        <v>6815121</v>
+        <v>6815105</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20919,7 +20939,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -20929,7 +20949,7 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20956,7 +20976,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>131195877</v>
+        <v>131195866</v>
       </c>
       <c r="B189" t="n">
         <v>79245</v>
@@ -20991,10 +21011,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>440882</v>
+        <v>440817</v>
       </c>
       <c r="R189" t="n">
-        <v>6814639</v>
+        <v>6814896</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21026,7 +21046,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -21036,7 +21056,7 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -21063,7 +21083,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>131195794</v>
+        <v>131195905</v>
       </c>
       <c r="B190" t="n">
         <v>79245</v>
@@ -21098,10 +21118,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>440773</v>
+        <v>440845</v>
       </c>
       <c r="R190" t="n">
-        <v>6815278</v>
+        <v>6814361</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21133,7 +21153,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -21143,7 +21163,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -21170,7 +21190,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>131195902</v>
+        <v>131195741</v>
       </c>
       <c r="B191" t="n">
         <v>79245</v>
@@ -21205,10 +21225,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>440860</v>
+        <v>441179</v>
       </c>
       <c r="R191" t="n">
-        <v>6814447</v>
+        <v>6814662</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21240,7 +21260,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -21250,7 +21270,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -21277,10 +21297,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>131195622</v>
+        <v>131195850</v>
       </c>
       <c r="B192" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21288,39 +21308,34 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
-      <c r="M192" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P192" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>440736</v>
+        <v>440439</v>
       </c>
       <c r="R192" t="n">
-        <v>6815133</v>
+        <v>6815121</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21352,7 +21367,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -21362,7 +21377,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -21389,10 +21404,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>131195598</v>
+        <v>131195877</v>
       </c>
       <c r="B193" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21400,39 +21415,34 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
-      <c r="M193" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P193" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>440953</v>
+        <v>440882</v>
       </c>
       <c r="R193" t="n">
-        <v>6815353</v>
+        <v>6814639</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21464,7 +21474,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -21474,7 +21484,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21501,10 +21511,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>131195611</v>
+        <v>131195794</v>
       </c>
       <c r="B194" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21512,39 +21522,34 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P194" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>441058</v>
+        <v>440773</v>
       </c>
       <c r="R194" t="n">
-        <v>6814648</v>
+        <v>6815278</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21576,7 +21581,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -21586,7 +21591,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21613,10 +21618,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>131195631</v>
+        <v>131195902</v>
       </c>
       <c r="B195" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -21624,39 +21629,34 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P195" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>440506</v>
+        <v>440860</v>
       </c>
       <c r="R195" t="n">
-        <v>6815165</v>
+        <v>6814447</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21688,7 +21688,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -21698,7 +21698,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -23992,10 +23992,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>131195666</v>
+        <v>131195628</v>
       </c>
       <c r="B217" t="n">
-        <v>81230</v>
+        <v>57884</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -24003,34 +24003,39 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>1049</v>
+        <v>100109</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P217" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>441125</v>
+        <v>440428</v>
       </c>
       <c r="R217" t="n">
-        <v>6815280</v>
+        <v>6815159</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -24062,7 +24067,7 @@
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
@@ -24072,7 +24077,7 @@
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -24099,7 +24104,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>131195628</v>
+        <v>131195634</v>
       </c>
       <c r="B218" t="n">
         <v>57884</v>
@@ -24139,10 +24144,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>440428</v>
+        <v>440584</v>
       </c>
       <c r="R218" t="n">
-        <v>6815159</v>
+        <v>6815078</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24174,7 +24179,7 @@
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
@@ -24184,7 +24189,7 @@
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -24211,10 +24216,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>131195634</v>
+        <v>131195666</v>
       </c>
       <c r="B219" t="n">
-        <v>57884</v>
+        <v>81230</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24222,39 +24227,34 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>100109</v>
+        <v>1049</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
-      <c r="M219" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P219" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>440584</v>
+        <v>441125</v>
       </c>
       <c r="R219" t="n">
-        <v>6815078</v>
+        <v>6815280</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24286,7 +24286,7 @@
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
@@ -24296,7 +24296,7 @@
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -32958,10 +32958,10 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>131176293</v>
+        <v>131187941</v>
       </c>
       <c r="B302" t="n">
-        <v>79245</v>
+        <v>57881</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -32969,34 +32969,39 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I302" t="inlineStr"/>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P302" t="inlineStr">
         <is>
-          <t>Ytter-Navardalen, Dlr</t>
+          <t>Navarnäsberget, Dlr</t>
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>440860</v>
+        <v>440573</v>
       </c>
       <c r="R302" t="n">
-        <v>6815093</v>
+        <v>6815085</v>
       </c>
       <c r="S302" t="n">
         <v>10</v>
@@ -33026,19 +33031,14 @@
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="Z302" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AA302" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="AB302" t="inlineStr">
-        <is>
-          <t>09:13</t>
+      <c r="AC302" t="inlineStr">
+        <is>
+          <t>1 bild äldre gran många hack</t>
         </is>
       </c>
       <c r="AD302" t="b">
@@ -33065,10 +33065,10 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>131187941</v>
+        <v>131186236</v>
       </c>
       <c r="B303" t="n">
-        <v>57881</v>
+        <v>57884</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -33076,16 +33076,16 @@
         </is>
       </c>
       <c r="E303" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -33096,7 +33096,7 @@
       <c r="I303" t="inlineStr"/>
       <c r="M303" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P303" t="inlineStr">
@@ -33105,10 +33105,10 @@
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>440573</v>
+        <v>440643</v>
       </c>
       <c r="R303" t="n">
-        <v>6815085</v>
+        <v>6814928</v>
       </c>
       <c r="S303" t="n">
         <v>10</v>
@@ -33141,11 +33141,6 @@
       <c r="AA303" t="inlineStr">
         <is>
           <t>2026-02-16</t>
-        </is>
-      </c>
-      <c r="AC303" t="inlineStr">
-        <is>
-          <t>1 bild äldre gran många hack</t>
         </is>
       </c>
       <c r="AD303" t="b">
@@ -33172,7 +33167,7 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>131186236</v>
+        <v>131176405</v>
       </c>
       <c r="B304" t="n">
         <v>57884</v>
@@ -33203,19 +33198,19 @@
       <c r="I304" t="inlineStr"/>
       <c r="M304" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P304" t="inlineStr">
         <is>
-          <t>Navarnäsberget, Dlr</t>
+          <t>Ytter-Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>440643</v>
+        <v>440856</v>
       </c>
       <c r="R304" t="n">
-        <v>6814928</v>
+        <v>6815124</v>
       </c>
       <c r="S304" t="n">
         <v>10</v>
@@ -33245,9 +33240,19 @@
           <t>2026-02-16</t>
         </is>
       </c>
+      <c r="Z304" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AA304" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AB304" t="inlineStr">
+        <is>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD304" t="b">
@@ -33274,10 +33279,10 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>131176405</v>
+        <v>131176293</v>
       </c>
       <c r="B305" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -33285,39 +33290,34 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I305" t="inlineStr"/>
-      <c r="M305" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P305" t="inlineStr">
         <is>
           <t>Ytter-Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>440856</v>
+        <v>440860</v>
       </c>
       <c r="R305" t="n">
-        <v>6815124</v>
+        <v>6815093</v>
       </c>
       <c r="S305" t="n">
         <v>10</v>

--- a/artfynd/A 5994-2026 artfynd.xlsx
+++ b/artfynd/A 5994-2026 artfynd.xlsx
@@ -5652,10 +5652,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131195792</v>
+        <v>131195646</v>
       </c>
       <c r="B48" t="n">
-        <v>79245</v>
+        <v>57881</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5663,34 +5663,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>440746</v>
+        <v>440867</v>
       </c>
       <c r="R48" t="n">
-        <v>6815201</v>
+        <v>6814841</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5722,7 +5727,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5732,7 +5737,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5759,10 +5764,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131195826</v>
+        <v>131195648</v>
       </c>
       <c r="B49" t="n">
-        <v>79245</v>
+        <v>57881</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5770,34 +5775,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440688</v>
+        <v>440835</v>
       </c>
       <c r="R49" t="n">
-        <v>6815083</v>
+        <v>6815088</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5829,7 +5839,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5839,7 +5849,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5866,7 +5876,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131195772</v>
+        <v>131195792</v>
       </c>
       <c r="B50" t="n">
         <v>79245</v>
@@ -5901,10 +5911,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>440955</v>
+        <v>440746</v>
       </c>
       <c r="R50" t="n">
-        <v>6814897</v>
+        <v>6815201</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5936,7 +5946,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5946,7 +5956,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5973,7 +5983,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131195880</v>
+        <v>131195826</v>
       </c>
       <c r="B51" t="n">
         <v>79245</v>
@@ -6008,10 +6018,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>440820</v>
+        <v>440688</v>
       </c>
       <c r="R51" t="n">
-        <v>6814616</v>
+        <v>6815083</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6043,7 +6053,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6053,7 +6063,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6080,7 +6090,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131195803</v>
+        <v>131195772</v>
       </c>
       <c r="B52" t="n">
         <v>79245</v>
@@ -6115,10 +6125,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>441101</v>
+        <v>440955</v>
       </c>
       <c r="R52" t="n">
-        <v>6815283</v>
+        <v>6814897</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6150,7 +6160,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6160,7 +6170,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6187,7 +6197,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131195748</v>
+        <v>131195880</v>
       </c>
       <c r="B53" t="n">
         <v>79245</v>
@@ -6222,10 +6232,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>441151</v>
+        <v>440820</v>
       </c>
       <c r="R53" t="n">
-        <v>6814715</v>
+        <v>6814616</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6257,7 +6267,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6267,7 +6277,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6294,7 +6304,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131195860</v>
+        <v>131195803</v>
       </c>
       <c r="B54" t="n">
         <v>79245</v>
@@ -6329,10 +6339,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>440531</v>
+        <v>441101</v>
       </c>
       <c r="R54" t="n">
-        <v>6815095</v>
+        <v>6815283</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6364,7 +6374,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6374,7 +6384,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6401,7 +6411,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131195778</v>
+        <v>131195748</v>
       </c>
       <c r="B55" t="n">
         <v>79245</v>
@@ -6436,10 +6446,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>440906</v>
+        <v>441151</v>
       </c>
       <c r="R55" t="n">
-        <v>6814928</v>
+        <v>6814715</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6471,7 +6481,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6481,7 +6491,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6508,10 +6518,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131195608</v>
+        <v>131195860</v>
       </c>
       <c r="B56" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6519,39 +6529,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>441099</v>
+        <v>440531</v>
       </c>
       <c r="R56" t="n">
-        <v>6814647</v>
+        <v>6815095</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6583,7 +6588,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6593,7 +6598,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6620,10 +6625,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131195646</v>
+        <v>131195778</v>
       </c>
       <c r="B57" t="n">
-        <v>57881</v>
+        <v>79245</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6631,39 +6636,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>440867</v>
+        <v>440906</v>
       </c>
       <c r="R57" t="n">
-        <v>6814841</v>
+        <v>6814928</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6695,7 +6695,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6732,10 +6732,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131195648</v>
+        <v>131195608</v>
       </c>
       <c r="B58" t="n">
-        <v>57881</v>
+        <v>57884</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6743,16 +6743,16 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6772,10 +6772,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>440835</v>
+        <v>441099</v>
       </c>
       <c r="R58" t="n">
-        <v>6815088</v>
+        <v>6814647</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6807,7 +6807,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -9444,10 +9444,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131195769</v>
+        <v>131195642</v>
       </c>
       <c r="B83" t="n">
-        <v>79245</v>
+        <v>57881</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9455,34 +9455,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>440947</v>
+        <v>440965</v>
       </c>
       <c r="R83" t="n">
-        <v>6814871</v>
+        <v>6814690</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9514,7 +9519,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9524,7 +9529,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9551,10 +9556,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131195766</v>
+        <v>131195595</v>
       </c>
       <c r="B84" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9562,34 +9567,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>440973</v>
+        <v>440866</v>
       </c>
       <c r="R84" t="n">
-        <v>6814836</v>
+        <v>6815064</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9621,7 +9631,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9631,7 +9641,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9658,7 +9673,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131195889</v>
+        <v>131195769</v>
       </c>
       <c r="B85" t="n">
         <v>79245</v>
@@ -9693,10 +9708,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>440851</v>
+        <v>440947</v>
       </c>
       <c r="R85" t="n">
-        <v>6814582</v>
+        <v>6814871</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9728,7 +9743,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9738,7 +9753,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9765,7 +9780,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131195868</v>
+        <v>131195766</v>
       </c>
       <c r="B86" t="n">
         <v>79245</v>
@@ -9800,10 +9815,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>440849</v>
+        <v>440973</v>
       </c>
       <c r="R86" t="n">
-        <v>6814889</v>
+        <v>6814836</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9835,7 +9850,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9845,7 +9860,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9872,7 +9887,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131195704</v>
+        <v>131195889</v>
       </c>
       <c r="B87" t="n">
         <v>79245</v>
@@ -9901,21 +9916,16 @@
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>440460</v>
+        <v>440851</v>
       </c>
       <c r="R87" t="n">
-        <v>6815198</v>
+        <v>6814582</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9947,7 +9957,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9957,7 +9967,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9984,7 +9994,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131195775</v>
+        <v>131195868</v>
       </c>
       <c r="B88" t="n">
         <v>79245</v>
@@ -10019,10 +10029,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>440923</v>
+        <v>440849</v>
       </c>
       <c r="R88" t="n">
-        <v>6814881</v>
+        <v>6814889</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10054,7 +10064,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10064,7 +10074,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10091,7 +10101,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131195869</v>
+        <v>131195704</v>
       </c>
       <c r="B89" t="n">
         <v>79245</v>
@@ -10120,16 +10130,21 @@
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>440867</v>
+        <v>440460</v>
       </c>
       <c r="R89" t="n">
-        <v>6814841</v>
+        <v>6815198</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10161,7 +10176,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10171,7 +10186,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10198,7 +10213,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131195861</v>
+        <v>131195775</v>
       </c>
       <c r="B90" t="n">
         <v>79245</v>
@@ -10233,10 +10248,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>440568</v>
+        <v>440923</v>
       </c>
       <c r="R90" t="n">
-        <v>6815075</v>
+        <v>6814881</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10268,7 +10283,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10278,7 +10293,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10305,10 +10320,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131195642</v>
+        <v>131195869</v>
       </c>
       <c r="B91" t="n">
-        <v>57881</v>
+        <v>79245</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10316,39 +10331,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>440965</v>
+        <v>440867</v>
       </c>
       <c r="R91" t="n">
-        <v>6814690</v>
+        <v>6814841</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10380,7 +10390,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10390,7 +10400,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10417,10 +10427,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131195595</v>
+        <v>131195861</v>
       </c>
       <c r="B92" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10428,39 +10438,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>440866</v>
+        <v>440568</v>
       </c>
       <c r="R92" t="n">
-        <v>6815064</v>
+        <v>6815075</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10492,7 +10497,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10502,12 +10507,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:48</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -12383,10 +12383,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>131195567</v>
+        <v>131195917</v>
       </c>
       <c r="B110" t="n">
-        <v>91773</v>
+        <v>5177</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12394,34 +12394,39 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>440907</v>
+        <v>440934</v>
       </c>
       <c r="R110" t="n">
-        <v>6814875</v>
+        <v>6814927</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12453,7 +12458,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12463,7 +12468,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12490,45 +12495,50 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>131195573</v>
+        <v>131195600</v>
       </c>
       <c r="B111" t="n">
-        <v>91773</v>
+        <v>57884</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>440508</v>
+        <v>440842</v>
       </c>
       <c r="R111" t="n">
-        <v>6815137</v>
+        <v>6815077</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12560,7 +12570,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12570,14 +12580,14 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
       <c r="AE111" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG111" t="b">
         <v>0</v>
@@ -12597,10 +12607,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>131195637</v>
+        <v>131195798</v>
       </c>
       <c r="B112" t="n">
-        <v>58043</v>
+        <v>79245</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12608,21 +12618,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12632,10 +12642,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>441072</v>
+        <v>440943</v>
       </c>
       <c r="R112" t="n">
-        <v>6814663</v>
+        <v>6815341</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12667,7 +12677,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12677,7 +12687,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12704,7 +12714,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131195798</v>
+        <v>131195842</v>
       </c>
       <c r="B113" t="n">
         <v>79245</v>
@@ -12739,10 +12749,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>440943</v>
+        <v>440509</v>
       </c>
       <c r="R113" t="n">
-        <v>6815341</v>
+        <v>6815018</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12774,7 +12784,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12784,7 +12794,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12811,7 +12821,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131195842</v>
+        <v>131195776</v>
       </c>
       <c r="B114" t="n">
         <v>79245</v>
@@ -12846,10 +12856,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>440509</v>
+        <v>440926</v>
       </c>
       <c r="R114" t="n">
-        <v>6815018</v>
+        <v>6814927</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12881,7 +12891,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12891,7 +12901,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12918,7 +12928,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131195776</v>
+        <v>131195884</v>
       </c>
       <c r="B115" t="n">
         <v>79245</v>
@@ -12953,10 +12963,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>440926</v>
+        <v>440736</v>
       </c>
       <c r="R115" t="n">
-        <v>6814927</v>
+        <v>6814569</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12988,7 +12998,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12998,7 +13008,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13025,7 +13035,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131195884</v>
+        <v>131195739</v>
       </c>
       <c r="B116" t="n">
         <v>79245</v>
@@ -13060,10 +13070,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>440736</v>
+        <v>441199</v>
       </c>
       <c r="R116" t="n">
-        <v>6814569</v>
+        <v>6814633</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13095,7 +13105,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13105,7 +13115,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13132,7 +13142,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131195739</v>
+        <v>131195871</v>
       </c>
       <c r="B117" t="n">
         <v>79245</v>
@@ -13167,10 +13177,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>441199</v>
+        <v>440853</v>
       </c>
       <c r="R117" t="n">
-        <v>6814633</v>
+        <v>6814767</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13202,7 +13212,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13212,7 +13222,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13239,7 +13249,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131195871</v>
+        <v>131195839</v>
       </c>
       <c r="B118" t="n">
         <v>79245</v>
@@ -13274,10 +13284,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>440853</v>
+        <v>440519</v>
       </c>
       <c r="R118" t="n">
-        <v>6814767</v>
+        <v>6814964</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13309,7 +13319,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13319,7 +13329,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13346,10 +13356,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131195839</v>
+        <v>131195558</v>
       </c>
       <c r="B119" t="n">
-        <v>79245</v>
+        <v>83225</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13357,21 +13367,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13381,10 +13391,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>440519</v>
+        <v>440881</v>
       </c>
       <c r="R119" t="n">
-        <v>6814964</v>
+        <v>6815052</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13416,7 +13426,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13426,7 +13436,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13453,10 +13463,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131195558</v>
+        <v>131195840</v>
       </c>
       <c r="B120" t="n">
-        <v>83225</v>
+        <v>79245</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13464,21 +13474,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13488,10 +13498,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>440881</v>
+        <v>440518</v>
       </c>
       <c r="R120" t="n">
-        <v>6815052</v>
+        <v>6814966</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13523,7 +13533,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13533,7 +13543,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13560,7 +13570,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>131195840</v>
+        <v>131195844</v>
       </c>
       <c r="B121" t="n">
         <v>79245</v>
@@ -13595,10 +13605,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>440518</v>
+        <v>440488</v>
       </c>
       <c r="R121" t="n">
-        <v>6814966</v>
+        <v>6815047</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13630,7 +13640,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13640,7 +13650,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13667,32 +13677,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>131195844</v>
+        <v>131195567</v>
       </c>
       <c r="B122" t="n">
-        <v>79245</v>
+        <v>91773</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13702,10 +13712,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>440488</v>
+        <v>440907</v>
       </c>
       <c r="R122" t="n">
-        <v>6815047</v>
+        <v>6814875</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13737,7 +13747,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13747,7 +13757,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13774,10 +13784,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>131195917</v>
+        <v>131195573</v>
       </c>
       <c r="B123" t="n">
-        <v>5177</v>
+        <v>91773</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13785,39 +13795,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>440934</v>
+        <v>440508</v>
       </c>
       <c r="R123" t="n">
-        <v>6814927</v>
+        <v>6815137</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13849,7 +13854,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13859,7 +13864,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13886,10 +13891,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>131195600</v>
+        <v>131195637</v>
       </c>
       <c r="B124" t="n">
-        <v>57884</v>
+        <v>58043</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13897,39 +13902,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>440842</v>
+        <v>441072</v>
       </c>
       <c r="R124" t="n">
-        <v>6815077</v>
+        <v>6814663</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13961,7 +13961,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13971,14 +13971,14 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD124" t="b">
         <v>0</v>
       </c>
       <c r="AE124" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG124" t="b">
         <v>0</v>
@@ -20314,10 +20314,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>131195622</v>
+        <v>131195888</v>
       </c>
       <c r="B183" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20325,39 +20325,34 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P183" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>440736</v>
+        <v>440842</v>
       </c>
       <c r="R183" t="n">
-        <v>6815133</v>
+        <v>6814583</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20389,7 +20384,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -20399,7 +20394,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -20426,10 +20421,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>131195598</v>
+        <v>131195563</v>
       </c>
       <c r="B184" t="n">
-        <v>57884</v>
+        <v>83225</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20437,39 +20432,34 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P184" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>440953</v>
+        <v>440440</v>
       </c>
       <c r="R184" t="n">
-        <v>6815353</v>
+        <v>6815105</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20501,7 +20491,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -20511,7 +20501,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -20538,10 +20528,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>131195611</v>
+        <v>131195866</v>
       </c>
       <c r="B185" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20549,39 +20539,34 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P185" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>441058</v>
+        <v>440817</v>
       </c>
       <c r="R185" t="n">
-        <v>6814648</v>
+        <v>6814896</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20613,7 +20598,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -20623,7 +20608,7 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -20650,10 +20635,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>131195631</v>
+        <v>131195905</v>
       </c>
       <c r="B186" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -20661,39 +20646,34 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P186" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>440506</v>
+        <v>440845</v>
       </c>
       <c r="R186" t="n">
-        <v>6815165</v>
+        <v>6814361</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20725,7 +20705,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -20735,7 +20715,7 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20762,7 +20742,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>131195888</v>
+        <v>131195741</v>
       </c>
       <c r="B187" t="n">
         <v>79245</v>
@@ -20797,10 +20777,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>440842</v>
+        <v>441179</v>
       </c>
       <c r="R187" t="n">
-        <v>6814583</v>
+        <v>6814662</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20832,7 +20812,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -20842,7 +20822,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20869,10 +20849,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>131195563</v>
+        <v>131195850</v>
       </c>
       <c r="B188" t="n">
-        <v>83225</v>
+        <v>79245</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20880,21 +20860,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -20904,10 +20884,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>440440</v>
+        <v>440439</v>
       </c>
       <c r="R188" t="n">
-        <v>6815105</v>
+        <v>6815121</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20939,7 +20919,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -20949,7 +20929,7 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20976,7 +20956,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>131195866</v>
+        <v>131195877</v>
       </c>
       <c r="B189" t="n">
         <v>79245</v>
@@ -21011,10 +20991,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>440817</v>
+        <v>440882</v>
       </c>
       <c r="R189" t="n">
-        <v>6814896</v>
+        <v>6814639</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21046,7 +21026,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -21056,7 +21036,7 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -21083,7 +21063,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>131195905</v>
+        <v>131195794</v>
       </c>
       <c r="B190" t="n">
         <v>79245</v>
@@ -21118,10 +21098,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>440845</v>
+        <v>440773</v>
       </c>
       <c r="R190" t="n">
-        <v>6814361</v>
+        <v>6815278</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21153,7 +21133,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -21163,7 +21143,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -21190,7 +21170,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>131195741</v>
+        <v>131195902</v>
       </c>
       <c r="B191" t="n">
         <v>79245</v>
@@ -21225,10 +21205,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>441179</v>
+        <v>440860</v>
       </c>
       <c r="R191" t="n">
-        <v>6814662</v>
+        <v>6814447</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21260,7 +21240,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -21270,7 +21250,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -21297,10 +21277,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>131195850</v>
+        <v>131195622</v>
       </c>
       <c r="B192" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21308,34 +21288,39 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P192" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>440439</v>
+        <v>440736</v>
       </c>
       <c r="R192" t="n">
-        <v>6815121</v>
+        <v>6815133</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21367,7 +21352,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -21377,7 +21362,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -21404,10 +21389,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>131195877</v>
+        <v>131195598</v>
       </c>
       <c r="B193" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21415,34 +21400,39 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P193" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>440882</v>
+        <v>440953</v>
       </c>
       <c r="R193" t="n">
-        <v>6814639</v>
+        <v>6815353</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21474,7 +21464,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -21484,7 +21474,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21511,10 +21501,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>131195794</v>
+        <v>131195611</v>
       </c>
       <c r="B194" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21522,34 +21512,39 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P194" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>440773</v>
+        <v>441058</v>
       </c>
       <c r="R194" t="n">
-        <v>6815278</v>
+        <v>6814648</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21581,7 +21576,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -21591,7 +21586,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21618,10 +21613,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>131195902</v>
+        <v>131195631</v>
       </c>
       <c r="B195" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -21629,34 +21624,39 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P195" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>440860</v>
+        <v>440506</v>
       </c>
       <c r="R195" t="n">
-        <v>6814447</v>
+        <v>6815165</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21688,7 +21688,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -21698,7 +21698,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -23992,10 +23992,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>131195628</v>
+        <v>131195666</v>
       </c>
       <c r="B217" t="n">
-        <v>57884</v>
+        <v>81230</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -24003,39 +24003,34 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>100109</v>
+        <v>1049</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
-      <c r="M217" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P217" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>440428</v>
+        <v>441125</v>
       </c>
       <c r="R217" t="n">
-        <v>6815159</v>
+        <v>6815280</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -24067,7 +24062,7 @@
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
@@ -24077,7 +24072,7 @@
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -24104,7 +24099,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>131195634</v>
+        <v>131195628</v>
       </c>
       <c r="B218" t="n">
         <v>57884</v>
@@ -24144,10 +24139,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>440584</v>
+        <v>440428</v>
       </c>
       <c r="R218" t="n">
-        <v>6815078</v>
+        <v>6815159</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24179,7 +24174,7 @@
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
@@ -24189,7 +24184,7 @@
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -24216,10 +24211,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>131195666</v>
+        <v>131195634</v>
       </c>
       <c r="B219" t="n">
-        <v>81230</v>
+        <v>57884</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24227,34 +24222,39 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>1049</v>
+        <v>100109</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P219" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>441125</v>
+        <v>440584</v>
       </c>
       <c r="R219" t="n">
-        <v>6815280</v>
+        <v>6815078</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24286,7 +24286,7 @@
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
@@ -24296,7 +24296,7 @@
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -31159,10 +31159,10 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>131185283</v>
+        <v>131177861</v>
       </c>
       <c r="B285" t="n">
-        <v>57881</v>
+        <v>79245</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -31170,39 +31170,34 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
-      <c r="M285" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P285" t="inlineStr">
         <is>
-          <t>Navarnäsberget, Dlr</t>
+          <t>Ytter-Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>440715</v>
+        <v>440765</v>
       </c>
       <c r="R285" t="n">
-        <v>6815098</v>
+        <v>6815236</v>
       </c>
       <c r="S285" t="n">
         <v>10</v>
@@ -31232,9 +31227,19 @@
           <t>2026-02-16</t>
         </is>
       </c>
+      <c r="Z285" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AA285" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AB285" t="inlineStr">
+        <is>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD285" t="b">
@@ -31261,10 +31266,10 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>131178243</v>
+        <v>131175229</v>
       </c>
       <c r="B286" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -31272,39 +31277,34 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I286" t="inlineStr"/>
-      <c r="M286" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P286" t="inlineStr">
         <is>
           <t>Ytter-Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>440782</v>
+        <v>440944</v>
       </c>
       <c r="R286" t="n">
-        <v>6815262</v>
+        <v>6814965</v>
       </c>
       <c r="S286" t="n">
         <v>10</v>
@@ -31347,11 +31347,6 @@
       <c r="AB286" t="inlineStr">
         <is>
           <t>09:13</t>
-        </is>
-      </c>
-      <c r="AC286" t="inlineStr">
-        <is>
-          <t>2 bild på tall</t>
         </is>
       </c>
       <c r="AD286" t="b">
@@ -31378,10 +31373,10 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>131170627</v>
+        <v>131176451</v>
       </c>
       <c r="B287" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -31389,39 +31384,34 @@
         </is>
       </c>
       <c r="E287" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I287" t="inlineStr"/>
-      <c r="M287" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P287" t="inlineStr">
         <is>
           <t>Ytter-Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>441047</v>
+        <v>440856</v>
       </c>
       <c r="R287" t="n">
-        <v>6814660</v>
+        <v>6815124</v>
       </c>
       <c r="S287" t="n">
         <v>10</v>
@@ -31490,10 +31480,10 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>131186199</v>
+        <v>131185283</v>
       </c>
       <c r="B288" t="n">
-        <v>57884</v>
+        <v>57881</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -31501,16 +31491,16 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -31521,7 +31511,7 @@
       <c r="I288" t="inlineStr"/>
       <c r="M288" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P288" t="inlineStr">
@@ -31530,10 +31520,10 @@
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>440702</v>
+        <v>440715</v>
       </c>
       <c r="R288" t="n">
-        <v>6814996</v>
+        <v>6815098</v>
       </c>
       <c r="S288" t="n">
         <v>10</v>
@@ -31566,11 +31556,6 @@
       <c r="AA288" t="inlineStr">
         <is>
           <t>2026-02-16</t>
-        </is>
-      </c>
-      <c r="AC288" t="inlineStr">
-        <is>
-          <t>1 bild, samma gran som spillkr</t>
         </is>
       </c>
       <c r="AD288" t="b">
@@ -31597,10 +31582,10 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>131177861</v>
+        <v>131178243</v>
       </c>
       <c r="B289" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -31608,34 +31593,39 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I289" t="inlineStr"/>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P289" t="inlineStr">
         <is>
           <t>Ytter-Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>440765</v>
+        <v>440782</v>
       </c>
       <c r="R289" t="n">
-        <v>6815236</v>
+        <v>6815262</v>
       </c>
       <c r="S289" t="n">
         <v>10</v>
@@ -31678,6 +31668,11 @@
       <c r="AB289" t="inlineStr">
         <is>
           <t>09:13</t>
+        </is>
+      </c>
+      <c r="AC289" t="inlineStr">
+        <is>
+          <t>2 bild på tall</t>
         </is>
       </c>
       <c r="AD289" t="b">
@@ -31704,10 +31699,10 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>131175229</v>
+        <v>131170627</v>
       </c>
       <c r="B290" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -31715,34 +31710,39 @@
         </is>
       </c>
       <c r="E290" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I290" t="inlineStr"/>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P290" t="inlineStr">
         <is>
           <t>Ytter-Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q290" t="n">
-        <v>440944</v>
+        <v>441047</v>
       </c>
       <c r="R290" t="n">
-        <v>6814965</v>
+        <v>6814660</v>
       </c>
       <c r="S290" t="n">
         <v>10</v>
@@ -31811,10 +31811,10 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>131176451</v>
+        <v>131186199</v>
       </c>
       <c r="B291" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -31822,34 +31822,39 @@
         </is>
       </c>
       <c r="E291" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I291" t="inlineStr"/>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P291" t="inlineStr">
         <is>
-          <t>Ytter-Navardalen, Dlr</t>
+          <t>Navarnäsberget, Dlr</t>
         </is>
       </c>
       <c r="Q291" t="n">
-        <v>440856</v>
+        <v>440702</v>
       </c>
       <c r="R291" t="n">
-        <v>6815124</v>
+        <v>6814996</v>
       </c>
       <c r="S291" t="n">
         <v>10</v>
@@ -31879,19 +31884,14 @@
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="Z291" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AA291" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="AB291" t="inlineStr">
-        <is>
-          <t>09:13</t>
+      <c r="AC291" t="inlineStr">
+        <is>
+          <t>1 bild, samma gran som spillkr</t>
         </is>
       </c>
       <c r="AD291" t="b">

--- a/artfynd/A 5994-2026 artfynd.xlsx
+++ b/artfynd/A 5994-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131195663</v>
+        <v>131195625</v>
       </c>
       <c r="B2" t="n">
-        <v>78257</v>
+        <v>57884</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440887</v>
+        <v>440675</v>
       </c>
       <c r="R2" t="n">
-        <v>6815021</v>
+        <v>6815027</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,45 +787,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131195571</v>
+        <v>131195599</v>
       </c>
       <c r="B3" t="n">
-        <v>91773</v>
+        <v>57884</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440493</v>
+        <v>440704</v>
       </c>
       <c r="R3" t="n">
-        <v>6815011</v>
+        <v>6815002</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131195625</v>
+        <v>131195618</v>
       </c>
       <c r="B4" t="n">
         <v>57884</v>
@@ -929,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440675</v>
+        <v>440764</v>
       </c>
       <c r="R4" t="n">
-        <v>6815027</v>
+        <v>6815130</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131195599</v>
+        <v>131195621</v>
       </c>
       <c r="B5" t="n">
         <v>57884</v>
@@ -1032,7 +1042,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1041,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440704</v>
+        <v>441062</v>
       </c>
       <c r="R5" t="n">
-        <v>6815002</v>
+        <v>6815338</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131195618</v>
+        <v>131195663</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>78257</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,39 +1134,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440764</v>
+        <v>440887</v>
       </c>
       <c r="R6" t="n">
-        <v>6815130</v>
+        <v>6815021</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,7 +1203,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131195621</v>
+        <v>131195799</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1236,39 +1241,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441062</v>
+        <v>440984</v>
       </c>
       <c r="R7" t="n">
-        <v>6815338</v>
+        <v>6815335</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,7 +1337,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131195799</v>
+        <v>131195702</v>
       </c>
       <c r="B8" t="n">
         <v>79245</v>
@@ -1366,16 +1366,21 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440984</v>
+        <v>440424</v>
       </c>
       <c r="R8" t="n">
-        <v>6815335</v>
+        <v>6815142</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,7 +1412,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1417,7 +1422,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1444,10 +1449,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131195702</v>
+        <v>131195557</v>
       </c>
       <c r="B9" t="n">
-        <v>79245</v>
+        <v>83225</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,39 +1460,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440424</v>
+        <v>440888</v>
       </c>
       <c r="R9" t="n">
-        <v>6815142</v>
+        <v>6815023</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1556,10 +1556,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131195557</v>
+        <v>131195899</v>
       </c>
       <c r="B10" t="n">
-        <v>83225</v>
+        <v>79245</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1567,21 +1567,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440888</v>
+        <v>440906</v>
       </c>
       <c r="R10" t="n">
-        <v>6815023</v>
+        <v>6814493</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1663,32 +1663,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131195899</v>
+        <v>131195571</v>
       </c>
       <c r="B11" t="n">
-        <v>79245</v>
+        <v>91776</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440906</v>
+        <v>440493</v>
       </c>
       <c r="R11" t="n">
-        <v>6814493</v>
+        <v>6815011</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2950,7 +2950,7 @@
         <v>131195654</v>
       </c>
       <c r="B23" t="n">
-        <v>92269</v>
+        <v>92272</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -4567,27 +4567,27 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131195551</v>
+        <v>131195643</v>
       </c>
       <c r="B38" t="n">
-        <v>5197</v>
+        <v>57881</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4598,7 +4598,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4607,10 +4607,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440944</v>
+        <v>440858</v>
       </c>
       <c r="R38" t="n">
-        <v>6814700</v>
+        <v>6815063</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4679,27 +4679,27 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131195643</v>
+        <v>131195551</v>
       </c>
       <c r="B39" t="n">
-        <v>57881</v>
+        <v>5197</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4710,7 +4710,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4719,10 +4719,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440858</v>
+        <v>440944</v>
       </c>
       <c r="R39" t="n">
-        <v>6815063</v>
+        <v>6814700</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4754,7 +4754,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4791,32 +4791,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131195570</v>
+        <v>131195579</v>
       </c>
       <c r="B40" t="n">
-        <v>91773</v>
+        <v>91813</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4826,10 +4826,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>441037</v>
+        <v>440686</v>
       </c>
       <c r="R40" t="n">
-        <v>6815351</v>
+        <v>6815080</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4861,7 +4861,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5326,32 +5326,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131195893</v>
+        <v>131195570</v>
       </c>
       <c r="B45" t="n">
-        <v>79245</v>
+        <v>91776</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5361,10 +5361,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440928</v>
+        <v>441037</v>
       </c>
       <c r="R45" t="n">
-        <v>6814610</v>
+        <v>6815351</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5433,7 +5433,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131195696</v>
+        <v>131195893</v>
       </c>
       <c r="B46" t="n">
         <v>79245</v>
@@ -5462,21 +5462,16 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440740</v>
+        <v>440928</v>
       </c>
       <c r="R46" t="n">
-        <v>6815216</v>
+        <v>6814610</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5508,7 +5503,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5518,7 +5513,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5545,10 +5540,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131195579</v>
+        <v>131195696</v>
       </c>
       <c r="B47" t="n">
-        <v>91810</v>
+        <v>79245</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5556,34 +5551,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>440686</v>
+        <v>440740</v>
       </c>
       <c r="R47" t="n">
-        <v>6815080</v>
+        <v>6815216</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5652,10 +5652,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131195646</v>
+        <v>131195792</v>
       </c>
       <c r="B48" t="n">
-        <v>57881</v>
+        <v>79245</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5663,39 +5663,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>440867</v>
+        <v>440746</v>
       </c>
       <c r="R48" t="n">
-        <v>6814841</v>
+        <v>6815201</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5727,7 +5722,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5737,7 +5732,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5764,10 +5759,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131195648</v>
+        <v>131195826</v>
       </c>
       <c r="B49" t="n">
-        <v>57881</v>
+        <v>79245</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5775,39 +5770,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440835</v>
+        <v>440688</v>
       </c>
       <c r="R49" t="n">
-        <v>6815088</v>
+        <v>6815083</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5839,7 +5829,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5849,7 +5839,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5876,7 +5866,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131195792</v>
+        <v>131195772</v>
       </c>
       <c r="B50" t="n">
         <v>79245</v>
@@ -5911,10 +5901,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>440746</v>
+        <v>440955</v>
       </c>
       <c r="R50" t="n">
-        <v>6815201</v>
+        <v>6814897</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5946,7 +5936,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5956,7 +5946,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5983,7 +5973,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131195826</v>
+        <v>131195880</v>
       </c>
       <c r="B51" t="n">
         <v>79245</v>
@@ -6018,10 +6008,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>440688</v>
+        <v>440820</v>
       </c>
       <c r="R51" t="n">
-        <v>6815083</v>
+        <v>6814616</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6053,7 +6043,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6063,7 +6053,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6090,7 +6080,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131195772</v>
+        <v>131195803</v>
       </c>
       <c r="B52" t="n">
         <v>79245</v>
@@ -6125,10 +6115,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>440955</v>
+        <v>441101</v>
       </c>
       <c r="R52" t="n">
-        <v>6814897</v>
+        <v>6815283</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6160,7 +6150,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6170,7 +6160,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6197,7 +6187,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131195880</v>
+        <v>131195748</v>
       </c>
       <c r="B53" t="n">
         <v>79245</v>
@@ -6232,10 +6222,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>440820</v>
+        <v>441151</v>
       </c>
       <c r="R53" t="n">
-        <v>6814616</v>
+        <v>6814715</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6267,7 +6257,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6277,7 +6267,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6304,7 +6294,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131195803</v>
+        <v>131195860</v>
       </c>
       <c r="B54" t="n">
         <v>79245</v>
@@ -6339,10 +6329,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>441101</v>
+        <v>440531</v>
       </c>
       <c r="R54" t="n">
-        <v>6815283</v>
+        <v>6815095</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6374,7 +6364,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6384,7 +6374,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6411,7 +6401,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131195748</v>
+        <v>131195778</v>
       </c>
       <c r="B55" t="n">
         <v>79245</v>
@@ -6446,10 +6436,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>441151</v>
+        <v>440906</v>
       </c>
       <c r="R55" t="n">
-        <v>6814715</v>
+        <v>6814928</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6481,7 +6471,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6491,7 +6481,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6518,10 +6508,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131195860</v>
+        <v>131195608</v>
       </c>
       <c r="B56" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6529,34 +6519,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>440531</v>
+        <v>441099</v>
       </c>
       <c r="R56" t="n">
-        <v>6815095</v>
+        <v>6814647</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6588,7 +6583,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6598,7 +6593,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6625,10 +6620,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131195778</v>
+        <v>131195620</v>
       </c>
       <c r="B57" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6636,34 +6631,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>440906</v>
+        <v>440802</v>
       </c>
       <c r="R57" t="n">
-        <v>6814928</v>
+        <v>6815292</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6695,7 +6695,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6732,10 +6732,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131195608</v>
+        <v>131195646</v>
       </c>
       <c r="B58" t="n">
-        <v>57884</v>
+        <v>57881</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6743,16 +6743,16 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6763,7 +6763,7 @@
       <c r="I58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -6772,10 +6772,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>441099</v>
+        <v>440867</v>
       </c>
       <c r="R58" t="n">
-        <v>6814647</v>
+        <v>6814841</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6807,7 +6807,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6844,10 +6844,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131195620</v>
+        <v>131195648</v>
       </c>
       <c r="B59" t="n">
-        <v>57884</v>
+        <v>57881</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6855,16 +6855,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6884,10 +6884,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>440802</v>
+        <v>440835</v>
       </c>
       <c r="R59" t="n">
-        <v>6815292</v>
+        <v>6815088</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6919,7 +6919,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8265,10 +8265,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131195757</v>
+        <v>131195596</v>
       </c>
       <c r="B72" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8276,34 +8276,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>441069</v>
+        <v>440681</v>
       </c>
       <c r="R72" t="n">
-        <v>6814629</v>
+        <v>6815022</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8335,7 +8340,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8345,7 +8350,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8372,10 +8382,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131195848</v>
+        <v>131195680</v>
       </c>
       <c r="B73" t="n">
-        <v>79245</v>
+        <v>91833</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8383,23 +8393,19 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -8407,10 +8413,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>440440</v>
+        <v>440829</v>
       </c>
       <c r="R73" t="n">
-        <v>6815092</v>
+        <v>6814569</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8442,7 +8448,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8452,7 +8458,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8479,10 +8485,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131195843</v>
+        <v>131195678</v>
       </c>
       <c r="B74" t="n">
-        <v>79245</v>
+        <v>91833</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8490,23 +8496,19 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -8514,10 +8516,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>440489</v>
+        <v>440423</v>
       </c>
       <c r="R74" t="n">
-        <v>6815022</v>
+        <v>6815143</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8549,7 +8551,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8559,7 +8561,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8586,7 +8588,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131195870</v>
+        <v>131195757</v>
       </c>
       <c r="B75" t="n">
         <v>79245</v>
@@ -8621,10 +8623,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>440857</v>
+        <v>441069</v>
       </c>
       <c r="R75" t="n">
-        <v>6814795</v>
+        <v>6814629</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8656,7 +8658,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8666,7 +8668,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8693,7 +8695,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131195755</v>
+        <v>131195848</v>
       </c>
       <c r="B76" t="n">
         <v>79245</v>
@@ -8728,10 +8730,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>441098</v>
+        <v>440440</v>
       </c>
       <c r="R76" t="n">
-        <v>6814630</v>
+        <v>6815092</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8763,7 +8765,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8773,7 +8775,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8800,7 +8802,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131195830</v>
+        <v>131195843</v>
       </c>
       <c r="B77" t="n">
         <v>79245</v>
@@ -8835,10 +8837,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>440672</v>
+        <v>440489</v>
       </c>
       <c r="R77" t="n">
-        <v>6815003</v>
+        <v>6815022</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8870,7 +8872,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8880,7 +8882,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8907,10 +8909,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131195671</v>
+        <v>131195870</v>
       </c>
       <c r="B78" t="n">
-        <v>79002</v>
+        <v>79245</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8918,21 +8920,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8942,10 +8944,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>440740</v>
+        <v>440857</v>
       </c>
       <c r="R78" t="n">
-        <v>6814579</v>
+        <v>6814795</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8977,7 +8979,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8987,7 +8989,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9014,7 +9016,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131195805</v>
+        <v>131195755</v>
       </c>
       <c r="B79" t="n">
         <v>79245</v>
@@ -9049,10 +9051,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>441170</v>
+        <v>441098</v>
       </c>
       <c r="R79" t="n">
-        <v>6815286</v>
+        <v>6814630</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9084,7 +9086,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9094,7 +9096,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9121,10 +9123,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131195680</v>
+        <v>131195830</v>
       </c>
       <c r="B80" t="n">
-        <v>91830</v>
+        <v>79245</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9132,19 +9134,23 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -9152,10 +9158,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>440829</v>
+        <v>440672</v>
       </c>
       <c r="R80" t="n">
-        <v>6814569</v>
+        <v>6815003</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9187,7 +9193,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9197,7 +9203,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9224,10 +9230,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131195678</v>
+        <v>131195671</v>
       </c>
       <c r="B81" t="n">
-        <v>91830</v>
+        <v>79002</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9235,19 +9241,23 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5432</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr"/>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -9255,10 +9265,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>440423</v>
+        <v>440740</v>
       </c>
       <c r="R81" t="n">
-        <v>6815143</v>
+        <v>6814579</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9290,7 +9300,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9300,7 +9310,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9327,10 +9337,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131195596</v>
+        <v>131195805</v>
       </c>
       <c r="B82" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9338,39 +9348,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>440681</v>
+        <v>441170</v>
       </c>
       <c r="R82" t="n">
-        <v>6815022</v>
+        <v>6815286</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9402,7 +9407,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9412,12 +9417,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:44</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9444,10 +9444,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131195642</v>
+        <v>131195595</v>
       </c>
       <c r="B83" t="n">
-        <v>57881</v>
+        <v>57884</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9455,16 +9455,16 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -9475,7 +9475,7 @@
       <c r="I83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9484,10 +9484,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>440965</v>
+        <v>440866</v>
       </c>
       <c r="R83" t="n">
-        <v>6814690</v>
+        <v>6815064</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9529,7 +9529,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9556,10 +9561,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131195595</v>
+        <v>131195642</v>
       </c>
       <c r="B84" t="n">
-        <v>57884</v>
+        <v>57881</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9567,16 +9572,16 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -9587,7 +9592,7 @@
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -9596,10 +9601,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>440866</v>
+        <v>440965</v>
       </c>
       <c r="R84" t="n">
-        <v>6815064</v>
+        <v>6814690</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9631,7 +9636,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9641,12 +9646,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:48</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9673,10 +9673,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131195769</v>
+        <v>131195664</v>
       </c>
       <c r="B85" t="n">
-        <v>79245</v>
+        <v>78257</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9684,21 +9684,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9708,10 +9708,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>440947</v>
+        <v>440489</v>
       </c>
       <c r="R85" t="n">
-        <v>6814871</v>
+        <v>6815022</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9743,7 +9743,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9753,7 +9753,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9780,7 +9780,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131195766</v>
+        <v>131195769</v>
       </c>
       <c r="B86" t="n">
         <v>79245</v>
@@ -9815,10 +9815,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>440973</v>
+        <v>440947</v>
       </c>
       <c r="R86" t="n">
-        <v>6814836</v>
+        <v>6814871</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9850,7 +9850,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9860,7 +9860,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9887,7 +9887,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131195889</v>
+        <v>131195766</v>
       </c>
       <c r="B87" t="n">
         <v>79245</v>
@@ -9922,10 +9922,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>440851</v>
+        <v>440973</v>
       </c>
       <c r="R87" t="n">
-        <v>6814582</v>
+        <v>6814836</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9957,7 +9957,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9967,7 +9967,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9994,7 +9994,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131195868</v>
+        <v>131195889</v>
       </c>
       <c r="B88" t="n">
         <v>79245</v>
@@ -10029,10 +10029,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>440849</v>
+        <v>440851</v>
       </c>
       <c r="R88" t="n">
-        <v>6814889</v>
+        <v>6814582</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10074,7 +10074,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10101,7 +10101,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131195704</v>
+        <v>131195868</v>
       </c>
       <c r="B89" t="n">
         <v>79245</v>
@@ -10130,21 +10130,16 @@
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>440460</v>
+        <v>440849</v>
       </c>
       <c r="R89" t="n">
-        <v>6815198</v>
+        <v>6814889</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10176,7 +10171,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10186,7 +10181,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10213,7 +10208,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131195775</v>
+        <v>131195704</v>
       </c>
       <c r="B90" t="n">
         <v>79245</v>
@@ -10242,16 +10237,21 @@
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>440923</v>
+        <v>440460</v>
       </c>
       <c r="R90" t="n">
-        <v>6814881</v>
+        <v>6815198</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10283,7 +10283,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10293,7 +10293,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10320,7 +10320,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131195869</v>
+        <v>131195775</v>
       </c>
       <c r="B91" t="n">
         <v>79245</v>
@@ -10355,10 +10355,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>440867</v>
+        <v>440923</v>
       </c>
       <c r="R91" t="n">
-        <v>6814841</v>
+        <v>6814881</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10390,7 +10390,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10400,7 +10400,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10427,7 +10427,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131195861</v>
+        <v>131195869</v>
       </c>
       <c r="B92" t="n">
         <v>79245</v>
@@ -10462,10 +10462,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>440568</v>
+        <v>440867</v>
       </c>
       <c r="R92" t="n">
-        <v>6815075</v>
+        <v>6814841</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10497,7 +10497,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10507,7 +10507,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10534,10 +10534,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131195664</v>
+        <v>131195861</v>
       </c>
       <c r="B93" t="n">
-        <v>78257</v>
+        <v>79245</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10545,21 +10545,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10569,10 +10569,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>440489</v>
+        <v>440568</v>
       </c>
       <c r="R93" t="n">
-        <v>6815022</v>
+        <v>6815075</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10604,7 +10604,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12607,10 +12607,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>131195798</v>
+        <v>131195637</v>
       </c>
       <c r="B112" t="n">
-        <v>79245</v>
+        <v>58043</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12618,21 +12618,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12642,10 +12642,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>440943</v>
+        <v>441072</v>
       </c>
       <c r="R112" t="n">
-        <v>6815341</v>
+        <v>6814663</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12677,7 +12677,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12687,7 +12687,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12714,10 +12714,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131195842</v>
+        <v>131195662</v>
       </c>
       <c r="B113" t="n">
-        <v>79245</v>
+        <v>78257</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12725,21 +12725,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12749,10 +12749,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>440509</v>
+        <v>440925</v>
       </c>
       <c r="R113" t="n">
-        <v>6815018</v>
+        <v>6814889</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12784,7 +12784,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12794,7 +12794,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12821,7 +12821,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131195776</v>
+        <v>131195798</v>
       </c>
       <c r="B114" t="n">
         <v>79245</v>
@@ -12856,10 +12856,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>440926</v>
+        <v>440943</v>
       </c>
       <c r="R114" t="n">
-        <v>6814927</v>
+        <v>6815341</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12891,7 +12891,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12901,7 +12901,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12928,32 +12928,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131195884</v>
+        <v>131195567</v>
       </c>
       <c r="B115" t="n">
-        <v>79245</v>
+        <v>91776</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12963,10 +12963,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>440736</v>
+        <v>440907</v>
       </c>
       <c r="R115" t="n">
-        <v>6814569</v>
+        <v>6814875</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12998,7 +12998,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13008,7 +13008,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13035,7 +13035,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131195739</v>
+        <v>131195842</v>
       </c>
       <c r="B116" t="n">
         <v>79245</v>
@@ -13070,10 +13070,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>441199</v>
+        <v>440509</v>
       </c>
       <c r="R116" t="n">
-        <v>6814633</v>
+        <v>6815018</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13105,7 +13105,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13115,7 +13115,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13142,7 +13142,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131195871</v>
+        <v>131195776</v>
       </c>
       <c r="B117" t="n">
         <v>79245</v>
@@ -13177,10 +13177,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>440853</v>
+        <v>440926</v>
       </c>
       <c r="R117" t="n">
-        <v>6814767</v>
+        <v>6814927</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13212,7 +13212,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13222,7 +13222,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13249,7 +13249,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131195839</v>
+        <v>131195884</v>
       </c>
       <c r="B118" t="n">
         <v>79245</v>
@@ -13284,10 +13284,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>440519</v>
+        <v>440736</v>
       </c>
       <c r="R118" t="n">
-        <v>6814964</v>
+        <v>6814569</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13319,7 +13319,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13329,7 +13329,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13356,10 +13356,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131195558</v>
+        <v>131195739</v>
       </c>
       <c r="B119" t="n">
-        <v>83225</v>
+        <v>79245</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13367,21 +13367,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13391,10 +13391,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>440881</v>
+        <v>441199</v>
       </c>
       <c r="R119" t="n">
-        <v>6815052</v>
+        <v>6814633</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13426,7 +13426,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13436,7 +13436,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13463,7 +13463,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131195840</v>
+        <v>131195871</v>
       </c>
       <c r="B120" t="n">
         <v>79245</v>
@@ -13498,10 +13498,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>440518</v>
+        <v>440853</v>
       </c>
       <c r="R120" t="n">
-        <v>6814966</v>
+        <v>6814767</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13543,7 +13543,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13570,7 +13570,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>131195844</v>
+        <v>131195839</v>
       </c>
       <c r="B121" t="n">
         <v>79245</v>
@@ -13605,10 +13605,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>440488</v>
+        <v>440519</v>
       </c>
       <c r="R121" t="n">
-        <v>6815047</v>
+        <v>6814964</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13640,7 +13640,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13650,7 +13650,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13677,32 +13677,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>131195567</v>
+        <v>131195558</v>
       </c>
       <c r="B122" t="n">
-        <v>91773</v>
+        <v>83225</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13712,10 +13712,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>440907</v>
+        <v>440881</v>
       </c>
       <c r="R122" t="n">
-        <v>6814875</v>
+        <v>6815052</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13747,7 +13747,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13757,7 +13757,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13784,32 +13784,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>131195573</v>
+        <v>131195840</v>
       </c>
       <c r="B123" t="n">
-        <v>91773</v>
+        <v>79245</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13819,10 +13819,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>440508</v>
+        <v>440518</v>
       </c>
       <c r="R123" t="n">
-        <v>6815137</v>
+        <v>6814966</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13854,7 +13854,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13864,7 +13864,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13891,10 +13891,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>131195637</v>
+        <v>131195844</v>
       </c>
       <c r="B124" t="n">
-        <v>58043</v>
+        <v>79245</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13902,21 +13902,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13926,10 +13926,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>441072</v>
+        <v>440488</v>
       </c>
       <c r="R124" t="n">
-        <v>6814663</v>
+        <v>6815047</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13961,7 +13961,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13971,7 +13971,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13998,32 +13998,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>131195662</v>
+        <v>131195573</v>
       </c>
       <c r="B125" t="n">
-        <v>78257</v>
+        <v>91776</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>228579</v>
+        <v>5447</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14033,10 +14033,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>440925</v>
+        <v>440508</v>
       </c>
       <c r="R125" t="n">
-        <v>6814889</v>
+        <v>6815137</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14068,7 +14068,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14078,7 +14078,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14538,10 +14538,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>131195650</v>
+        <v>131195624</v>
       </c>
       <c r="B130" t="n">
-        <v>57881</v>
+        <v>57884</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14549,16 +14549,16 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -14578,10 +14578,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>441062</v>
+        <v>440693</v>
       </c>
       <c r="R130" t="n">
-        <v>6815341</v>
+        <v>6815072</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14613,7 +14613,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14623,7 +14623,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14650,7 +14650,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>131195624</v>
+        <v>131195630</v>
       </c>
       <c r="B131" t="n">
         <v>57884</v>
@@ -14690,10 +14690,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>440693</v>
+        <v>440458</v>
       </c>
       <c r="R131" t="n">
-        <v>6815072</v>
+        <v>6815199</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14725,7 +14725,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14735,7 +14735,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14762,10 +14762,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>131195630</v>
+        <v>131195650</v>
       </c>
       <c r="B132" t="n">
-        <v>57884</v>
+        <v>57881</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14773,16 +14773,16 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -14802,10 +14802,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>440458</v>
+        <v>441062</v>
       </c>
       <c r="R132" t="n">
-        <v>6815199</v>
+        <v>6815341</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14837,7 +14837,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14847,7 +14847,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15857,10 +15857,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>131195906</v>
+        <v>131195673</v>
       </c>
       <c r="B142" t="n">
-        <v>79245</v>
+        <v>79324</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15868,21 +15868,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15892,10 +15892,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>440879</v>
+        <v>440938</v>
       </c>
       <c r="R142" t="n">
-        <v>6814346</v>
+        <v>6814901</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15927,7 +15927,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15937,7 +15937,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15964,7 +15964,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>131195891</v>
+        <v>131195906</v>
       </c>
       <c r="B143" t="n">
         <v>79245</v>
@@ -15999,10 +15999,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>440887</v>
+        <v>440879</v>
       </c>
       <c r="R143" t="n">
-        <v>6814607</v>
+        <v>6814346</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16034,7 +16034,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16071,7 +16071,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>131195827</v>
+        <v>131195891</v>
       </c>
       <c r="B144" t="n">
         <v>79245</v>
@@ -16106,10 +16106,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>440707</v>
+        <v>440887</v>
       </c>
       <c r="R144" t="n">
-        <v>6815064</v>
+        <v>6814607</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16141,7 +16141,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16151,7 +16151,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16178,7 +16178,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>131195710</v>
+        <v>131195827</v>
       </c>
       <c r="B145" t="n">
         <v>79245</v>
@@ -16207,21 +16207,16 @@
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>440823</v>
+        <v>440707</v>
       </c>
       <c r="R145" t="n">
-        <v>6815085</v>
+        <v>6815064</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16253,7 +16248,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16263,7 +16258,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16290,10 +16285,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>131195554</v>
+        <v>131195710</v>
       </c>
       <c r="B146" t="n">
-        <v>83225</v>
+        <v>79245</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16301,34 +16296,39 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P146" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>440956</v>
+        <v>440823</v>
       </c>
       <c r="R146" t="n">
-        <v>6814835</v>
+        <v>6815085</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16360,7 +16360,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16370,7 +16370,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16397,10 +16397,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>131195773</v>
+        <v>131195554</v>
       </c>
       <c r="B147" t="n">
-        <v>79245</v>
+        <v>83225</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16408,21 +16408,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16432,10 +16432,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>440934</v>
+        <v>440956</v>
       </c>
       <c r="R147" t="n">
-        <v>6814904</v>
+        <v>6814835</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16467,7 +16467,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16477,7 +16477,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16504,7 +16504,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>131195864</v>
+        <v>131195773</v>
       </c>
       <c r="B148" t="n">
         <v>79245</v>
@@ -16539,10 +16539,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>440728</v>
+        <v>440934</v>
       </c>
       <c r="R148" t="n">
-        <v>6814986</v>
+        <v>6814904</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16574,7 +16574,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16584,7 +16584,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16611,7 +16611,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>131195903</v>
+        <v>131195864</v>
       </c>
       <c r="B149" t="n">
         <v>79245</v>
@@ -16646,10 +16646,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>440822</v>
+        <v>440728</v>
       </c>
       <c r="R149" t="n">
-        <v>6814424</v>
+        <v>6814986</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16681,7 +16681,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16691,7 +16691,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16718,7 +16718,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>131195747</v>
+        <v>131195903</v>
       </c>
       <c r="B150" t="n">
         <v>79245</v>
@@ -16753,10 +16753,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>441175</v>
+        <v>440822</v>
       </c>
       <c r="R150" t="n">
-        <v>6814695</v>
+        <v>6814424</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16788,7 +16788,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16798,7 +16798,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16825,7 +16825,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>131195875</v>
+        <v>131195747</v>
       </c>
       <c r="B151" t="n">
         <v>79245</v>
@@ -16860,10 +16860,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>440861</v>
+        <v>441175</v>
       </c>
       <c r="R151" t="n">
-        <v>6814659</v>
+        <v>6814695</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16895,7 +16895,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16905,7 +16905,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16932,10 +16932,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>131195652</v>
+        <v>131195875</v>
       </c>
       <c r="B152" t="n">
-        <v>57881</v>
+        <v>79245</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16943,39 +16943,34 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P152" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>440755</v>
+        <v>440861</v>
       </c>
       <c r="R152" t="n">
-        <v>6815170</v>
+        <v>6814659</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17007,7 +17002,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -17017,7 +17012,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17044,10 +17039,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>131195673</v>
+        <v>131195652</v>
       </c>
       <c r="B153" t="n">
-        <v>79324</v>
+        <v>57881</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17055,34 +17050,39 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>864</v>
+        <v>100049</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>440938</v>
+        <v>440755</v>
       </c>
       <c r="R153" t="n">
-        <v>6814901</v>
+        <v>6815170</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17124,7 +17124,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17719,7 +17719,7 @@
         <v>131195913</v>
       </c>
       <c r="B159" t="n">
-        <v>89195</v>
+        <v>89198</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19005,10 +19005,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>131195914</v>
+        <v>131195847</v>
       </c>
       <c r="B171" t="n">
-        <v>89195</v>
+        <v>79245</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19016,21 +19016,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -19040,10 +19040,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>440856</v>
+        <v>440465</v>
       </c>
       <c r="R171" t="n">
-        <v>6814840</v>
+        <v>6815075</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19075,7 +19075,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -19085,7 +19085,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19112,7 +19112,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>131195847</v>
+        <v>131195788</v>
       </c>
       <c r="B172" t="n">
         <v>79245</v>
@@ -19147,10 +19147,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>440465</v>
+        <v>440795</v>
       </c>
       <c r="R172" t="n">
-        <v>6815075</v>
+        <v>6815104</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19182,7 +19182,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -19192,7 +19192,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19219,7 +19219,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>131195788</v>
+        <v>131195901</v>
       </c>
       <c r="B173" t="n">
         <v>79245</v>
@@ -19254,10 +19254,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>440795</v>
+        <v>440885</v>
       </c>
       <c r="R173" t="n">
-        <v>6815104</v>
+        <v>6814475</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19289,7 +19289,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -19299,7 +19299,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19326,7 +19326,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>131195901</v>
+        <v>131195804</v>
       </c>
       <c r="B174" t="n">
         <v>79245</v>
@@ -19361,10 +19361,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>440885</v>
+        <v>441158</v>
       </c>
       <c r="R174" t="n">
-        <v>6814475</v>
+        <v>6815289</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19396,7 +19396,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -19406,7 +19406,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19433,7 +19433,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>131195804</v>
+        <v>131195708</v>
       </c>
       <c r="B175" t="n">
         <v>79245</v>
@@ -19462,16 +19462,21 @@
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P175" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>441158</v>
+        <v>440774</v>
       </c>
       <c r="R175" t="n">
-        <v>6815289</v>
+        <v>6814546</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19503,7 +19508,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -19513,7 +19518,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19540,7 +19545,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>131195708</v>
+        <v>131195793</v>
       </c>
       <c r="B176" t="n">
         <v>79245</v>
@@ -19569,21 +19574,16 @@
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P176" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>440774</v>
+        <v>440758</v>
       </c>
       <c r="R176" t="n">
-        <v>6814546</v>
+        <v>6815261</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19615,7 +19615,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -19625,7 +19625,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19652,7 +19652,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>131195793</v>
+        <v>131195849</v>
       </c>
       <c r="B177" t="n">
         <v>79245</v>
@@ -19687,10 +19687,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>440758</v>
+        <v>440438</v>
       </c>
       <c r="R177" t="n">
-        <v>6815261</v>
+        <v>6815100</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19722,7 +19722,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -19732,7 +19732,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19759,7 +19759,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>131195849</v>
+        <v>131195783</v>
       </c>
       <c r="B178" t="n">
         <v>79245</v>
@@ -19794,10 +19794,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>440438</v>
+        <v>440881</v>
       </c>
       <c r="R178" t="n">
-        <v>6815100</v>
+        <v>6815052</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19829,7 +19829,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -19839,7 +19839,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19866,7 +19866,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>131195783</v>
+        <v>131195744</v>
       </c>
       <c r="B179" t="n">
         <v>79245</v>
@@ -19901,10 +19901,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>440881</v>
+        <v>441179</v>
       </c>
       <c r="R179" t="n">
-        <v>6815052</v>
+        <v>6814681</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19936,7 +19936,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -19946,7 +19946,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19973,10 +19973,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>131195744</v>
+        <v>131195914</v>
       </c>
       <c r="B180" t="n">
-        <v>79245</v>
+        <v>89198</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19984,21 +19984,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -20008,10 +20008,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>441179</v>
+        <v>440856</v>
       </c>
       <c r="R180" t="n">
-        <v>6814681</v>
+        <v>6814840</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20043,7 +20043,7 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -20053,7 +20053,7 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -21725,10 +21725,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>131195668</v>
+        <v>131195587</v>
       </c>
       <c r="B196" t="n">
-        <v>81230</v>
+        <v>57884</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21736,34 +21736,39 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1049</v>
+        <v>100109</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P196" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>440425</v>
+        <v>440939</v>
       </c>
       <c r="R196" t="n">
-        <v>6815146</v>
+        <v>6814909</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21795,7 +21800,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -21805,7 +21810,12 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AC196" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -21832,10 +21842,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>131195667</v>
+        <v>131195674</v>
       </c>
       <c r="B197" t="n">
-        <v>81230</v>
+        <v>79324</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -21843,21 +21853,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>1049</v>
+        <v>864</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -21867,10 +21877,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>441160</v>
+        <v>441088</v>
       </c>
       <c r="R197" t="n">
-        <v>6815244</v>
+        <v>6815269</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21902,7 +21912,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -21912,7 +21922,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21939,10 +21949,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>131195674</v>
+        <v>131195668</v>
       </c>
       <c r="B198" t="n">
-        <v>79324</v>
+        <v>81230</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21950,21 +21960,21 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>864</v>
+        <v>1049</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -21974,10 +21984,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>441088</v>
+        <v>440425</v>
       </c>
       <c r="R198" t="n">
-        <v>6815269</v>
+        <v>6815146</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22009,7 +22019,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -22019,7 +22029,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -22046,10 +22056,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>131195876</v>
+        <v>131195667</v>
       </c>
       <c r="B199" t="n">
-        <v>79245</v>
+        <v>81230</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22057,21 +22067,21 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -22081,10 +22091,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>440875</v>
+        <v>441160</v>
       </c>
       <c r="R199" t="n">
-        <v>6814650</v>
+        <v>6815244</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22116,7 +22126,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -22126,7 +22136,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -22153,7 +22163,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>131195823</v>
+        <v>131195876</v>
       </c>
       <c r="B200" t="n">
         <v>79245</v>
@@ -22188,10 +22198,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>440717</v>
+        <v>440875</v>
       </c>
       <c r="R200" t="n">
-        <v>6815120</v>
+        <v>6814650</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22223,7 +22233,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -22233,7 +22243,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -22260,7 +22270,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>131195771</v>
+        <v>131195823</v>
       </c>
       <c r="B201" t="n">
         <v>79245</v>
@@ -22295,10 +22305,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>440944</v>
+        <v>440717</v>
       </c>
       <c r="R201" t="n">
-        <v>6814890</v>
+        <v>6815120</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22330,7 +22340,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -22340,7 +22350,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -22367,7 +22377,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>131195808</v>
+        <v>131195771</v>
       </c>
       <c r="B202" t="n">
         <v>79245</v>
@@ -22402,10 +22412,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>441109</v>
+        <v>440944</v>
       </c>
       <c r="R202" t="n">
-        <v>6815261</v>
+        <v>6814890</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22437,7 +22447,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -22447,7 +22457,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -22474,7 +22484,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>131195781</v>
+        <v>131195808</v>
       </c>
       <c r="B203" t="n">
         <v>79245</v>
@@ -22509,10 +22519,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>440908</v>
+        <v>441109</v>
       </c>
       <c r="R203" t="n">
-        <v>6815012</v>
+        <v>6815261</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22544,7 +22554,7 @@
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -22554,7 +22564,7 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -22581,7 +22591,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>131195780</v>
+        <v>131195781</v>
       </c>
       <c r="B204" t="n">
         <v>79245</v>
@@ -22616,10 +22626,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>440931</v>
+        <v>440908</v>
       </c>
       <c r="R204" t="n">
-        <v>6814966</v>
+        <v>6815012</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22651,7 +22661,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -22661,7 +22671,7 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -22688,7 +22698,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>131195895</v>
+        <v>131195780</v>
       </c>
       <c r="B205" t="n">
         <v>79245</v>
@@ -22723,10 +22733,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>440948</v>
+        <v>440931</v>
       </c>
       <c r="R205" t="n">
-        <v>6814582</v>
+        <v>6814966</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -22758,7 +22768,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -22768,7 +22778,7 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -22795,7 +22805,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>131195865</v>
+        <v>131195895</v>
       </c>
       <c r="B206" t="n">
         <v>79245</v>
@@ -22830,10 +22840,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>440765</v>
+        <v>440948</v>
       </c>
       <c r="R206" t="n">
-        <v>6814953</v>
+        <v>6814582</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -22865,7 +22875,7 @@
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
@@ -22875,7 +22885,7 @@
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -22902,10 +22912,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>131195627</v>
+        <v>131195865</v>
       </c>
       <c r="B207" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -22913,39 +22923,34 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
-      <c r="M207" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P207" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>440466</v>
+        <v>440765</v>
       </c>
       <c r="R207" t="n">
-        <v>6815077</v>
+        <v>6814953</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22977,7 +22982,7 @@
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -22987,7 +22992,7 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -23014,7 +23019,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>131195587</v>
+        <v>131195627</v>
       </c>
       <c r="B208" t="n">
         <v>57884</v>
@@ -23045,7 +23050,7 @@
       <c r="I208" t="inlineStr"/>
       <c r="M208" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
@@ -23054,10 +23059,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>440939</v>
+        <v>440466</v>
       </c>
       <c r="R208" t="n">
-        <v>6814909</v>
+        <v>6815077</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23089,7 +23094,7 @@
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
@@ -23099,12 +23104,7 @@
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>10:05</t>
-        </is>
-      </c>
-      <c r="AC208" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -23992,10 +23992,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>131195666</v>
+        <v>131195628</v>
       </c>
       <c r="B217" t="n">
-        <v>81230</v>
+        <v>57884</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -24003,34 +24003,39 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>1049</v>
+        <v>100109</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P217" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>441125</v>
+        <v>440428</v>
       </c>
       <c r="R217" t="n">
-        <v>6815280</v>
+        <v>6815159</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -24062,7 +24067,7 @@
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
@@ -24072,7 +24077,7 @@
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -24099,7 +24104,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>131195628</v>
+        <v>131195634</v>
       </c>
       <c r="B218" t="n">
         <v>57884</v>
@@ -24139,10 +24144,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>440428</v>
+        <v>440584</v>
       </c>
       <c r="R218" t="n">
-        <v>6815159</v>
+        <v>6815078</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24174,7 +24179,7 @@
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
@@ -24184,7 +24189,7 @@
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -24211,10 +24216,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>131195634</v>
+        <v>131195666</v>
       </c>
       <c r="B219" t="n">
-        <v>57884</v>
+        <v>81230</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24222,39 +24227,34 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>100109</v>
+        <v>1049</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
-      <c r="M219" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P219" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>440584</v>
+        <v>441125</v>
       </c>
       <c r="R219" t="n">
-        <v>6815078</v>
+        <v>6815280</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24286,7 +24286,7 @@
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
@@ -24296,7 +24296,7 @@
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -25508,7 +25508,7 @@
         <v>131197397</v>
       </c>
       <c r="B231" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -25708,10 +25708,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>131197406</v>
+        <v>131197394</v>
       </c>
       <c r="B233" t="n">
-        <v>79245</v>
+        <v>57881</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -25719,34 +25719,42 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
+      <c r="K233" t="inlineStr"/>
+      <c r="L233" t="inlineStr"/>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>441114</v>
+        <v>440950</v>
       </c>
       <c r="R233" t="n">
-        <v>6814652</v>
+        <v>6815375</v>
       </c>
       <c r="S233" t="n">
         <v>25</v>
@@ -25779,6 +25787,11 @@
       <c r="AA233" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AC233" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -25805,10 +25818,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>131197394</v>
+        <v>131197390</v>
       </c>
       <c r="B234" t="n">
-        <v>57881</v>
+        <v>57884</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -25816,16 +25829,16 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -25838,7 +25851,7 @@
       <c r="L234" t="inlineStr"/>
       <c r="M234" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N234" t="inlineStr"/>
@@ -25848,10 +25861,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>440950</v>
+        <v>440857</v>
       </c>
       <c r="R234" t="n">
-        <v>6815375</v>
+        <v>6815078</v>
       </c>
       <c r="S234" t="n">
         <v>25</v>
@@ -25884,11 +25897,6 @@
       <c r="AA234" t="inlineStr">
         <is>
           <t>2026-02-16</t>
-        </is>
-      </c>
-      <c r="AC234" t="inlineStr">
-        <is>
-          <t>Födosök</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -25915,10 +25923,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>131197390</v>
+        <v>131197406</v>
       </c>
       <c r="B235" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -25926,42 +25934,34 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
-      <c r="K235" t="inlineStr"/>
-      <c r="L235" t="inlineStr"/>
-      <c r="M235" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>440857</v>
+        <v>441114</v>
       </c>
       <c r="R235" t="n">
-        <v>6815078</v>
+        <v>6814652</v>
       </c>
       <c r="S235" t="n">
         <v>25</v>
@@ -26023,7 +26023,7 @@
         <v>131197398</v>
       </c>
       <c r="B236" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -26226,7 +26226,7 @@
         <v>131197396</v>
       </c>
       <c r="B238" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -26722,10 +26722,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>131197393</v>
+        <v>131197391</v>
       </c>
       <c r="B243" t="n">
-        <v>57881</v>
+        <v>57884</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -26733,16 +26733,16 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -26765,10 +26765,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>440751</v>
+        <v>440926</v>
       </c>
       <c r="R243" t="n">
-        <v>6815273</v>
+        <v>6814891</v>
       </c>
       <c r="S243" t="n">
         <v>25</v>
@@ -26827,10 +26827,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>131197391</v>
+        <v>131197393</v>
       </c>
       <c r="B244" t="n">
-        <v>57884</v>
+        <v>57881</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -26838,16 +26838,16 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -26870,10 +26870,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>440926</v>
+        <v>440751</v>
       </c>
       <c r="R244" t="n">
-        <v>6814891</v>
+        <v>6815273</v>
       </c>
       <c r="S244" t="n">
         <v>25</v>
@@ -27126,45 +27126,53 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>131197380</v>
+        <v>131197389</v>
       </c>
       <c r="B247" t="n">
-        <v>91773</v>
+        <v>57884</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
+      <c r="K247" t="inlineStr"/>
+      <c r="L247" t="inlineStr"/>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N247" t="inlineStr"/>
       <c r="P247" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>441011</v>
+        <v>440759</v>
       </c>
       <c r="R247" t="n">
-        <v>6815357</v>
+        <v>6815171</v>
       </c>
       <c r="S247" t="n">
         <v>25</v>
@@ -27223,7 +27231,7 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>131197389</v>
+        <v>131197392</v>
       </c>
       <c r="B248" t="n">
         <v>57884</v>
@@ -27266,10 +27274,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>440759</v>
+        <v>440842</v>
       </c>
       <c r="R248" t="n">
-        <v>6815171</v>
+        <v>6815082</v>
       </c>
       <c r="S248" t="n">
         <v>25</v>
@@ -27308,7 +27316,7 @@
         <v>0</v>
       </c>
       <c r="AE248" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG248" t="b">
         <v>0</v>
@@ -27328,53 +27336,45 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>131197392</v>
+        <v>131197380</v>
       </c>
       <c r="B249" t="n">
-        <v>57884</v>
+        <v>91776</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
-      <c r="K249" t="inlineStr"/>
-      <c r="L249" t="inlineStr"/>
-      <c r="M249" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>440842</v>
+        <v>441011</v>
       </c>
       <c r="R249" t="n">
-        <v>6815082</v>
+        <v>6815357</v>
       </c>
       <c r="S249" t="n">
         <v>25</v>
@@ -27413,7 +27413,7 @@
         <v>0</v>
       </c>
       <c r="AE249" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG249" t="b">
         <v>0</v>
@@ -27735,7 +27735,7 @@
         <v>131197382</v>
       </c>
       <c r="B253" t="n">
-        <v>91810</v>
+        <v>91813</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -28981,10 +28981,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>131170634</v>
+        <v>131176226</v>
       </c>
       <c r="B265" t="n">
-        <v>57881</v>
+        <v>79245</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -28992,39 +28992,34 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
-      <c r="M265" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P265" t="inlineStr">
         <is>
           <t>Ytter-Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>441047</v>
+        <v>440926</v>
       </c>
       <c r="R265" t="n">
-        <v>6814660</v>
+        <v>6815004</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -29093,7 +29088,7 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>131176226</v>
+        <v>131175193</v>
       </c>
       <c r="B266" t="n">
         <v>79245</v>
@@ -29128,10 +29123,10 @@
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>440926</v>
+        <v>440948</v>
       </c>
       <c r="R266" t="n">
-        <v>6815004</v>
+        <v>6814948</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -29174,6 +29169,11 @@
       <c r="AB266" t="inlineStr">
         <is>
           <t>09:13</t>
+        </is>
+      </c>
+      <c r="AC266" t="inlineStr">
+        <is>
+          <t>1 bild gran</t>
         </is>
       </c>
       <c r="AD266" t="b">
@@ -29200,10 +29200,10 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>131175193</v>
+        <v>131176319</v>
       </c>
       <c r="B267" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -29211,34 +29211,39 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P267" t="inlineStr">
         <is>
           <t>Ytter-Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>440948</v>
+        <v>440860</v>
       </c>
       <c r="R267" t="n">
-        <v>6814948</v>
+        <v>6815093</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -29285,7 +29290,7 @@
       </c>
       <c r="AC267" t="inlineStr">
         <is>
-          <t>1 bild gran</t>
+          <t>2 bilder, gran 7 ring</t>
         </is>
       </c>
       <c r="AD267" t="b">
@@ -29312,7 +29317,7 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>131176319</v>
+        <v>131185758</v>
       </c>
       <c r="B268" t="n">
         <v>57884</v>
@@ -29348,14 +29353,14 @@
       </c>
       <c r="P268" t="inlineStr">
         <is>
-          <t>Ytter-Navardalen, Dlr</t>
+          <t>Navarnäsberget, Dlr</t>
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>440860</v>
+        <v>440698</v>
       </c>
       <c r="R268" t="n">
-        <v>6815093</v>
+        <v>6815085</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -29385,24 +29390,14 @@
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="Z268" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AA268" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="AB268" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AC268" t="inlineStr">
         <is>
-          <t>2 bilder, gran 7 ring</t>
+          <t>2 bild, gran</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -29429,10 +29424,10 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>131185758</v>
+        <v>131170634</v>
       </c>
       <c r="B269" t="n">
-        <v>57884</v>
+        <v>57881</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -29440,16 +29435,16 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -29465,14 +29460,14 @@
       </c>
       <c r="P269" t="inlineStr">
         <is>
-          <t>Navarnäsberget, Dlr</t>
+          <t>Ytter-Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>440698</v>
+        <v>441047</v>
       </c>
       <c r="R269" t="n">
-        <v>6815085</v>
+        <v>6814660</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -29502,14 +29497,19 @@
           <t>2026-02-16</t>
         </is>
       </c>
+      <c r="Z269" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AA269" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="AC269" t="inlineStr">
-        <is>
-          <t>2 bild, gran</t>
+      <c r="AB269" t="inlineStr">
+        <is>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -29929,10 +29929,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>131180289</v>
+        <v>131170517</v>
       </c>
       <c r="B274" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -29940,37 +29940,39 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
-      <c r="J274" t="inlineStr"/>
-      <c r="K274" t="inlineStr"/>
-      <c r="N274" t="inlineStr"/>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P274" t="inlineStr">
         <is>
-          <t>Navarnäsberget, Dlr</t>
+          <t>Ytter-Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>441013</v>
+        <v>441106</v>
       </c>
       <c r="R274" t="n">
-        <v>6815402</v>
+        <v>6814655</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -30017,7 +30019,7 @@
       </c>
       <c r="AC274" t="inlineStr">
         <is>
-          <t>1 bild, garn vid källa</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD274" t="b">
@@ -30026,7 +30028,6 @@
       <c r="AE274" t="b">
         <v>0</v>
       </c>
-      <c r="AF274" t="inlineStr"/>
       <c r="AG274" t="b">
         <v>0</v>
       </c>
@@ -30045,7 +30046,7 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>131187704</v>
+        <v>131180289</v>
       </c>
       <c r="B275" t="n">
         <v>79245</v>
@@ -30074,16 +30075,19 @@
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
+      <c r="J275" t="inlineStr"/>
+      <c r="K275" t="inlineStr"/>
+      <c r="N275" t="inlineStr"/>
       <c r="P275" t="inlineStr">
         <is>
           <t>Navarnäsberget, Dlr</t>
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>440434</v>
+        <v>441013</v>
       </c>
       <c r="R275" t="n">
-        <v>6815187</v>
+        <v>6815402</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -30113,17 +30117,33 @@
           <t>2026-02-16</t>
         </is>
       </c>
+      <c r="Z275" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AA275" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
+      <c r="AB275" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
+      <c r="AC275" t="inlineStr">
+        <is>
+          <t>1 bild, garn vid källa</t>
+        </is>
+      </c>
       <c r="AD275" t="b">
         <v>0</v>
       </c>
       <c r="AE275" t="b">
         <v>0</v>
       </c>
+      <c r="AF275" t="inlineStr"/>
       <c r="AG275" t="b">
         <v>0</v>
       </c>
@@ -30142,10 +30162,10 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>131170517</v>
+        <v>131187704</v>
       </c>
       <c r="B276" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -30153,39 +30173,34 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
-      <c r="M276" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P276" t="inlineStr">
         <is>
-          <t>Ytter-Navardalen, Dlr</t>
+          <t>Navarnäsberget, Dlr</t>
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>441106</v>
+        <v>440434</v>
       </c>
       <c r="R276" t="n">
-        <v>6814655</v>
+        <v>6815187</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -30215,24 +30230,9 @@
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="Z276" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AA276" t="inlineStr">
         <is>
           <t>2026-02-16</t>
-        </is>
-      </c>
-      <c r="AB276" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
-      <c r="AC276" t="inlineStr">
-        <is>
-          <t>1 bild</t>
         </is>
       </c>
       <c r="AD276" t="b">
@@ -31159,10 +31159,10 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>131177861</v>
+        <v>131178243</v>
       </c>
       <c r="B285" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -31170,34 +31170,39 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P285" t="inlineStr">
         <is>
           <t>Ytter-Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>440765</v>
+        <v>440782</v>
       </c>
       <c r="R285" t="n">
-        <v>6815236</v>
+        <v>6815262</v>
       </c>
       <c r="S285" t="n">
         <v>10</v>
@@ -31240,6 +31245,11 @@
       <c r="AB285" t="inlineStr">
         <is>
           <t>09:13</t>
+        </is>
+      </c>
+      <c r="AC285" t="inlineStr">
+        <is>
+          <t>2 bild på tall</t>
         </is>
       </c>
       <c r="AD285" t="b">
@@ -31266,10 +31276,10 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>131175229</v>
+        <v>131170627</v>
       </c>
       <c r="B286" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -31277,34 +31287,39 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I286" t="inlineStr"/>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P286" t="inlineStr">
         <is>
           <t>Ytter-Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>440944</v>
+        <v>441047</v>
       </c>
       <c r="R286" t="n">
-        <v>6814965</v>
+        <v>6814660</v>
       </c>
       <c r="S286" t="n">
         <v>10</v>
@@ -31373,10 +31388,10 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>131176451</v>
+        <v>131186199</v>
       </c>
       <c r="B287" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -31384,34 +31399,39 @@
         </is>
       </c>
       <c r="E287" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I287" t="inlineStr"/>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P287" t="inlineStr">
         <is>
-          <t>Ytter-Navardalen, Dlr</t>
+          <t>Navarnäsberget, Dlr</t>
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>440856</v>
+        <v>440702</v>
       </c>
       <c r="R287" t="n">
-        <v>6815124</v>
+        <v>6814996</v>
       </c>
       <c r="S287" t="n">
         <v>10</v>
@@ -31441,19 +31461,14 @@
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="Z287" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AA287" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="AB287" t="inlineStr">
-        <is>
-          <t>09:13</t>
+      <c r="AC287" t="inlineStr">
+        <is>
+          <t>1 bild, samma gran som spillkr</t>
         </is>
       </c>
       <c r="AD287" t="b">
@@ -31480,10 +31495,10 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>131185283</v>
+        <v>131177861</v>
       </c>
       <c r="B288" t="n">
-        <v>57881</v>
+        <v>79245</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -31491,39 +31506,34 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I288" t="inlineStr"/>
-      <c r="M288" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P288" t="inlineStr">
         <is>
-          <t>Navarnäsberget, Dlr</t>
+          <t>Ytter-Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>440715</v>
+        <v>440765</v>
       </c>
       <c r="R288" t="n">
-        <v>6815098</v>
+        <v>6815236</v>
       </c>
       <c r="S288" t="n">
         <v>10</v>
@@ -31553,9 +31563,19 @@
           <t>2026-02-16</t>
         </is>
       </c>
+      <c r="Z288" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AA288" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AB288" t="inlineStr">
+        <is>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD288" t="b">
@@ -31582,10 +31602,10 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>131178243</v>
+        <v>131175229</v>
       </c>
       <c r="B289" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -31593,39 +31613,34 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I289" t="inlineStr"/>
-      <c r="M289" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P289" t="inlineStr">
         <is>
           <t>Ytter-Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>440782</v>
+        <v>440944</v>
       </c>
       <c r="R289" t="n">
-        <v>6815262</v>
+        <v>6814965</v>
       </c>
       <c r="S289" t="n">
         <v>10</v>
@@ -31668,11 +31683,6 @@
       <c r="AB289" t="inlineStr">
         <is>
           <t>09:13</t>
-        </is>
-      </c>
-      <c r="AC289" t="inlineStr">
-        <is>
-          <t>2 bild på tall</t>
         </is>
       </c>
       <c r="AD289" t="b">
@@ -31699,10 +31709,10 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>131170627</v>
+        <v>131176451</v>
       </c>
       <c r="B290" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -31710,39 +31720,34 @@
         </is>
       </c>
       <c r="E290" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I290" t="inlineStr"/>
-      <c r="M290" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P290" t="inlineStr">
         <is>
           <t>Ytter-Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q290" t="n">
-        <v>441047</v>
+        <v>440856</v>
       </c>
       <c r="R290" t="n">
-        <v>6814660</v>
+        <v>6815124</v>
       </c>
       <c r="S290" t="n">
         <v>10</v>
@@ -31811,10 +31816,10 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>131186199</v>
+        <v>131185283</v>
       </c>
       <c r="B291" t="n">
-        <v>57884</v>
+        <v>57881</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -31822,16 +31827,16 @@
         </is>
       </c>
       <c r="E291" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -31842,7 +31847,7 @@
       <c r="I291" t="inlineStr"/>
       <c r="M291" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P291" t="inlineStr">
@@ -31851,10 +31856,10 @@
         </is>
       </c>
       <c r="Q291" t="n">
-        <v>440702</v>
+        <v>440715</v>
       </c>
       <c r="R291" t="n">
-        <v>6814996</v>
+        <v>6815098</v>
       </c>
       <c r="S291" t="n">
         <v>10</v>
@@ -31887,11 +31892,6 @@
       <c r="AA291" t="inlineStr">
         <is>
           <t>2026-02-16</t>
-        </is>
-      </c>
-      <c r="AC291" t="inlineStr">
-        <is>
-          <t>1 bild, samma gran som spillkr</t>
         </is>
       </c>
       <c r="AD291" t="b">
@@ -32229,10 +32229,10 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>131187947</v>
+        <v>131187700</v>
       </c>
       <c r="B295" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -32240,34 +32240,39 @@
         </is>
       </c>
       <c r="E295" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I295" t="inlineStr"/>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P295" t="inlineStr">
         <is>
           <t>Navarnäsberget, Dlr</t>
         </is>
       </c>
       <c r="Q295" t="n">
-        <v>440573</v>
+        <v>440434</v>
       </c>
       <c r="R295" t="n">
-        <v>6815085</v>
+        <v>6815187</v>
       </c>
       <c r="S295" t="n">
         <v>10</v>
@@ -32300,6 +32305,11 @@
       <c r="AA295" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AC295" t="inlineStr">
+        <is>
+          <t>2 bild band</t>
         </is>
       </c>
       <c r="AD295" t="b">
@@ -32326,7 +32336,7 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>131175447</v>
+        <v>131187947</v>
       </c>
       <c r="B296" t="n">
         <v>79245</v>
@@ -32357,14 +32367,14 @@
       <c r="I296" t="inlineStr"/>
       <c r="P296" t="inlineStr">
         <is>
-          <t>Ytter-Navardalen, Dlr</t>
+          <t>Navarnäsberget, Dlr</t>
         </is>
       </c>
       <c r="Q296" t="n">
-        <v>440933</v>
+        <v>440573</v>
       </c>
       <c r="R296" t="n">
-        <v>6814979</v>
+        <v>6815085</v>
       </c>
       <c r="S296" t="n">
         <v>10</v>
@@ -32394,19 +32404,9 @@
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="Z296" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AA296" t="inlineStr">
         <is>
           <t>2026-02-16</t>
-        </is>
-      </c>
-      <c r="AB296" t="inlineStr">
-        <is>
-          <t>09:13</t>
         </is>
       </c>
       <c r="AD296" t="b">
@@ -32433,10 +32433,10 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>131187700</v>
+        <v>131175447</v>
       </c>
       <c r="B297" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -32444,39 +32444,34 @@
         </is>
       </c>
       <c r="E297" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I297" t="inlineStr"/>
-      <c r="M297" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P297" t="inlineStr">
         <is>
-          <t>Navarnäsberget, Dlr</t>
+          <t>Ytter-Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q297" t="n">
-        <v>440434</v>
+        <v>440933</v>
       </c>
       <c r="R297" t="n">
-        <v>6815187</v>
+        <v>6814979</v>
       </c>
       <c r="S297" t="n">
         <v>10</v>
@@ -32506,14 +32501,19 @@
           <t>2026-02-16</t>
         </is>
       </c>
+      <c r="Z297" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AA297" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="AC297" t="inlineStr">
-        <is>
-          <t>2 bild band</t>
+      <c r="AB297" t="inlineStr">
+        <is>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD297" t="b">
@@ -33065,10 +33065,10 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>131186236</v>
+        <v>131176293</v>
       </c>
       <c r="B303" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -33076,39 +33076,34 @@
         </is>
       </c>
       <c r="E303" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I303" t="inlineStr"/>
-      <c r="M303" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P303" t="inlineStr">
         <is>
-          <t>Navarnäsberget, Dlr</t>
+          <t>Ytter-Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>440643</v>
+        <v>440860</v>
       </c>
       <c r="R303" t="n">
-        <v>6814928</v>
+        <v>6815093</v>
       </c>
       <c r="S303" t="n">
         <v>10</v>
@@ -33138,9 +33133,19 @@
           <t>2026-02-16</t>
         </is>
       </c>
+      <c r="Z303" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AA303" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AB303" t="inlineStr">
+        <is>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD303" t="b">
@@ -33167,7 +33172,7 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>131176405</v>
+        <v>131186236</v>
       </c>
       <c r="B304" t="n">
         <v>57884</v>
@@ -33198,19 +33203,19 @@
       <c r="I304" t="inlineStr"/>
       <c r="M304" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P304" t="inlineStr">
         <is>
-          <t>Ytter-Navardalen, Dlr</t>
+          <t>Navarnäsberget, Dlr</t>
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>440856</v>
+        <v>440643</v>
       </c>
       <c r="R304" t="n">
-        <v>6815124</v>
+        <v>6814928</v>
       </c>
       <c r="S304" t="n">
         <v>10</v>
@@ -33240,19 +33245,9 @@
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="Z304" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AA304" t="inlineStr">
         <is>
           <t>2026-02-16</t>
-        </is>
-      </c>
-      <c r="AB304" t="inlineStr">
-        <is>
-          <t>09:13</t>
         </is>
       </c>
       <c r="AD304" t="b">
@@ -33279,10 +33274,10 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>131176293</v>
+        <v>131176405</v>
       </c>
       <c r="B305" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -33290,34 +33285,39 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I305" t="inlineStr"/>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P305" t="inlineStr">
         <is>
           <t>Ytter-Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>440860</v>
+        <v>440856</v>
       </c>
       <c r="R305" t="n">
-        <v>6815093</v>
+        <v>6815124</v>
       </c>
       <c r="S305" t="n">
         <v>10</v>
@@ -33677,10 +33677,10 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>131186107</v>
+        <v>131176233</v>
       </c>
       <c r="B309" t="n">
-        <v>89195</v>
+        <v>79245</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -33688,34 +33688,34 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I309" t="inlineStr"/>
       <c r="P309" t="inlineStr">
         <is>
-          <t>Navarnäsberget, Dlr</t>
+          <t>Ytter-Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>440715</v>
+        <v>440893</v>
       </c>
       <c r="R309" t="n">
-        <v>6815098</v>
+        <v>6815041</v>
       </c>
       <c r="S309" t="n">
         <v>10</v>
@@ -33745,14 +33745,19 @@
           <t>2026-02-16</t>
         </is>
       </c>
+      <c r="Z309" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AA309" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="AC309" t="inlineStr">
-        <is>
-          <t>2 bild</t>
+      <c r="AB309" t="inlineStr">
+        <is>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD309" t="b">
@@ -33779,7 +33784,7 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>131176233</v>
+        <v>131189930</v>
       </c>
       <c r="B310" t="n">
         <v>79245</v>
@@ -33814,10 +33819,10 @@
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>440893</v>
+        <v>440855</v>
       </c>
       <c r="R310" t="n">
-        <v>6815041</v>
+        <v>6814679</v>
       </c>
       <c r="S310" t="n">
         <v>10</v>
@@ -33847,19 +33852,14 @@
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="Z310" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AA310" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="AB310" t="inlineStr">
-        <is>
-          <t>09:13</t>
+      <c r="AC310" t="inlineStr">
+        <is>
+          <t>Rikligt på tallstam</t>
         </is>
       </c>
       <c r="AD310" t="b">
@@ -33886,10 +33886,10 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>131189930</v>
+        <v>131186107</v>
       </c>
       <c r="B311" t="n">
-        <v>79245</v>
+        <v>89198</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -33897,34 +33897,34 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I311" t="inlineStr"/>
       <c r="P311" t="inlineStr">
         <is>
-          <t>Ytter-Navardalen, Dlr</t>
+          <t>Navarnäsberget, Dlr</t>
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>440855</v>
+        <v>440715</v>
       </c>
       <c r="R311" t="n">
-        <v>6814679</v>
+        <v>6815098</v>
       </c>
       <c r="S311" t="n">
         <v>10</v>
@@ -33961,7 +33961,7 @@
       </c>
       <c r="AC311" t="inlineStr">
         <is>
-          <t>Rikligt på tallstam</t>
+          <t>2 bild</t>
         </is>
       </c>
       <c r="AD311" t="b">

--- a/artfynd/A 5994-2026 artfynd.xlsx
+++ b/artfynd/A 5994-2026 artfynd.xlsx
@@ -8265,10 +8265,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131195671</v>
+        <v>131195848</v>
       </c>
       <c r="B72" t="n">
-        <v>79003</v>
+        <v>79246</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8276,21 +8276,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8300,10 +8300,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>440740</v>
+        <v>440440</v>
       </c>
       <c r="R72" t="n">
-        <v>6814579</v>
+        <v>6815092</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8335,7 +8335,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8345,7 +8345,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8372,10 +8372,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131195596</v>
+        <v>131195843</v>
       </c>
       <c r="B73" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8383,36 +8383,31 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>440681</v>
+        <v>440489</v>
       </c>
       <c r="R73" t="n">
         <v>6815022</v>
@@ -8447,7 +8442,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8457,12 +8452,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:44</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8489,10 +8479,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131195848</v>
+        <v>131195680</v>
       </c>
       <c r="B74" t="n">
-        <v>79246</v>
+        <v>91834</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8500,23 +8490,19 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -8524,10 +8510,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>440440</v>
+        <v>440829</v>
       </c>
       <c r="R74" t="n">
-        <v>6815092</v>
+        <v>6814569</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8559,7 +8545,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8569,7 +8555,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8596,7 +8582,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131195843</v>
+        <v>131195870</v>
       </c>
       <c r="B75" t="n">
         <v>79246</v>
@@ -8631,10 +8617,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>440489</v>
+        <v>440857</v>
       </c>
       <c r="R75" t="n">
-        <v>6815022</v>
+        <v>6814795</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8666,7 +8652,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8676,7 +8662,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8703,10 +8689,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131195680</v>
+        <v>131195755</v>
       </c>
       <c r="B76" t="n">
-        <v>91834</v>
+        <v>79246</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8714,19 +8700,23 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -8734,10 +8724,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>440829</v>
+        <v>441098</v>
       </c>
       <c r="R76" t="n">
-        <v>6814569</v>
+        <v>6814630</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8769,7 +8759,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8779,7 +8769,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8806,10 +8796,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131195870</v>
+        <v>131195678</v>
       </c>
       <c r="B77" t="n">
-        <v>79246</v>
+        <v>91834</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8817,23 +8807,19 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -8841,10 +8827,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>440857</v>
+        <v>440423</v>
       </c>
       <c r="R77" t="n">
-        <v>6814795</v>
+        <v>6815143</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8876,7 +8862,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8886,7 +8872,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8913,7 +8899,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131195755</v>
+        <v>131195830</v>
       </c>
       <c r="B78" t="n">
         <v>79246</v>
@@ -8948,10 +8934,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>441098</v>
+        <v>440672</v>
       </c>
       <c r="R78" t="n">
-        <v>6814630</v>
+        <v>6815003</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8983,7 +8969,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8993,7 +8979,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9020,10 +9006,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131195678</v>
+        <v>131195805</v>
       </c>
       <c r="B79" t="n">
-        <v>91834</v>
+        <v>79246</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9031,19 +9017,23 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -9051,10 +9041,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>440423</v>
+        <v>441170</v>
       </c>
       <c r="R79" t="n">
-        <v>6815143</v>
+        <v>6815286</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9086,7 +9076,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9096,7 +9086,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9123,7 +9113,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131195830</v>
+        <v>131195757</v>
       </c>
       <c r="B80" t="n">
         <v>79246</v>
@@ -9158,10 +9148,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>440672</v>
+        <v>441069</v>
       </c>
       <c r="R80" t="n">
-        <v>6815003</v>
+        <v>6814629</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9193,7 +9183,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9203,7 +9193,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9230,10 +9220,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131195805</v>
+        <v>131195671</v>
       </c>
       <c r="B81" t="n">
-        <v>79246</v>
+        <v>79003</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9241,21 +9231,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9265,10 +9255,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>441170</v>
+        <v>440740</v>
       </c>
       <c r="R81" t="n">
-        <v>6815286</v>
+        <v>6814579</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9300,7 +9290,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9310,7 +9300,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9337,10 +9327,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131195757</v>
+        <v>131195596</v>
       </c>
       <c r="B82" t="n">
-        <v>79246</v>
+        <v>57884</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9348,34 +9338,39 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>441069</v>
+        <v>440681</v>
       </c>
       <c r="R82" t="n">
-        <v>6814629</v>
+        <v>6815022</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9407,7 +9402,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9417,7 +9412,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10641,10 +10641,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131195585</v>
+        <v>131195759</v>
       </c>
       <c r="B94" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10652,39 +10652,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>440954</v>
+        <v>440974</v>
       </c>
       <c r="R94" t="n">
-        <v>6814835</v>
+        <v>6814684</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10716,7 +10711,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10726,12 +10721,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>09:47</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10758,10 +10748,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131195617</v>
+        <v>131195699</v>
       </c>
       <c r="B95" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10769,27 +10759,27 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -10798,10 +10788,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>440769</v>
+        <v>441115</v>
       </c>
       <c r="R95" t="n">
-        <v>6815128</v>
+        <v>6815286</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10833,7 +10823,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10843,7 +10833,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10870,7 +10860,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131195763</v>
+        <v>131195701</v>
       </c>
       <c r="B96" t="n">
         <v>79246</v>
@@ -10899,16 +10889,21 @@
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>440983</v>
+        <v>440529</v>
       </c>
       <c r="R96" t="n">
-        <v>6814769</v>
+        <v>6814939</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10940,7 +10935,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10950,7 +10945,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10977,7 +10972,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131195789</v>
+        <v>131195763</v>
       </c>
       <c r="B97" t="n">
         <v>79246</v>
@@ -11012,10 +11007,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>440756</v>
+        <v>440983</v>
       </c>
       <c r="R97" t="n">
-        <v>6815138</v>
+        <v>6814769</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11047,7 +11042,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11057,7 +11052,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11084,10 +11079,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131195556</v>
+        <v>131195789</v>
       </c>
       <c r="B98" t="n">
-        <v>83226</v>
+        <v>79246</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11095,21 +11090,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11119,10 +11114,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>440904</v>
+        <v>440756</v>
       </c>
       <c r="R98" t="n">
-        <v>6814873</v>
+        <v>6815138</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11154,7 +11149,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11164,7 +11159,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11191,10 +11186,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131195759</v>
+        <v>131195556</v>
       </c>
       <c r="B99" t="n">
-        <v>79246</v>
+        <v>83226</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11202,21 +11197,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11226,10 +11221,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>440974</v>
+        <v>440904</v>
       </c>
       <c r="R99" t="n">
-        <v>6814684</v>
+        <v>6814873</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11261,7 +11256,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11271,7 +11266,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11298,10 +11293,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131195699</v>
+        <v>131195585</v>
       </c>
       <c r="B100" t="n">
-        <v>79246</v>
+        <v>57884</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11309,27 +11304,27 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -11338,10 +11333,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>441115</v>
+        <v>440954</v>
       </c>
       <c r="R100" t="n">
-        <v>6815286</v>
+        <v>6814835</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11373,7 +11368,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11383,7 +11378,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11410,10 +11410,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131195701</v>
+        <v>131195617</v>
       </c>
       <c r="B101" t="n">
-        <v>79246</v>
+        <v>57884</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11421,27 +11421,27 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -11450,10 +11450,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>440529</v>
+        <v>440769</v>
       </c>
       <c r="R101" t="n">
-        <v>6814939</v>
+        <v>6815128</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11485,7 +11485,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11495,7 +11495,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11522,10 +11522,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131195872</v>
+        <v>131195603</v>
       </c>
       <c r="B102" t="n">
-        <v>79246</v>
+        <v>57884</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11533,34 +11533,39 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>440835</v>
+        <v>440799</v>
       </c>
       <c r="R102" t="n">
-        <v>6814722</v>
+        <v>6814924</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11592,7 +11597,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11602,7 +11607,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11629,7 +11634,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131195738</v>
+        <v>131195872</v>
       </c>
       <c r="B103" t="n">
         <v>79246</v>
@@ -11664,10 +11669,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>441201</v>
+        <v>440835</v>
       </c>
       <c r="R103" t="n">
-        <v>6814618</v>
+        <v>6814722</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11699,7 +11704,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11709,7 +11714,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11736,7 +11741,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131195828</v>
+        <v>131195738</v>
       </c>
       <c r="B104" t="n">
         <v>79246</v>
@@ -11771,10 +11776,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>440682</v>
+        <v>441201</v>
       </c>
       <c r="R104" t="n">
-        <v>6815041</v>
+        <v>6814618</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11806,7 +11811,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11816,7 +11821,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11843,7 +11848,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131195777</v>
+        <v>131195828</v>
       </c>
       <c r="B105" t="n">
         <v>79246</v>
@@ -11878,10 +11883,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>440923</v>
+        <v>440682</v>
       </c>
       <c r="R105" t="n">
-        <v>6814920</v>
+        <v>6815041</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11913,7 +11918,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11923,7 +11928,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11950,10 +11955,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131195561</v>
+        <v>131195777</v>
       </c>
       <c r="B106" t="n">
-        <v>83226</v>
+        <v>79246</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11961,21 +11966,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11985,10 +11990,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>441034</v>
+        <v>440923</v>
       </c>
       <c r="R106" t="n">
-        <v>6815350</v>
+        <v>6814920</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12020,7 +12025,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12030,7 +12035,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12057,10 +12062,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131195603</v>
+        <v>131195561</v>
       </c>
       <c r="B107" t="n">
-        <v>57884</v>
+        <v>83226</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12068,39 +12073,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>440799</v>
+        <v>441034</v>
       </c>
       <c r="R107" t="n">
-        <v>6814924</v>
+        <v>6815350</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12132,7 +12132,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12142,7 +12142,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12383,32 +12383,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>131195637</v>
+        <v>131195567</v>
       </c>
       <c r="B110" t="n">
-        <v>58043</v>
+        <v>91777</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12418,10 +12418,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>441072</v>
+        <v>440907</v>
       </c>
       <c r="R110" t="n">
-        <v>6814663</v>
+        <v>6814875</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12453,7 +12453,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12463,7 +12463,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12490,32 +12490,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>131195567</v>
+        <v>131195776</v>
       </c>
       <c r="B111" t="n">
-        <v>91777</v>
+        <v>79246</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12525,10 +12525,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>440907</v>
+        <v>440926</v>
       </c>
       <c r="R111" t="n">
-        <v>6814875</v>
+        <v>6814927</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12570,7 +12570,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12597,7 +12597,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>131195776</v>
+        <v>131195884</v>
       </c>
       <c r="B112" t="n">
         <v>79246</v>
@@ -12632,10 +12632,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>440926</v>
+        <v>440736</v>
       </c>
       <c r="R112" t="n">
-        <v>6814927</v>
+        <v>6814569</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12667,7 +12667,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12677,7 +12677,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12704,7 +12704,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131195884</v>
+        <v>131195739</v>
       </c>
       <c r="B113" t="n">
         <v>79246</v>
@@ -12739,10 +12739,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>440736</v>
+        <v>441199</v>
       </c>
       <c r="R113" t="n">
-        <v>6814569</v>
+        <v>6814633</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12784,7 +12784,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12811,7 +12811,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131195739</v>
+        <v>131195871</v>
       </c>
       <c r="B114" t="n">
         <v>79246</v>
@@ -12846,10 +12846,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>441199</v>
+        <v>440853</v>
       </c>
       <c r="R114" t="n">
-        <v>6814633</v>
+        <v>6814767</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12881,7 +12881,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12891,7 +12891,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12918,7 +12918,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131195871</v>
+        <v>131195844</v>
       </c>
       <c r="B115" t="n">
         <v>79246</v>
@@ -12953,10 +12953,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>440853</v>
+        <v>440488</v>
       </c>
       <c r="R115" t="n">
-        <v>6814767</v>
+        <v>6815047</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12988,7 +12988,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12998,7 +12998,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13025,32 +13025,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131195844</v>
+        <v>131195573</v>
       </c>
       <c r="B116" t="n">
-        <v>79246</v>
+        <v>91777</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13060,10 +13060,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>440488</v>
+        <v>440508</v>
       </c>
       <c r="R116" t="n">
-        <v>6815047</v>
+        <v>6815137</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13095,7 +13095,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13105,7 +13105,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13132,45 +13132,50 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131195573</v>
+        <v>131195600</v>
       </c>
       <c r="B117" t="n">
-        <v>91777</v>
+        <v>57884</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>440508</v>
+        <v>440842</v>
       </c>
       <c r="R117" t="n">
-        <v>6815137</v>
+        <v>6815077</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13202,7 +13207,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13212,14 +13217,14 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
       <c r="AE117" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG117" t="b">
         <v>0</v>
@@ -13239,45 +13244,50 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131195558</v>
+        <v>131195917</v>
       </c>
       <c r="B118" t="n">
-        <v>83226</v>
+        <v>5177</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6440</v>
+        <v>100526</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>440881</v>
+        <v>440934</v>
       </c>
       <c r="R118" t="n">
-        <v>6815052</v>
+        <v>6814927</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13309,7 +13319,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13319,7 +13329,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13346,10 +13356,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131195798</v>
+        <v>131195637</v>
       </c>
       <c r="B119" t="n">
-        <v>79246</v>
+        <v>58043</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13357,21 +13367,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13381,10 +13391,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>440943</v>
+        <v>441072</v>
       </c>
       <c r="R119" t="n">
-        <v>6815341</v>
+        <v>6814663</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13416,7 +13426,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13426,7 +13436,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13453,10 +13463,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131195842</v>
+        <v>131195558</v>
       </c>
       <c r="B120" t="n">
-        <v>79246</v>
+        <v>83226</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13464,21 +13474,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13488,10 +13498,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>440509</v>
+        <v>440881</v>
       </c>
       <c r="R120" t="n">
-        <v>6815018</v>
+        <v>6815052</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13523,7 +13533,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13533,7 +13543,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13560,7 +13570,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>131195839</v>
+        <v>131195798</v>
       </c>
       <c r="B121" t="n">
         <v>79246</v>
@@ -13595,10 +13605,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>440519</v>
+        <v>440943</v>
       </c>
       <c r="R121" t="n">
-        <v>6814964</v>
+        <v>6815341</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13630,7 +13640,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13640,7 +13650,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13667,7 +13677,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>131195840</v>
+        <v>131195842</v>
       </c>
       <c r="B122" t="n">
         <v>79246</v>
@@ -13702,10 +13712,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>440518</v>
+        <v>440509</v>
       </c>
       <c r="R122" t="n">
-        <v>6814966</v>
+        <v>6815018</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13737,7 +13747,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13747,7 +13757,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13774,10 +13784,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>131195600</v>
+        <v>131195839</v>
       </c>
       <c r="B123" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13785,39 +13795,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>440842</v>
+        <v>440519</v>
       </c>
       <c r="R123" t="n">
-        <v>6815077</v>
+        <v>6814964</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13849,7 +13854,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13859,14 +13864,14 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
       <c r="AE123" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG123" t="b">
         <v>0</v>
@@ -13886,50 +13891,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>131195917</v>
+        <v>131195840</v>
       </c>
       <c r="B124" t="n">
-        <v>5177</v>
+        <v>79246</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>440934</v>
+        <v>440518</v>
       </c>
       <c r="R124" t="n">
-        <v>6814927</v>
+        <v>6814966</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13961,7 +13961,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13971,7 +13971,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -25708,10 +25708,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>131197394</v>
+        <v>131197406</v>
       </c>
       <c r="B233" t="n">
-        <v>57881</v>
+        <v>79246</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -25719,42 +25719,34 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
-      <c r="K233" t="inlineStr"/>
-      <c r="L233" t="inlineStr"/>
-      <c r="M233" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>440950</v>
+        <v>441114</v>
       </c>
       <c r="R233" t="n">
-        <v>6815375</v>
+        <v>6814652</v>
       </c>
       <c r="S233" t="n">
         <v>25</v>
@@ -25787,11 +25779,6 @@
       <c r="AA233" t="inlineStr">
         <is>
           <t>2026-02-16</t>
-        </is>
-      </c>
-      <c r="AC233" t="inlineStr">
-        <is>
-          <t>Födosök</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -25818,10 +25805,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>131197406</v>
+        <v>131197390</v>
       </c>
       <c r="B234" t="n">
-        <v>79246</v>
+        <v>57884</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -25829,34 +25816,42 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
+      <c r="K234" t="inlineStr"/>
+      <c r="L234" t="inlineStr"/>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>441114</v>
+        <v>440857</v>
       </c>
       <c r="R234" t="n">
-        <v>6814652</v>
+        <v>6815078</v>
       </c>
       <c r="S234" t="n">
         <v>25</v>
@@ -25915,10 +25910,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>131197390</v>
+        <v>131197394</v>
       </c>
       <c r="B235" t="n">
-        <v>57884</v>
+        <v>57881</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -25926,16 +25921,16 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -25948,7 +25943,7 @@
       <c r="L235" t="inlineStr"/>
       <c r="M235" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N235" t="inlineStr"/>
@@ -25958,10 +25953,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>440857</v>
+        <v>440950</v>
       </c>
       <c r="R235" t="n">
-        <v>6815078</v>
+        <v>6815375</v>
       </c>
       <c r="S235" t="n">
         <v>25</v>
@@ -25994,6 +25989,11 @@
       <c r="AA235" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AC235" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -26423,10 +26423,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>131197376</v>
+        <v>131197384</v>
       </c>
       <c r="B240" t="n">
-        <v>83226</v>
+        <v>57884</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -26434,34 +26434,42 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
+      <c r="K240" t="inlineStr"/>
+      <c r="L240" t="inlineStr"/>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>440433</v>
+        <v>440757</v>
       </c>
       <c r="R240" t="n">
-        <v>6815150</v>
+        <v>6815220</v>
       </c>
       <c r="S240" t="n">
         <v>25</v>
@@ -26500,7 +26508,7 @@
         <v>0</v>
       </c>
       <c r="AE240" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG240" t="b">
         <v>0</v>
@@ -26520,10 +26528,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>131197384</v>
+        <v>131197376</v>
       </c>
       <c r="B241" t="n">
-        <v>57884</v>
+        <v>83226</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -26531,42 +26539,34 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
-      <c r="K241" t="inlineStr"/>
-      <c r="L241" t="inlineStr"/>
-      <c r="M241" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N241" t="inlineStr"/>
       <c r="P241" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>440757</v>
+        <v>440433</v>
       </c>
       <c r="R241" t="n">
-        <v>6815220</v>
+        <v>6815150</v>
       </c>
       <c r="S241" t="n">
         <v>25</v>
@@ -26605,7 +26605,7 @@
         <v>0</v>
       </c>
       <c r="AE241" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG241" t="b">
         <v>0</v>
@@ -28359,10 +28359,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>131178705</v>
+        <v>131186232</v>
       </c>
       <c r="B259" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -28370,39 +28370,34 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
-      <c r="M259" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P259" t="inlineStr">
         <is>
-          <t>Ytter-Navardalen, Dlr</t>
+          <t>Navarnäsberget, Dlr</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>440802</v>
+        <v>440664</v>
       </c>
       <c r="R259" t="n">
-        <v>6815254</v>
+        <v>6814943</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -28432,24 +28427,9 @@
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="Z259" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AA259" t="inlineStr">
         <is>
           <t>2026-02-16</t>
-        </is>
-      </c>
-      <c r="AB259" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
-      <c r="AC259" t="inlineStr">
-        <is>
-          <t>2 bild gran, ringhack garn</t>
         </is>
       </c>
       <c r="AD259" t="b">
@@ -28583,10 +28563,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>131186232</v>
+        <v>131178705</v>
       </c>
       <c r="B261" t="n">
-        <v>79246</v>
+        <v>57884</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -28594,34 +28574,39 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P261" t="inlineStr">
         <is>
-          <t>Navarnäsberget, Dlr</t>
+          <t>Ytter-Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>440664</v>
+        <v>440802</v>
       </c>
       <c r="R261" t="n">
-        <v>6814943</v>
+        <v>6815254</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -28651,9 +28636,24 @@
           <t>2026-02-16</t>
         </is>
       </c>
+      <c r="Z261" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AA261" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AB261" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
+      <c r="AC261" t="inlineStr">
+        <is>
+          <t>2 bild gran, ringhack garn</t>
         </is>
       </c>
       <c r="AD261" t="b">
@@ -28787,7 +28787,7 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>131192250</v>
+        <v>131191942</v>
       </c>
       <c r="B263" t="n">
         <v>79246</v>
@@ -28822,10 +28822,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>440909</v>
+        <v>440731</v>
       </c>
       <c r="R263" t="n">
-        <v>6814338</v>
+        <v>6814532</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -28884,7 +28884,7 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>131191942</v>
+        <v>131192250</v>
       </c>
       <c r="B264" t="n">
         <v>79246</v>
@@ -28919,10 +28919,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>440731</v>
+        <v>440909</v>
       </c>
       <c r="R264" t="n">
-        <v>6814532</v>
+        <v>6814338</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -29536,10 +29536,10 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>131186470</v>
+        <v>131186418</v>
       </c>
       <c r="B270" t="n">
-        <v>79246</v>
+        <v>57884</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -29547,24 +29547,29 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P270" t="inlineStr">
         <is>
           <t>Navarnäsberget, Dlr</t>
@@ -29633,7 +29638,7 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>131185798</v>
+        <v>131186470</v>
       </c>
       <c r="B271" t="n">
         <v>79246</v>
@@ -29668,10 +29673,10 @@
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>440698</v>
+        <v>440503</v>
       </c>
       <c r="R271" t="n">
-        <v>6815085</v>
+        <v>6815000</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -29730,10 +29735,10 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>131186418</v>
+        <v>131185798</v>
       </c>
       <c r="B272" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -29741,39 +29746,34 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
-      <c r="M272" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P272" t="inlineStr">
         <is>
           <t>Navarnäsberget, Dlr</t>
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>440503</v>
+        <v>440698</v>
       </c>
       <c r="R272" t="n">
-        <v>6815000</v>
+        <v>6815085</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -29929,10 +29929,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>131170517</v>
+        <v>131180289</v>
       </c>
       <c r="B274" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -29940,39 +29940,37 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
-      <c r="M274" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J274" t="inlineStr"/>
+      <c r="K274" t="inlineStr"/>
+      <c r="N274" t="inlineStr"/>
       <c r="P274" t="inlineStr">
         <is>
-          <t>Ytter-Navardalen, Dlr</t>
+          <t>Navarnäsberget, Dlr</t>
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>441106</v>
+        <v>441013</v>
       </c>
       <c r="R274" t="n">
-        <v>6814655</v>
+        <v>6815402</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -30019,7 +30017,7 @@
       </c>
       <c r="AC274" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>1 bild, garn vid källa</t>
         </is>
       </c>
       <c r="AD274" t="b">
@@ -30028,6 +30026,7 @@
       <c r="AE274" t="b">
         <v>0</v>
       </c>
+      <c r="AF274" t="inlineStr"/>
       <c r="AG274" t="b">
         <v>0</v>
       </c>
@@ -30046,7 +30045,7 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>131180289</v>
+        <v>131187704</v>
       </c>
       <c r="B275" t="n">
         <v>79246</v>
@@ -30075,19 +30074,16 @@
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
-      <c r="J275" t="inlineStr"/>
-      <c r="K275" t="inlineStr"/>
-      <c r="N275" t="inlineStr"/>
       <c r="P275" t="inlineStr">
         <is>
           <t>Navarnäsberget, Dlr</t>
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>441013</v>
+        <v>440434</v>
       </c>
       <c r="R275" t="n">
-        <v>6815402</v>
+        <v>6815187</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -30117,33 +30113,17 @@
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="Z275" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AA275" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="AB275" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
-      <c r="AC275" t="inlineStr">
-        <is>
-          <t>1 bild, garn vid källa</t>
-        </is>
-      </c>
       <c r="AD275" t="b">
         <v>0</v>
       </c>
       <c r="AE275" t="b">
         <v>0</v>
       </c>
-      <c r="AF275" t="inlineStr"/>
       <c r="AG275" t="b">
         <v>0</v>
       </c>
@@ -30162,10 +30142,10 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>131187704</v>
+        <v>131170517</v>
       </c>
       <c r="B276" t="n">
-        <v>79246</v>
+        <v>57884</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -30173,34 +30153,39 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P276" t="inlineStr">
         <is>
-          <t>Navarnäsberget, Dlr</t>
+          <t>Ytter-Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>440434</v>
+        <v>441106</v>
       </c>
       <c r="R276" t="n">
-        <v>6815187</v>
+        <v>6814655</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -30230,9 +30215,24 @@
           <t>2026-02-16</t>
         </is>
       </c>
+      <c r="Z276" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AA276" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AB276" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
+      <c r="AC276" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD276" t="b">
@@ -31266,10 +31266,10 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>131185283</v>
+        <v>131178243</v>
       </c>
       <c r="B286" t="n">
-        <v>57881</v>
+        <v>57884</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -31277,16 +31277,16 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -31297,19 +31297,19 @@
       <c r="I286" t="inlineStr"/>
       <c r="M286" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P286" t="inlineStr">
         <is>
-          <t>Navarnäsberget, Dlr</t>
+          <t>Ytter-Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>440715</v>
+        <v>440782</v>
       </c>
       <c r="R286" t="n">
-        <v>6815098</v>
+        <v>6815262</v>
       </c>
       <c r="S286" t="n">
         <v>10</v>
@@ -31339,9 +31339,24 @@
           <t>2026-02-16</t>
         </is>
       </c>
+      <c r="Z286" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AA286" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AB286" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
+      <c r="AC286" t="inlineStr">
+        <is>
+          <t>2 bild på tall</t>
         </is>
       </c>
       <c r="AD286" t="b">
@@ -31368,10 +31383,10 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>131177861</v>
+        <v>131170627</v>
       </c>
       <c r="B287" t="n">
-        <v>79246</v>
+        <v>57884</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -31379,34 +31394,39 @@
         </is>
       </c>
       <c r="E287" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I287" t="inlineStr"/>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P287" t="inlineStr">
         <is>
           <t>Ytter-Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>440765</v>
+        <v>441047</v>
       </c>
       <c r="R287" t="n">
-        <v>6815236</v>
+        <v>6814660</v>
       </c>
       <c r="S287" t="n">
         <v>10</v>
@@ -31475,10 +31495,10 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>131176451</v>
+        <v>131186199</v>
       </c>
       <c r="B288" t="n">
-        <v>79246</v>
+        <v>57884</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -31486,34 +31506,39 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I288" t="inlineStr"/>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P288" t="inlineStr">
         <is>
-          <t>Ytter-Navardalen, Dlr</t>
+          <t>Navarnäsberget, Dlr</t>
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>440856</v>
+        <v>440702</v>
       </c>
       <c r="R288" t="n">
-        <v>6815124</v>
+        <v>6814996</v>
       </c>
       <c r="S288" t="n">
         <v>10</v>
@@ -31543,19 +31568,14 @@
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="Z288" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AA288" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="AB288" t="inlineStr">
-        <is>
-          <t>09:13</t>
+      <c r="AC288" t="inlineStr">
+        <is>
+          <t>1 bild, samma gran som spillkr</t>
         </is>
       </c>
       <c r="AD288" t="b">
@@ -31582,10 +31602,10 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>131178243</v>
+        <v>131177861</v>
       </c>
       <c r="B289" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -31593,39 +31613,34 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I289" t="inlineStr"/>
-      <c r="M289" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P289" t="inlineStr">
         <is>
           <t>Ytter-Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>440782</v>
+        <v>440765</v>
       </c>
       <c r="R289" t="n">
-        <v>6815262</v>
+        <v>6815236</v>
       </c>
       <c r="S289" t="n">
         <v>10</v>
@@ -31668,11 +31683,6 @@
       <c r="AB289" t="inlineStr">
         <is>
           <t>09:13</t>
-        </is>
-      </c>
-      <c r="AC289" t="inlineStr">
-        <is>
-          <t>2 bild på tall</t>
         </is>
       </c>
       <c r="AD289" t="b">
@@ -31699,10 +31709,10 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>131170627</v>
+        <v>131176451</v>
       </c>
       <c r="B290" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -31710,39 +31720,34 @@
         </is>
       </c>
       <c r="E290" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I290" t="inlineStr"/>
-      <c r="M290" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P290" t="inlineStr">
         <is>
           <t>Ytter-Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q290" t="n">
-        <v>441047</v>
+        <v>440856</v>
       </c>
       <c r="R290" t="n">
-        <v>6814660</v>
+        <v>6815124</v>
       </c>
       <c r="S290" t="n">
         <v>10</v>
@@ -31811,10 +31816,10 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>131186199</v>
+        <v>131185283</v>
       </c>
       <c r="B291" t="n">
-        <v>57884</v>
+        <v>57881</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -31822,16 +31827,16 @@
         </is>
       </c>
       <c r="E291" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -31842,7 +31847,7 @@
       <c r="I291" t="inlineStr"/>
       <c r="M291" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P291" t="inlineStr">
@@ -31851,10 +31856,10 @@
         </is>
       </c>
       <c r="Q291" t="n">
-        <v>440702</v>
+        <v>440715</v>
       </c>
       <c r="R291" t="n">
-        <v>6814996</v>
+        <v>6815098</v>
       </c>
       <c r="S291" t="n">
         <v>10</v>
@@ -31887,11 +31892,6 @@
       <c r="AA291" t="inlineStr">
         <is>
           <t>2026-02-16</t>
-        </is>
-      </c>
-      <c r="AC291" t="inlineStr">
-        <is>
-          <t>1 bild, samma gran som spillkr</t>
         </is>
       </c>
       <c r="AD291" t="b">
@@ -32637,10 +32637,10 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>131192073</v>
+        <v>131180739</v>
       </c>
       <c r="B299" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -32648,39 +32648,34 @@
         </is>
       </c>
       <c r="E299" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I299" t="inlineStr"/>
-      <c r="M299" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P299" t="inlineStr">
         <is>
-          <t>Ytter-Navardalen, Dlr</t>
+          <t>Navarnäsberget, Dlr</t>
         </is>
       </c>
       <c r="Q299" t="n">
-        <v>440917</v>
+        <v>441163</v>
       </c>
       <c r="R299" t="n">
-        <v>6814603</v>
+        <v>6815248</v>
       </c>
       <c r="S299" t="n">
         <v>10</v>
@@ -32710,14 +32705,19 @@
           <t>2026-02-16</t>
         </is>
       </c>
+      <c r="Z299" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AA299" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="AC299" t="inlineStr">
-        <is>
-          <t>3 bilder med person</t>
+      <c r="AB299" t="inlineStr">
+        <is>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD299" t="b">
@@ -32744,10 +32744,10 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>131180074</v>
+        <v>131192073</v>
       </c>
       <c r="B300" t="n">
-        <v>79246</v>
+        <v>57884</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -32755,34 +32755,39 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I300" t="inlineStr"/>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P300" t="inlineStr">
         <is>
-          <t>Navarnäsberget, Dlr</t>
+          <t>Ytter-Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q300" t="n">
-        <v>440948</v>
+        <v>440917</v>
       </c>
       <c r="R300" t="n">
-        <v>6815355</v>
+        <v>6814603</v>
       </c>
       <c r="S300" t="n">
         <v>10</v>
@@ -32812,19 +32817,14 @@
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="Z300" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AA300" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="AB300" t="inlineStr">
-        <is>
-          <t>09:13</t>
+      <c r="AC300" t="inlineStr">
+        <is>
+          <t>3 bilder med person</t>
         </is>
       </c>
       <c r="AD300" t="b">
@@ -32851,7 +32851,7 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>131180739</v>
+        <v>131180074</v>
       </c>
       <c r="B301" t="n">
         <v>79246</v>
@@ -32886,10 +32886,10 @@
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>441163</v>
+        <v>440948</v>
       </c>
       <c r="R301" t="n">
-        <v>6815248</v>
+        <v>6815355</v>
       </c>
       <c r="S301" t="n">
         <v>10</v>
@@ -33483,7 +33483,7 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>131185285</v>
+        <v>131192080</v>
       </c>
       <c r="B307" t="n">
         <v>79246</v>
@@ -33514,14 +33514,14 @@
       <c r="I307" t="inlineStr"/>
       <c r="P307" t="inlineStr">
         <is>
-          <t>Navarnäsberget, Dlr</t>
+          <t>Ytter-Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>440715</v>
+        <v>440917</v>
       </c>
       <c r="R307" t="n">
-        <v>6815098</v>
+        <v>6814603</v>
       </c>
       <c r="S307" t="n">
         <v>10</v>
@@ -33580,7 +33580,7 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>131192080</v>
+        <v>131185285</v>
       </c>
       <c r="B308" t="n">
         <v>79246</v>
@@ -33611,14 +33611,14 @@
       <c r="I308" t="inlineStr"/>
       <c r="P308" t="inlineStr">
         <is>
-          <t>Ytter-Navardalen, Dlr</t>
+          <t>Navarnäsberget, Dlr</t>
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>440917</v>
+        <v>440715</v>
       </c>
       <c r="R308" t="n">
-        <v>6814603</v>
+        <v>6815098</v>
       </c>
       <c r="S308" t="n">
         <v>10</v>

--- a/artfynd/A 5994-2026 artfynd.xlsx
+++ b/artfynd/A 5994-2026 artfynd.xlsx
@@ -4791,10 +4791,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131195818</v>
+        <v>131195579</v>
       </c>
       <c r="B40" t="n">
-        <v>79250</v>
+        <v>91818</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4802,21 +4802,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4826,10 +4826,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440728</v>
+        <v>440686</v>
       </c>
       <c r="R40" t="n">
-        <v>6815184</v>
+        <v>6815080</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4861,7 +4861,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4898,7 +4898,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131195832</v>
+        <v>131195818</v>
       </c>
       <c r="B41" t="n">
         <v>79250</v>
@@ -4933,10 +4933,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440618</v>
+        <v>440728</v>
       </c>
       <c r="R41" t="n">
-        <v>6814951</v>
+        <v>6815184</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4968,7 +4968,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5005,7 +5005,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131195890</v>
+        <v>131195832</v>
       </c>
       <c r="B42" t="n">
         <v>79250</v>
@@ -5040,10 +5040,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440863</v>
+        <v>440618</v>
       </c>
       <c r="R42" t="n">
-        <v>6814594</v>
+        <v>6814951</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5075,7 +5075,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5085,7 +5085,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5112,7 +5112,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131195845</v>
+        <v>131195890</v>
       </c>
       <c r="B43" t="n">
         <v>79250</v>
@@ -5147,10 +5147,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440470</v>
+        <v>440863</v>
       </c>
       <c r="R43" t="n">
-        <v>6815085</v>
+        <v>6814594</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5182,7 +5182,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5219,32 +5219,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131195570</v>
+        <v>131195845</v>
       </c>
       <c r="B44" t="n">
-        <v>91781</v>
+        <v>79250</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5254,10 +5254,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>441037</v>
+        <v>440470</v>
       </c>
       <c r="R44" t="n">
-        <v>6815351</v>
+        <v>6815085</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5289,7 +5289,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5326,32 +5326,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131195893</v>
+        <v>131195570</v>
       </c>
       <c r="B45" t="n">
-        <v>79250</v>
+        <v>91781</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5361,10 +5361,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440928</v>
+        <v>441037</v>
       </c>
       <c r="R45" t="n">
-        <v>6814610</v>
+        <v>6815351</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5433,7 +5433,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131195696</v>
+        <v>131195893</v>
       </c>
       <c r="B46" t="n">
         <v>79250</v>
@@ -5462,21 +5462,16 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440740</v>
+        <v>440928</v>
       </c>
       <c r="R46" t="n">
-        <v>6815216</v>
+        <v>6814610</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5508,7 +5503,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5518,7 +5513,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5545,10 +5540,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131195579</v>
+        <v>131195696</v>
       </c>
       <c r="B47" t="n">
-        <v>91818</v>
+        <v>79250</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5556,34 +5551,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>440686</v>
+        <v>440740</v>
       </c>
       <c r="R47" t="n">
-        <v>6815080</v>
+        <v>6815216</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5652,10 +5652,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131195608</v>
+        <v>131195648</v>
       </c>
       <c r="B48" t="n">
-        <v>57888</v>
+        <v>57885</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5663,16 +5663,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5692,10 +5692,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>441099</v>
+        <v>440835</v>
       </c>
       <c r="R48" t="n">
-        <v>6814647</v>
+        <v>6815088</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5727,7 +5727,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5764,10 +5764,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131195620</v>
+        <v>131195646</v>
       </c>
       <c r="B49" t="n">
-        <v>57888</v>
+        <v>57885</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5775,16 +5775,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5795,7 +5795,7 @@
       <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5804,10 +5804,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440802</v>
+        <v>440867</v>
       </c>
       <c r="R49" t="n">
-        <v>6815292</v>
+        <v>6814841</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5876,10 +5876,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131195792</v>
+        <v>131195608</v>
       </c>
       <c r="B50" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5887,34 +5887,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>440746</v>
+        <v>441099</v>
       </c>
       <c r="R50" t="n">
-        <v>6815201</v>
+        <v>6814647</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5946,7 +5951,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5956,7 +5961,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5983,10 +5988,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131195826</v>
+        <v>131195620</v>
       </c>
       <c r="B51" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5994,34 +5999,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>440688</v>
+        <v>440802</v>
       </c>
       <c r="R51" t="n">
-        <v>6815083</v>
+        <v>6815292</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6053,7 +6063,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6063,7 +6073,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6090,7 +6100,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131195772</v>
+        <v>131195792</v>
       </c>
       <c r="B52" t="n">
         <v>79250</v>
@@ -6125,10 +6135,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>440955</v>
+        <v>440746</v>
       </c>
       <c r="R52" t="n">
-        <v>6814897</v>
+        <v>6815201</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6160,7 +6170,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6170,7 +6180,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6197,7 +6207,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131195880</v>
+        <v>131195826</v>
       </c>
       <c r="B53" t="n">
         <v>79250</v>
@@ -6232,10 +6242,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>440820</v>
+        <v>440688</v>
       </c>
       <c r="R53" t="n">
-        <v>6814616</v>
+        <v>6815083</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6267,7 +6277,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6277,7 +6287,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6304,7 +6314,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131195803</v>
+        <v>131195772</v>
       </c>
       <c r="B54" t="n">
         <v>79250</v>
@@ -6339,10 +6349,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>441101</v>
+        <v>440955</v>
       </c>
       <c r="R54" t="n">
-        <v>6815283</v>
+        <v>6814897</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6374,7 +6384,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6384,7 +6394,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6411,7 +6421,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131195748</v>
+        <v>131195880</v>
       </c>
       <c r="B55" t="n">
         <v>79250</v>
@@ -6446,10 +6456,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>441151</v>
+        <v>440820</v>
       </c>
       <c r="R55" t="n">
-        <v>6814715</v>
+        <v>6814616</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6481,7 +6491,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6491,7 +6501,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6518,7 +6528,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131195860</v>
+        <v>131195803</v>
       </c>
       <c r="B56" t="n">
         <v>79250</v>
@@ -6553,10 +6563,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>440531</v>
+        <v>441101</v>
       </c>
       <c r="R56" t="n">
-        <v>6815095</v>
+        <v>6815283</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6588,7 +6598,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6598,7 +6608,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6625,7 +6635,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131195778</v>
+        <v>131195748</v>
       </c>
       <c r="B57" t="n">
         <v>79250</v>
@@ -6660,10 +6670,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>440906</v>
+        <v>441151</v>
       </c>
       <c r="R57" t="n">
-        <v>6814928</v>
+        <v>6814715</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6695,7 +6705,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6705,7 +6715,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6732,10 +6742,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131195648</v>
+        <v>131195860</v>
       </c>
       <c r="B58" t="n">
-        <v>57885</v>
+        <v>79250</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6743,39 +6753,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>440835</v>
+        <v>440531</v>
       </c>
       <c r="R58" t="n">
-        <v>6815088</v>
+        <v>6815095</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6807,7 +6812,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6817,7 +6822,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6844,10 +6849,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131195646</v>
+        <v>131195778</v>
       </c>
       <c r="B59" t="n">
-        <v>57885</v>
+        <v>79250</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6855,39 +6860,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>440867</v>
+        <v>440906</v>
       </c>
       <c r="R59" t="n">
-        <v>6814841</v>
+        <v>6814928</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6919,7 +6919,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7063,10 +7063,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131195767</v>
+        <v>131195612</v>
       </c>
       <c r="B61" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7074,34 +7074,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>440955</v>
+        <v>440929</v>
       </c>
       <c r="R61" t="n">
-        <v>6814833</v>
+        <v>6814703</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7133,7 +7138,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7143,7 +7148,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7170,10 +7175,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131195816</v>
+        <v>131195626</v>
       </c>
       <c r="B62" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7181,34 +7186,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>440817</v>
+        <v>440651</v>
       </c>
       <c r="R62" t="n">
-        <v>6815256</v>
+        <v>6814982</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7240,7 +7250,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7250,7 +7260,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7277,10 +7287,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131195791</v>
+        <v>131195632</v>
       </c>
       <c r="B63" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7288,34 +7298,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>440752</v>
+        <v>440502</v>
       </c>
       <c r="R63" t="n">
-        <v>6815180</v>
+        <v>6815157</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7347,7 +7362,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7357,7 +7372,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7384,10 +7399,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131195672</v>
+        <v>131195647</v>
       </c>
       <c r="B64" t="n">
-        <v>79007</v>
+        <v>57885</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7395,34 +7410,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>440792</v>
+        <v>440845</v>
       </c>
       <c r="R64" t="n">
-        <v>6814547</v>
+        <v>6814584</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7454,7 +7474,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7464,7 +7484,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7491,7 +7511,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131195883</v>
+        <v>131195767</v>
       </c>
       <c r="B65" t="n">
         <v>79250</v>
@@ -7526,10 +7546,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>440739</v>
+        <v>440955</v>
       </c>
       <c r="R65" t="n">
-        <v>6814583</v>
+        <v>6814833</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7561,7 +7581,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7571,7 +7591,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7598,7 +7618,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131195797</v>
+        <v>131195816</v>
       </c>
       <c r="B66" t="n">
         <v>79250</v>
@@ -7633,10 +7653,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>440932</v>
+        <v>440817</v>
       </c>
       <c r="R66" t="n">
-        <v>6815337</v>
+        <v>6815256</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7668,7 +7688,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7678,7 +7698,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7705,7 +7725,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131195695</v>
+        <v>131195791</v>
       </c>
       <c r="B67" t="n">
         <v>79250</v>
@@ -7734,21 +7754,16 @@
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>440757</v>
+        <v>440752</v>
       </c>
       <c r="R67" t="n">
-        <v>6815193</v>
+        <v>6815180</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7780,7 +7795,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7790,7 +7805,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7817,10 +7832,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131195647</v>
+        <v>131195672</v>
       </c>
       <c r="B68" t="n">
-        <v>57885</v>
+        <v>79007</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7828,39 +7843,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>440845</v>
+        <v>440792</v>
       </c>
       <c r="R68" t="n">
-        <v>6814584</v>
+        <v>6814547</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7892,7 +7902,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7902,7 +7912,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7929,10 +7939,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131195612</v>
+        <v>131195883</v>
       </c>
       <c r="B69" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7940,39 +7950,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>440929</v>
+        <v>440739</v>
       </c>
       <c r="R69" t="n">
-        <v>6814703</v>
+        <v>6814583</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8004,7 +8009,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8014,7 +8019,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8041,10 +8046,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131195626</v>
+        <v>131195797</v>
       </c>
       <c r="B70" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8052,39 +8057,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>440651</v>
+        <v>440932</v>
       </c>
       <c r="R70" t="n">
-        <v>6814982</v>
+        <v>6815337</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8116,7 +8116,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8153,10 +8153,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131195632</v>
+        <v>131195695</v>
       </c>
       <c r="B71" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8164,27 +8164,27 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -8193,10 +8193,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>440502</v>
+        <v>440757</v>
       </c>
       <c r="R71" t="n">
-        <v>6815157</v>
+        <v>6815193</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8228,7 +8228,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -12383,45 +12383,50 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>131195637</v>
+        <v>131195917</v>
       </c>
       <c r="B110" t="n">
-        <v>58047</v>
+        <v>5177</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>441072</v>
+        <v>440934</v>
       </c>
       <c r="R110" t="n">
-        <v>6814663</v>
+        <v>6814927</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12453,7 +12458,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12463,7 +12468,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12490,38 +12495,38 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>131195917</v>
+        <v>131195600</v>
       </c>
       <c r="B111" t="n">
-        <v>5177</v>
+        <v>57888</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -12530,10 +12535,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>440934</v>
+        <v>440842</v>
       </c>
       <c r="R111" t="n">
-        <v>6814927</v>
+        <v>6815077</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12565,7 +12570,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12575,14 +12580,14 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
       <c r="AE111" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG111" t="b">
         <v>0</v>
@@ -12602,10 +12607,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>131195600</v>
+        <v>131195662</v>
       </c>
       <c r="B112" t="n">
-        <v>57888</v>
+        <v>78262</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12613,39 +12618,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>440842</v>
+        <v>440925</v>
       </c>
       <c r="R112" t="n">
-        <v>6815077</v>
+        <v>6814889</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12677,7 +12677,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12687,14 +12687,14 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
       <c r="AE112" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG112" t="b">
         <v>0</v>
@@ -12714,10 +12714,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131195662</v>
+        <v>131195798</v>
       </c>
       <c r="B113" t="n">
-        <v>78262</v>
+        <v>79250</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12725,21 +12725,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12749,10 +12749,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>440925</v>
+        <v>440943</v>
       </c>
       <c r="R113" t="n">
-        <v>6814889</v>
+        <v>6815341</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12784,7 +12784,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12794,7 +12794,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12821,32 +12821,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131195798</v>
+        <v>131195567</v>
       </c>
       <c r="B114" t="n">
-        <v>79250</v>
+        <v>91781</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12856,10 +12856,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>440943</v>
+        <v>440907</v>
       </c>
       <c r="R114" t="n">
-        <v>6815341</v>
+        <v>6814875</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12891,7 +12891,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12901,7 +12901,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12928,32 +12928,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131195567</v>
+        <v>131195842</v>
       </c>
       <c r="B115" t="n">
-        <v>91781</v>
+        <v>79250</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12963,10 +12963,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>440907</v>
+        <v>440509</v>
       </c>
       <c r="R115" t="n">
-        <v>6814875</v>
+        <v>6815018</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12998,7 +12998,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13008,7 +13008,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13035,7 +13035,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131195842</v>
+        <v>131195776</v>
       </c>
       <c r="B116" t="n">
         <v>79250</v>
@@ -13070,10 +13070,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>440509</v>
+        <v>440926</v>
       </c>
       <c r="R116" t="n">
-        <v>6815018</v>
+        <v>6814927</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13105,7 +13105,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13115,7 +13115,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13142,7 +13142,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131195776</v>
+        <v>131195884</v>
       </c>
       <c r="B117" t="n">
         <v>79250</v>
@@ -13177,10 +13177,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>440926</v>
+        <v>440736</v>
       </c>
       <c r="R117" t="n">
-        <v>6814927</v>
+        <v>6814569</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13212,7 +13212,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13222,7 +13222,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13249,7 +13249,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131195884</v>
+        <v>131195739</v>
       </c>
       <c r="B118" t="n">
         <v>79250</v>
@@ -13284,10 +13284,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>440736</v>
+        <v>441199</v>
       </c>
       <c r="R118" t="n">
-        <v>6814569</v>
+        <v>6814633</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13319,7 +13319,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13329,7 +13329,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13356,7 +13356,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131195739</v>
+        <v>131195871</v>
       </c>
       <c r="B119" t="n">
         <v>79250</v>
@@ -13391,10 +13391,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>441199</v>
+        <v>440853</v>
       </c>
       <c r="R119" t="n">
-        <v>6814633</v>
+        <v>6814767</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13426,7 +13426,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13436,7 +13436,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13463,7 +13463,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131195871</v>
+        <v>131195839</v>
       </c>
       <c r="B120" t="n">
         <v>79250</v>
@@ -13498,10 +13498,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>440853</v>
+        <v>440519</v>
       </c>
       <c r="R120" t="n">
-        <v>6814767</v>
+        <v>6814964</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13543,7 +13543,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13570,10 +13570,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>131195839</v>
+        <v>131195558</v>
       </c>
       <c r="B121" t="n">
-        <v>79250</v>
+        <v>83230</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13581,21 +13581,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13605,10 +13605,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>440519</v>
+        <v>440881</v>
       </c>
       <c r="R121" t="n">
-        <v>6814964</v>
+        <v>6815052</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13640,7 +13640,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13650,7 +13650,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13677,10 +13677,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>131195558</v>
+        <v>131195840</v>
       </c>
       <c r="B122" t="n">
-        <v>83230</v>
+        <v>79250</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13688,21 +13688,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13712,10 +13712,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>440881</v>
+        <v>440518</v>
       </c>
       <c r="R122" t="n">
-        <v>6815052</v>
+        <v>6814966</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13747,7 +13747,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13757,7 +13757,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13784,7 +13784,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>131195840</v>
+        <v>131195844</v>
       </c>
       <c r="B123" t="n">
         <v>79250</v>
@@ -13819,10 +13819,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>440518</v>
+        <v>440488</v>
       </c>
       <c r="R123" t="n">
-        <v>6814966</v>
+        <v>6815047</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13854,7 +13854,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13864,7 +13864,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13891,32 +13891,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>131195844</v>
+        <v>131195573</v>
       </c>
       <c r="B124" t="n">
-        <v>79250</v>
+        <v>91781</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13926,10 +13926,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>440488</v>
+        <v>440508</v>
       </c>
       <c r="R124" t="n">
-        <v>6815047</v>
+        <v>6815137</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13961,7 +13961,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13971,7 +13971,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13998,32 +13998,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>131195573</v>
+        <v>131195637</v>
       </c>
       <c r="B125" t="n">
-        <v>91781</v>
+        <v>58047</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14033,10 +14033,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>440508</v>
+        <v>441072</v>
       </c>
       <c r="R125" t="n">
-        <v>6815137</v>
+        <v>6814663</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14068,7 +14068,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14078,7 +14078,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -19005,10 +19005,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>131195914</v>
+        <v>131195847</v>
       </c>
       <c r="B171" t="n">
-        <v>89203</v>
+        <v>79250</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19016,21 +19016,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -19040,10 +19040,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>440856</v>
+        <v>440465</v>
       </c>
       <c r="R171" t="n">
-        <v>6814840</v>
+        <v>6815075</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19075,7 +19075,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -19085,7 +19085,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19112,7 +19112,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>131195847</v>
+        <v>131195788</v>
       </c>
       <c r="B172" t="n">
         <v>79250</v>
@@ -19147,10 +19147,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>440465</v>
+        <v>440795</v>
       </c>
       <c r="R172" t="n">
-        <v>6815075</v>
+        <v>6815104</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19182,7 +19182,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -19192,7 +19192,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19219,7 +19219,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>131195788</v>
+        <v>131195901</v>
       </c>
       <c r="B173" t="n">
         <v>79250</v>
@@ -19254,10 +19254,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>440795</v>
+        <v>440885</v>
       </c>
       <c r="R173" t="n">
-        <v>6815104</v>
+        <v>6814475</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19289,7 +19289,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -19299,7 +19299,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19326,7 +19326,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>131195901</v>
+        <v>131195804</v>
       </c>
       <c r="B174" t="n">
         <v>79250</v>
@@ -19361,10 +19361,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>440885</v>
+        <v>441158</v>
       </c>
       <c r="R174" t="n">
-        <v>6814475</v>
+        <v>6815289</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19396,7 +19396,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -19406,7 +19406,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19433,7 +19433,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>131195804</v>
+        <v>131195708</v>
       </c>
       <c r="B175" t="n">
         <v>79250</v>
@@ -19462,16 +19462,21 @@
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P175" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>441158</v>
+        <v>440774</v>
       </c>
       <c r="R175" t="n">
-        <v>6815289</v>
+        <v>6814546</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19503,7 +19508,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -19513,7 +19518,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19540,7 +19545,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>131195708</v>
+        <v>131195793</v>
       </c>
       <c r="B176" t="n">
         <v>79250</v>
@@ -19569,21 +19574,16 @@
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P176" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>440774</v>
+        <v>440758</v>
       </c>
       <c r="R176" t="n">
-        <v>6814546</v>
+        <v>6815261</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19615,7 +19615,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -19625,7 +19625,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19652,7 +19652,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>131195793</v>
+        <v>131195849</v>
       </c>
       <c r="B177" t="n">
         <v>79250</v>
@@ -19687,10 +19687,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>440758</v>
+        <v>440438</v>
       </c>
       <c r="R177" t="n">
-        <v>6815261</v>
+        <v>6815100</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19722,7 +19722,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -19732,7 +19732,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19759,7 +19759,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>131195849</v>
+        <v>131195783</v>
       </c>
       <c r="B178" t="n">
         <v>79250</v>
@@ -19794,10 +19794,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>440438</v>
+        <v>440881</v>
       </c>
       <c r="R178" t="n">
-        <v>6815100</v>
+        <v>6815052</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19829,7 +19829,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -19839,7 +19839,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19866,7 +19866,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>131195783</v>
+        <v>131195744</v>
       </c>
       <c r="B179" t="n">
         <v>79250</v>
@@ -19901,10 +19901,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>440881</v>
+        <v>441179</v>
       </c>
       <c r="R179" t="n">
-        <v>6815052</v>
+        <v>6814681</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19936,7 +19936,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -19946,7 +19946,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19973,10 +19973,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>131195744</v>
+        <v>131195914</v>
       </c>
       <c r="B180" t="n">
-        <v>79250</v>
+        <v>89203</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19984,21 +19984,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -20008,10 +20008,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>441179</v>
+        <v>440856</v>
       </c>
       <c r="R180" t="n">
-        <v>6814681</v>
+        <v>6814840</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20043,7 +20043,7 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -20053,7 +20053,7 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -24323,10 +24323,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>131195813</v>
+        <v>131195616</v>
       </c>
       <c r="B220" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -24334,34 +24334,39 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P220" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>440932</v>
+        <v>440778</v>
       </c>
       <c r="R220" t="n">
-        <v>6815320</v>
+        <v>6815139</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24393,7 +24398,7 @@
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
@@ -24403,7 +24408,7 @@
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -24430,7 +24435,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>131195779</v>
+        <v>131195813</v>
       </c>
       <c r="B221" t="n">
         <v>79250</v>
@@ -24465,10 +24470,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>440899</v>
+        <v>440932</v>
       </c>
       <c r="R221" t="n">
-        <v>6814894</v>
+        <v>6815320</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -24500,7 +24505,7 @@
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
@@ -24510,7 +24515,7 @@
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -24537,7 +24542,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>131195817</v>
+        <v>131195779</v>
       </c>
       <c r="B222" t="n">
         <v>79250</v>
@@ -24572,10 +24577,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>440796</v>
+        <v>440899</v>
       </c>
       <c r="R222" t="n">
-        <v>6815242</v>
+        <v>6814894</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24607,7 +24612,7 @@
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
@@ -24617,7 +24622,7 @@
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -24644,7 +24649,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>131195790</v>
+        <v>131195817</v>
       </c>
       <c r="B223" t="n">
         <v>79250</v>
@@ -24679,10 +24684,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>440755</v>
+        <v>440796</v>
       </c>
       <c r="R223" t="n">
-        <v>6815170</v>
+        <v>6815242</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -24714,7 +24719,7 @@
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -24724,7 +24729,7 @@
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -24751,7 +24756,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>131195881</v>
+        <v>131195790</v>
       </c>
       <c r="B224" t="n">
         <v>79250</v>
@@ -24786,10 +24791,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>440812</v>
+        <v>440755</v>
       </c>
       <c r="R224" t="n">
-        <v>6814615</v>
+        <v>6815170</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -24821,7 +24826,7 @@
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -24831,7 +24836,7 @@
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -24858,7 +24863,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>131195885</v>
+        <v>131195881</v>
       </c>
       <c r="B225" t="n">
         <v>79250</v>
@@ -24893,10 +24898,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>440763</v>
+        <v>440812</v>
       </c>
       <c r="R225" t="n">
-        <v>6814545</v>
+        <v>6814615</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24928,7 +24933,7 @@
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
@@ -24938,7 +24943,7 @@
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -24965,10 +24970,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>131195560</v>
+        <v>131195885</v>
       </c>
       <c r="B226" t="n">
-        <v>83230</v>
+        <v>79250</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -24976,21 +24981,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -25000,10 +25005,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>440870</v>
+        <v>440763</v>
       </c>
       <c r="R226" t="n">
-        <v>6815057</v>
+        <v>6814545</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -25035,7 +25040,7 @@
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -25045,7 +25050,7 @@
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -25072,10 +25077,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>131195787</v>
+        <v>131195560</v>
       </c>
       <c r="B227" t="n">
-        <v>79250</v>
+        <v>83230</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -25083,21 +25088,21 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -25107,10 +25112,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>440804</v>
+        <v>440870</v>
       </c>
       <c r="R227" t="n">
-        <v>6815082</v>
+        <v>6815057</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25142,7 +25147,7 @@
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
@@ -25152,7 +25157,7 @@
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -25179,7 +25184,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>131195782</v>
+        <v>131195787</v>
       </c>
       <c r="B228" t="n">
         <v>79250</v>
@@ -25214,10 +25219,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>440889</v>
+        <v>440804</v>
       </c>
       <c r="R228" t="n">
-        <v>6815021</v>
+        <v>6815082</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25249,7 +25254,7 @@
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
@@ -25259,7 +25264,7 @@
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -25286,7 +25291,7 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>131195907</v>
+        <v>131195782</v>
       </c>
       <c r="B229" t="n">
         <v>79250</v>
@@ -25321,10 +25326,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>440904</v>
+        <v>440889</v>
       </c>
       <c r="R229" t="n">
-        <v>6814327</v>
+        <v>6815021</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25356,7 +25361,7 @@
       </c>
       <c r="Z229" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
@@ -25366,7 +25371,7 @@
       </c>
       <c r="AB229" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -25393,10 +25398,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>131195616</v>
+        <v>131195907</v>
       </c>
       <c r="B230" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -25404,39 +25409,34 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
-      <c r="M230" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P230" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>440778</v>
+        <v>440904</v>
       </c>
       <c r="R230" t="n">
-        <v>6815139</v>
+        <v>6814327</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -25468,7 +25468,7 @@
       </c>
       <c r="Z230" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
@@ -25478,7 +25478,7 @@
       </c>
       <c r="AB230" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -26932,10 +26932,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>131197405</v>
+        <v>131197408</v>
       </c>
       <c r="B245" t="n">
-        <v>79250</v>
+        <v>83096</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -26943,21 +26943,21 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -26967,10 +26967,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>441095</v>
+        <v>440929</v>
       </c>
       <c r="R245" t="n">
-        <v>6814644</v>
+        <v>6814705</v>
       </c>
       <c r="S245" t="n">
         <v>25</v>
@@ -27029,10 +27029,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>131197408</v>
+        <v>131197405</v>
       </c>
       <c r="B246" t="n">
-        <v>83096</v>
+        <v>79250</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -27040,21 +27040,21 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -27064,10 +27064,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>440929</v>
+        <v>441095</v>
       </c>
       <c r="R246" t="n">
-        <v>6814705</v>
+        <v>6814644</v>
       </c>
       <c r="S246" t="n">
         <v>25</v>
@@ -28359,10 +28359,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>131178705</v>
+        <v>131186232</v>
       </c>
       <c r="B259" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -28370,39 +28370,34 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
-      <c r="M259" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P259" t="inlineStr">
         <is>
-          <t>Ytter-Navardalen, Dlr</t>
+          <t>Navarnäsberget, Dlr</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>440802</v>
+        <v>440664</v>
       </c>
       <c r="R259" t="n">
-        <v>6815254</v>
+        <v>6814943</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -28432,24 +28427,9 @@
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="Z259" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AA259" t="inlineStr">
         <is>
           <t>2026-02-16</t>
-        </is>
-      </c>
-      <c r="AB259" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
-      <c r="AC259" t="inlineStr">
-        <is>
-          <t>2 bild gran, ringhack garn</t>
         </is>
       </c>
       <c r="AD259" t="b">
@@ -28476,10 +28456,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>131186232</v>
+        <v>131186195</v>
       </c>
       <c r="B260" t="n">
-        <v>79250</v>
+        <v>57885</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -28487,34 +28467,39 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P260" t="inlineStr">
         <is>
           <t>Navarnäsberget, Dlr</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>440664</v>
+        <v>440702</v>
       </c>
       <c r="R260" t="n">
-        <v>6814943</v>
+        <v>6814996</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -28547,6 +28532,11 @@
       <c r="AA260" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AC260" t="inlineStr">
+        <is>
+          <t>2 bild</t>
         </is>
       </c>
       <c r="AD260" t="b">
@@ -28573,10 +28563,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>131186195</v>
+        <v>131178705</v>
       </c>
       <c r="B261" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -28584,16 +28574,16 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -28604,19 +28594,19 @@
       <c r="I261" t="inlineStr"/>
       <c r="M261" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P261" t="inlineStr">
         <is>
-          <t>Navarnäsberget, Dlr</t>
+          <t>Ytter-Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>440702</v>
+        <v>440802</v>
       </c>
       <c r="R261" t="n">
-        <v>6814996</v>
+        <v>6815254</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -28646,14 +28636,24 @@
           <t>2026-02-16</t>
         </is>
       </c>
+      <c r="Z261" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AA261" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
+      <c r="AB261" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AC261" t="inlineStr">
         <is>
-          <t>2 bild</t>
+          <t>2 bild gran, ringhack garn</t>
         </is>
       </c>
       <c r="AD261" t="b">
@@ -29536,10 +29536,10 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>131186470</v>
+        <v>131186418</v>
       </c>
       <c r="B270" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -29547,24 +29547,29 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P270" t="inlineStr">
         <is>
           <t>Navarnäsberget, Dlr</t>
@@ -29633,7 +29638,7 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>131185798</v>
+        <v>131186470</v>
       </c>
       <c r="B271" t="n">
         <v>79250</v>
@@ -29668,10 +29673,10 @@
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>440698</v>
+        <v>440503</v>
       </c>
       <c r="R271" t="n">
-        <v>6815085</v>
+        <v>6815000</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -29730,7 +29735,7 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>131186261</v>
+        <v>131185798</v>
       </c>
       <c r="B272" t="n">
         <v>79250</v>
@@ -29765,10 +29770,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>440643</v>
+        <v>440698</v>
       </c>
       <c r="R272" t="n">
-        <v>6814928</v>
+        <v>6815085</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -29827,10 +29832,10 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>131186418</v>
+        <v>131186261</v>
       </c>
       <c r="B273" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -29838,39 +29843,34 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
-      <c r="M273" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P273" t="inlineStr">
         <is>
           <t>Navarnäsberget, Dlr</t>
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>440503</v>
+        <v>440643</v>
       </c>
       <c r="R273" t="n">
-        <v>6815000</v>
+        <v>6814928</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -30930,10 +30930,10 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>131177681</v>
+        <v>131180507</v>
       </c>
       <c r="B283" t="n">
-        <v>79250</v>
+        <v>57885</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -30941,34 +30941,39 @@
         </is>
       </c>
       <c r="E283" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I283" t="inlineStr"/>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P283" t="inlineStr">
         <is>
-          <t>Ytter-Navardalen, Dlr</t>
+          <t>Navarnäsberget, Dlr</t>
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>440755</v>
+        <v>441151</v>
       </c>
       <c r="R283" t="n">
-        <v>6815214</v>
+        <v>6815264</v>
       </c>
       <c r="S283" t="n">
         <v>10</v>
@@ -31015,7 +31020,7 @@
       </c>
       <c r="AC283" t="inlineStr">
         <is>
-          <t>1 bild garn på gren</t>
+          <t>1 bild gran 2 hack</t>
         </is>
       </c>
       <c r="AD283" t="b">
@@ -31042,10 +31047,10 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>131180507</v>
+        <v>131177681</v>
       </c>
       <c r="B284" t="n">
-        <v>57885</v>
+        <v>79250</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -31053,39 +31058,34 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
-      <c r="M284" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P284" t="inlineStr">
         <is>
-          <t>Navarnäsberget, Dlr</t>
+          <t>Ytter-Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>441151</v>
+        <v>440755</v>
       </c>
       <c r="R284" t="n">
-        <v>6815264</v>
+        <v>6815214</v>
       </c>
       <c r="S284" t="n">
         <v>10</v>
@@ -31132,7 +31132,7 @@
       </c>
       <c r="AC284" t="inlineStr">
         <is>
-          <t>1 bild gran 2 hack</t>
+          <t>1 bild garn på gren</t>
         </is>
       </c>
       <c r="AD284" t="b">
@@ -32958,10 +32958,10 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>131187941</v>
+        <v>131186236</v>
       </c>
       <c r="B302" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -32969,16 +32969,16 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -32989,7 +32989,7 @@
       <c r="I302" t="inlineStr"/>
       <c r="M302" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P302" t="inlineStr">
@@ -32998,10 +32998,10 @@
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>440573</v>
+        <v>440643</v>
       </c>
       <c r="R302" t="n">
-        <v>6815085</v>
+        <v>6814928</v>
       </c>
       <c r="S302" t="n">
         <v>10</v>
@@ -33034,11 +33034,6 @@
       <c r="AA302" t="inlineStr">
         <is>
           <t>2026-02-16</t>
-        </is>
-      </c>
-      <c r="AC302" t="inlineStr">
-        <is>
-          <t>1 bild äldre gran många hack</t>
         </is>
       </c>
       <c r="AD302" t="b">
@@ -33065,7 +33060,7 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>131186236</v>
+        <v>131176405</v>
       </c>
       <c r="B303" t="n">
         <v>57888</v>
@@ -33096,19 +33091,19 @@
       <c r="I303" t="inlineStr"/>
       <c r="M303" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P303" t="inlineStr">
         <is>
-          <t>Navarnäsberget, Dlr</t>
+          <t>Ytter-Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>440643</v>
+        <v>440856</v>
       </c>
       <c r="R303" t="n">
-        <v>6814928</v>
+        <v>6815124</v>
       </c>
       <c r="S303" t="n">
         <v>10</v>
@@ -33138,9 +33133,19 @@
           <t>2026-02-16</t>
         </is>
       </c>
+      <c r="Z303" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AA303" t="inlineStr">
         <is>
           <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AB303" t="inlineStr">
+        <is>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD303" t="b">
@@ -33167,10 +33172,10 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>131176405</v>
+        <v>131176293</v>
       </c>
       <c r="B304" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -33178,39 +33183,34 @@
         </is>
       </c>
       <c r="E304" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I304" t="inlineStr"/>
-      <c r="M304" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P304" t="inlineStr">
         <is>
           <t>Ytter-Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>440856</v>
+        <v>440860</v>
       </c>
       <c r="R304" t="n">
-        <v>6815124</v>
+        <v>6815093</v>
       </c>
       <c r="S304" t="n">
         <v>10</v>
@@ -33279,10 +33279,10 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>131176293</v>
+        <v>131187941</v>
       </c>
       <c r="B305" t="n">
-        <v>79250</v>
+        <v>57885</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -33290,34 +33290,39 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I305" t="inlineStr"/>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P305" t="inlineStr">
         <is>
-          <t>Ytter-Navardalen, Dlr</t>
+          <t>Navarnäsberget, Dlr</t>
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>440860</v>
+        <v>440573</v>
       </c>
       <c r="R305" t="n">
-        <v>6815093</v>
+        <v>6815085</v>
       </c>
       <c r="S305" t="n">
         <v>10</v>
@@ -33347,19 +33352,14 @@
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="Z305" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AA305" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="AB305" t="inlineStr">
-        <is>
-          <t>09:13</t>
+      <c r="AC305" t="inlineStr">
+        <is>
+          <t>1 bild äldre gran många hack</t>
         </is>
       </c>
       <c r="AD305" t="b">
@@ -33677,10 +33677,10 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>131186107</v>
+        <v>131176233</v>
       </c>
       <c r="B309" t="n">
-        <v>89203</v>
+        <v>79250</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -33688,34 +33688,34 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I309" t="inlineStr"/>
       <c r="P309" t="inlineStr">
         <is>
-          <t>Navarnäsberget, Dlr</t>
+          <t>Ytter-Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>440715</v>
+        <v>440893</v>
       </c>
       <c r="R309" t="n">
-        <v>6815098</v>
+        <v>6815041</v>
       </c>
       <c r="S309" t="n">
         <v>10</v>
@@ -33745,14 +33745,19 @@
           <t>2026-02-16</t>
         </is>
       </c>
+      <c r="Z309" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AA309" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="AC309" t="inlineStr">
-        <is>
-          <t>2 bild</t>
+      <c r="AB309" t="inlineStr">
+        <is>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD309" t="b">
@@ -33779,7 +33784,7 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>131176233</v>
+        <v>131189930</v>
       </c>
       <c r="B310" t="n">
         <v>79250</v>
@@ -33814,10 +33819,10 @@
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>440893</v>
+        <v>440855</v>
       </c>
       <c r="R310" t="n">
-        <v>6815041</v>
+        <v>6814679</v>
       </c>
       <c r="S310" t="n">
         <v>10</v>
@@ -33847,19 +33852,14 @@
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="Z310" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AA310" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="AB310" t="inlineStr">
-        <is>
-          <t>09:13</t>
+      <c r="AC310" t="inlineStr">
+        <is>
+          <t>Rikligt på tallstam</t>
         </is>
       </c>
       <c r="AD310" t="b">
@@ -33886,10 +33886,10 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>131189930</v>
+        <v>131186107</v>
       </c>
       <c r="B311" t="n">
-        <v>79250</v>
+        <v>89203</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -33897,34 +33897,34 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I311" t="inlineStr"/>
       <c r="P311" t="inlineStr">
         <is>
-          <t>Ytter-Navardalen, Dlr</t>
+          <t>Navarnäsberget, Dlr</t>
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>440855</v>
+        <v>440715</v>
       </c>
       <c r="R311" t="n">
-        <v>6814679</v>
+        <v>6815098</v>
       </c>
       <c r="S311" t="n">
         <v>10</v>
@@ -33961,7 +33961,7 @@
       </c>
       <c r="AC311" t="inlineStr">
         <is>
-          <t>Rikligt på tallstam</t>
+          <t>2 bild</t>
         </is>
       </c>
       <c r="AD311" t="b">

--- a/artfynd/A 5994-2026 artfynd.xlsx
+++ b/artfynd/A 5994-2026 artfynd.xlsx
@@ -2947,10 +2947,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131195762</v>
+        <v>131195614</v>
       </c>
       <c r="B23" t="n">
-        <v>79254</v>
+        <v>57892</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2958,34 +2958,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440958</v>
+        <v>440798</v>
       </c>
       <c r="R23" t="n">
-        <v>6814746</v>
+        <v>6815081</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3017,7 +3022,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3027,7 +3032,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3054,10 +3059,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131195886</v>
+        <v>131195601</v>
       </c>
       <c r="B24" t="n">
-        <v>79254</v>
+        <v>57892</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3065,34 +3070,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440835</v>
+        <v>440519</v>
       </c>
       <c r="R24" t="n">
-        <v>6814572</v>
+        <v>6815131</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3124,7 +3134,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3134,7 +3144,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Dagsfärska spår efter födosök (små barkbitar på nysnö)</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3161,45 +3176,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131195873</v>
+        <v>131195551</v>
       </c>
       <c r="B25" t="n">
-        <v>79254</v>
+        <v>5197</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440848</v>
+        <v>440944</v>
       </c>
       <c r="R25" t="n">
-        <v>6814711</v>
+        <v>6814700</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3231,7 +3251,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3241,7 +3261,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3268,10 +3288,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131195904</v>
+        <v>131195670</v>
       </c>
       <c r="B26" t="n">
-        <v>79254</v>
+        <v>81239</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3279,21 +3299,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3303,10 +3323,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>440820</v>
+        <v>440868</v>
       </c>
       <c r="R26" t="n">
-        <v>6814384</v>
+        <v>6814651</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3338,7 +3358,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3348,7 +3368,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3375,32 +3395,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131195758</v>
+        <v>131195654</v>
       </c>
       <c r="B27" t="n">
-        <v>79254</v>
+        <v>92281</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3410,10 +3430,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>441015</v>
+        <v>440686</v>
       </c>
       <c r="R27" t="n">
-        <v>6814688</v>
+        <v>6815080</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3445,7 +3465,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3455,7 +3475,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3482,7 +3502,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131195751</v>
+        <v>131195762</v>
       </c>
       <c r="B28" t="n">
         <v>79254</v>
@@ -3517,10 +3537,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>441102</v>
+        <v>440958</v>
       </c>
       <c r="R28" t="n">
-        <v>6814644</v>
+        <v>6814746</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3552,7 +3572,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3562,7 +3582,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3589,7 +3609,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131195874</v>
+        <v>131195886</v>
       </c>
       <c r="B29" t="n">
         <v>79254</v>
@@ -3624,10 +3644,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>440845</v>
+        <v>440835</v>
       </c>
       <c r="R29" t="n">
-        <v>6814694</v>
+        <v>6814572</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3659,7 +3679,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3669,7 +3689,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3696,7 +3716,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131195821</v>
+        <v>131195873</v>
       </c>
       <c r="B30" t="n">
         <v>79254</v>
@@ -3731,10 +3751,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440732</v>
+        <v>440848</v>
       </c>
       <c r="R30" t="n">
-        <v>6815137</v>
+        <v>6814711</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3766,7 +3786,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3776,7 +3796,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3803,7 +3823,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131195774</v>
+        <v>131195904</v>
       </c>
       <c r="B31" t="n">
         <v>79254</v>
@@ -3838,10 +3858,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440927</v>
+        <v>440820</v>
       </c>
       <c r="R31" t="n">
-        <v>6814891</v>
+        <v>6814384</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3873,7 +3893,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3883,7 +3903,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3910,7 +3930,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131195851</v>
+        <v>131195758</v>
       </c>
       <c r="B32" t="n">
         <v>79254</v>
@@ -3945,10 +3965,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440426</v>
+        <v>441015</v>
       </c>
       <c r="R32" t="n">
-        <v>6815128</v>
+        <v>6814688</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3980,7 +4000,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3990,7 +4010,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4017,32 +4037,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131195654</v>
+        <v>131195751</v>
       </c>
       <c r="B33" t="n">
-        <v>92281</v>
+        <v>79254</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4052,10 +4072,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440686</v>
+        <v>441102</v>
       </c>
       <c r="R33" t="n">
-        <v>6815080</v>
+        <v>6814644</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4087,7 +4107,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4097,7 +4117,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4124,10 +4144,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131195670</v>
+        <v>131195874</v>
       </c>
       <c r="B34" t="n">
-        <v>81239</v>
+        <v>79254</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4135,21 +4155,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4159,10 +4179,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440868</v>
+        <v>440845</v>
       </c>
       <c r="R34" t="n">
-        <v>6814651</v>
+        <v>6814694</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4194,7 +4214,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4204,7 +4224,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4231,10 +4251,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131195564</v>
+        <v>131195821</v>
       </c>
       <c r="B35" t="n">
-        <v>83234</v>
+        <v>79254</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4242,21 +4262,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4266,10 +4286,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440439</v>
+        <v>440732</v>
       </c>
       <c r="R35" t="n">
-        <v>6815121</v>
+        <v>6815137</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4301,7 +4321,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4311,7 +4331,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4338,10 +4358,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131195643</v>
+        <v>131195774</v>
       </c>
       <c r="B36" t="n">
-        <v>57889</v>
+        <v>79254</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4349,39 +4369,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440858</v>
+        <v>440927</v>
       </c>
       <c r="R36" t="n">
-        <v>6815063</v>
+        <v>6814891</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4413,7 +4428,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4423,7 +4438,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4450,10 +4465,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131195614</v>
+        <v>131195851</v>
       </c>
       <c r="B37" t="n">
-        <v>57892</v>
+        <v>79254</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4461,39 +4476,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440798</v>
+        <v>440426</v>
       </c>
       <c r="R37" t="n">
-        <v>6815081</v>
+        <v>6815128</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4525,7 +4535,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4535,7 +4545,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4562,10 +4572,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131195601</v>
+        <v>131195564</v>
       </c>
       <c r="B38" t="n">
-        <v>57892</v>
+        <v>83234</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4573,39 +4583,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440519</v>
+        <v>440439</v>
       </c>
       <c r="R38" t="n">
-        <v>6815131</v>
+        <v>6815121</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4637,7 +4642,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4647,12 +4652,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:56</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Dagsfärska spår efter födosök (små barkbitar på nysnö)</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4679,27 +4679,27 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131195551</v>
+        <v>131195643</v>
       </c>
       <c r="B39" t="n">
-        <v>5197</v>
+        <v>57889</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4710,7 +4710,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4719,10 +4719,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440944</v>
+        <v>440858</v>
       </c>
       <c r="R39" t="n">
-        <v>6814700</v>
+        <v>6815063</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4754,7 +4754,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -6956,10 +6956,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131195767</v>
+        <v>131195912</v>
       </c>
       <c r="B60" t="n">
-        <v>79254</v>
+        <v>83100</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6967,21 +6967,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6991,10 +6991,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>440955</v>
+        <v>441062</v>
       </c>
       <c r="R60" t="n">
-        <v>6814833</v>
+        <v>6815338</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7063,10 +7063,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131195816</v>
+        <v>131195672</v>
       </c>
       <c r="B61" t="n">
-        <v>79254</v>
+        <v>79011</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7074,21 +7074,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7098,10 +7098,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>440817</v>
+        <v>440792</v>
       </c>
       <c r="R61" t="n">
-        <v>6815256</v>
+        <v>6814547</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7133,7 +7133,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7143,7 +7143,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7170,10 +7170,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131195791</v>
+        <v>131195647</v>
       </c>
       <c r="B62" t="n">
-        <v>79254</v>
+        <v>57889</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7181,34 +7181,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>440752</v>
+        <v>440845</v>
       </c>
       <c r="R62" t="n">
-        <v>6815180</v>
+        <v>6814584</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7240,7 +7245,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7250,7 +7255,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7277,10 +7282,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131195883</v>
+        <v>131195612</v>
       </c>
       <c r="B63" t="n">
-        <v>79254</v>
+        <v>57892</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7288,34 +7293,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>440739</v>
+        <v>440929</v>
       </c>
       <c r="R63" t="n">
-        <v>6814583</v>
+        <v>6814703</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7347,7 +7357,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7357,7 +7367,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7384,7 +7394,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131195797</v>
+        <v>131195767</v>
       </c>
       <c r="B64" t="n">
         <v>79254</v>
@@ -7419,10 +7429,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>440932</v>
+        <v>440955</v>
       </c>
       <c r="R64" t="n">
-        <v>6815337</v>
+        <v>6814833</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7454,7 +7464,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7464,7 +7474,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7491,7 +7501,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131195695</v>
+        <v>131195816</v>
       </c>
       <c r="B65" t="n">
         <v>79254</v>
@@ -7520,21 +7530,16 @@
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>440757</v>
+        <v>440817</v>
       </c>
       <c r="R65" t="n">
-        <v>6815193</v>
+        <v>6815256</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7566,7 +7571,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7576,7 +7581,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7603,10 +7608,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131195672</v>
+        <v>131195791</v>
       </c>
       <c r="B66" t="n">
-        <v>79011</v>
+        <v>79254</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7614,21 +7619,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7638,10 +7643,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>440792</v>
+        <v>440752</v>
       </c>
       <c r="R66" t="n">
-        <v>6814547</v>
+        <v>6815180</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7673,7 +7678,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7683,7 +7688,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7710,10 +7715,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131195647</v>
+        <v>131195883</v>
       </c>
       <c r="B67" t="n">
-        <v>57889</v>
+        <v>79254</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7721,39 +7726,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>440845</v>
+        <v>440739</v>
       </c>
       <c r="R67" t="n">
-        <v>6814584</v>
+        <v>6814583</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7785,7 +7785,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7795,7 +7795,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7822,10 +7822,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131195612</v>
+        <v>131195797</v>
       </c>
       <c r="B68" t="n">
-        <v>57892</v>
+        <v>79254</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7833,39 +7833,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>440929</v>
+        <v>440932</v>
       </c>
       <c r="R68" t="n">
-        <v>6814703</v>
+        <v>6815337</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7897,7 +7892,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7907,7 +7902,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7934,10 +7929,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131195912</v>
+        <v>131195695</v>
       </c>
       <c r="B69" t="n">
-        <v>83100</v>
+        <v>79254</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7945,34 +7940,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>441062</v>
+        <v>440757</v>
       </c>
       <c r="R69" t="n">
-        <v>6815338</v>
+        <v>6815193</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8004,7 +8004,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8265,10 +8265,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131195680</v>
+        <v>131195757</v>
       </c>
       <c r="B72" t="n">
-        <v>91842</v>
+        <v>79254</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8276,19 +8276,23 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -8296,10 +8300,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>440829</v>
+        <v>441069</v>
       </c>
       <c r="R72" t="n">
-        <v>6814569</v>
+        <v>6814629</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8331,7 +8335,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8341,7 +8345,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8368,10 +8372,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131195678</v>
+        <v>131195848</v>
       </c>
       <c r="B73" t="n">
-        <v>91842</v>
+        <v>79254</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8379,19 +8383,23 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -8399,10 +8407,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>440423</v>
+        <v>440440</v>
       </c>
       <c r="R73" t="n">
-        <v>6815143</v>
+        <v>6815092</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8434,7 +8442,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8444,7 +8452,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8471,7 +8479,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131195757</v>
+        <v>131195843</v>
       </c>
       <c r="B74" t="n">
         <v>79254</v>
@@ -8506,10 +8514,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>441069</v>
+        <v>440489</v>
       </c>
       <c r="R74" t="n">
-        <v>6814629</v>
+        <v>6815022</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8541,7 +8549,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8551,7 +8559,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8578,7 +8586,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131195848</v>
+        <v>131195870</v>
       </c>
       <c r="B75" t="n">
         <v>79254</v>
@@ -8613,10 +8621,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>440440</v>
+        <v>440857</v>
       </c>
       <c r="R75" t="n">
-        <v>6815092</v>
+        <v>6814795</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8648,7 +8656,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8658,7 +8666,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8685,7 +8693,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131195843</v>
+        <v>131195755</v>
       </c>
       <c r="B76" t="n">
         <v>79254</v>
@@ -8720,10 +8728,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>440489</v>
+        <v>441098</v>
       </c>
       <c r="R76" t="n">
-        <v>6815022</v>
+        <v>6814630</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8755,7 +8763,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8765,7 +8773,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8792,7 +8800,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131195870</v>
+        <v>131195830</v>
       </c>
       <c r="B77" t="n">
         <v>79254</v>
@@ -8827,10 +8835,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>440857</v>
+        <v>440672</v>
       </c>
       <c r="R77" t="n">
-        <v>6814795</v>
+        <v>6815003</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8862,7 +8870,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8872,7 +8880,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8899,7 +8907,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131195755</v>
+        <v>131195805</v>
       </c>
       <c r="B78" t="n">
         <v>79254</v>
@@ -8934,10 +8942,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>441098</v>
+        <v>441170</v>
       </c>
       <c r="R78" t="n">
-        <v>6814630</v>
+        <v>6815286</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8969,7 +8977,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8979,7 +8987,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9006,10 +9014,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131195830</v>
+        <v>131195671</v>
       </c>
       <c r="B79" t="n">
-        <v>79254</v>
+        <v>79011</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9017,21 +9025,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9041,10 +9049,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>440672</v>
+        <v>440740</v>
       </c>
       <c r="R79" t="n">
-        <v>6815003</v>
+        <v>6814579</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9076,7 +9084,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9086,7 +9094,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9113,10 +9121,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131195805</v>
+        <v>131195680</v>
       </c>
       <c r="B80" t="n">
-        <v>79254</v>
+        <v>91842</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9124,23 +9132,19 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -9148,10 +9152,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>441170</v>
+        <v>440829</v>
       </c>
       <c r="R80" t="n">
-        <v>6815286</v>
+        <v>6814569</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9183,7 +9187,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9193,7 +9197,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9220,10 +9224,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131195671</v>
+        <v>131195678</v>
       </c>
       <c r="B81" t="n">
-        <v>79011</v>
+        <v>91842</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9231,23 +9235,19 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -9255,10 +9255,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>440740</v>
+        <v>440423</v>
       </c>
       <c r="R81" t="n">
-        <v>6814579</v>
+        <v>6815143</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9300,7 +9300,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10641,10 +10641,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131195763</v>
+        <v>131195556</v>
       </c>
       <c r="B94" t="n">
-        <v>79254</v>
+        <v>83234</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10652,21 +10652,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10676,10 +10676,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>440983</v>
+        <v>440904</v>
       </c>
       <c r="R94" t="n">
-        <v>6814769</v>
+        <v>6814873</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10711,7 +10711,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10721,7 +10721,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10748,10 +10748,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131195759</v>
+        <v>131195585</v>
       </c>
       <c r="B95" t="n">
-        <v>79254</v>
+        <v>57892</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10759,34 +10759,39 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>440974</v>
+        <v>440954</v>
       </c>
       <c r="R95" t="n">
-        <v>6814684</v>
+        <v>6814835</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10818,7 +10823,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10828,7 +10833,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10855,10 +10865,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131195699</v>
+        <v>131195617</v>
       </c>
       <c r="B96" t="n">
-        <v>79254</v>
+        <v>57892</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10866,27 +10876,27 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -10895,10 +10905,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>441115</v>
+        <v>440769</v>
       </c>
       <c r="R96" t="n">
-        <v>6815286</v>
+        <v>6815128</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10930,7 +10940,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10940,7 +10950,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10967,7 +10977,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131195701</v>
+        <v>131195763</v>
       </c>
       <c r="B97" t="n">
         <v>79254</v>
@@ -10996,21 +11006,16 @@
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>440529</v>
+        <v>440983</v>
       </c>
       <c r="R97" t="n">
-        <v>6814939</v>
+        <v>6814769</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11042,7 +11047,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11052,7 +11057,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11079,7 +11084,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131195789</v>
+        <v>131195759</v>
       </c>
       <c r="B98" t="n">
         <v>79254</v>
@@ -11114,10 +11119,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>440756</v>
+        <v>440974</v>
       </c>
       <c r="R98" t="n">
-        <v>6815138</v>
+        <v>6814684</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11149,7 +11154,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11159,7 +11164,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11186,10 +11191,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131195556</v>
+        <v>131195699</v>
       </c>
       <c r="B99" t="n">
-        <v>83234</v>
+        <v>79254</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11197,34 +11202,39 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>440904</v>
+        <v>441115</v>
       </c>
       <c r="R99" t="n">
-        <v>6814873</v>
+        <v>6815286</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11256,7 +11266,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11266,7 +11276,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11293,10 +11303,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131195585</v>
+        <v>131195701</v>
       </c>
       <c r="B100" t="n">
-        <v>57892</v>
+        <v>79254</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11304,27 +11314,27 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -11333,10 +11343,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>440954</v>
+        <v>440529</v>
       </c>
       <c r="R100" t="n">
-        <v>6814835</v>
+        <v>6814939</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11368,7 +11378,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11378,12 +11388,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>09:47</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11410,10 +11415,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131195617</v>
+        <v>131195789</v>
       </c>
       <c r="B101" t="n">
-        <v>57892</v>
+        <v>79254</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11421,39 +11426,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>440769</v>
+        <v>440756</v>
       </c>
       <c r="R101" t="n">
-        <v>6815128</v>
+        <v>6815138</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11485,7 +11485,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11495,7 +11495,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -14105,10 +14105,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>131195796</v>
+        <v>131195650</v>
       </c>
       <c r="B126" t="n">
-        <v>79254</v>
+        <v>57889</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14116,34 +14116,39 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>440887</v>
+        <v>441062</v>
       </c>
       <c r="R126" t="n">
-        <v>6815322</v>
+        <v>6815341</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14175,7 +14180,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14185,7 +14190,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14212,7 +14217,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>131195785</v>
+        <v>131195796</v>
       </c>
       <c r="B127" t="n">
         <v>79254</v>
@@ -14247,10 +14252,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>440835</v>
+        <v>440887</v>
       </c>
       <c r="R127" t="n">
-        <v>6815088</v>
+        <v>6815322</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14282,7 +14287,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14292,7 +14297,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14319,7 +14324,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>131195700</v>
+        <v>131195785</v>
       </c>
       <c r="B128" t="n">
         <v>79254</v>
@@ -14348,21 +14353,16 @@
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>440915</v>
+        <v>440835</v>
       </c>
       <c r="R128" t="n">
-        <v>6815308</v>
+        <v>6815088</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14394,7 +14394,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14404,7 +14404,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14431,7 +14431,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>131195892</v>
+        <v>131195700</v>
       </c>
       <c r="B129" t="n">
         <v>79254</v>
@@ -14460,16 +14460,21 @@
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>440901</v>
+        <v>440915</v>
       </c>
       <c r="R129" t="n">
-        <v>6814603</v>
+        <v>6815308</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14501,7 +14506,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14511,7 +14516,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14538,10 +14543,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>131195650</v>
+        <v>131195892</v>
       </c>
       <c r="B130" t="n">
-        <v>57889</v>
+        <v>79254</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14549,39 +14554,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>441062</v>
+        <v>440901</v>
       </c>
       <c r="R130" t="n">
-        <v>6815341</v>
+        <v>6814603</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14613,7 +14613,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14623,7 +14623,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -19005,10 +19005,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>131195914</v>
+        <v>131195847</v>
       </c>
       <c r="B171" t="n">
-        <v>89207</v>
+        <v>79254</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19016,21 +19016,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -19040,10 +19040,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>440856</v>
+        <v>440465</v>
       </c>
       <c r="R171" t="n">
-        <v>6814840</v>
+        <v>6815075</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19075,7 +19075,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -19085,7 +19085,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19112,10 +19112,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>131195636</v>
+        <v>131195788</v>
       </c>
       <c r="B172" t="n">
-        <v>57892</v>
+        <v>79254</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19123,39 +19123,34 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
-      <c r="M172" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
       <c r="P172" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>440969</v>
+        <v>440795</v>
       </c>
       <c r="R172" t="n">
-        <v>6814838</v>
+        <v>6815104</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19187,7 +19182,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -19197,12 +19192,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC172" t="inlineStr">
-        <is>
-          <t>Äldre påbörjat bobygge</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19229,10 +19219,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>131195588</v>
+        <v>131195901</v>
       </c>
       <c r="B173" t="n">
-        <v>57892</v>
+        <v>79254</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19240,39 +19230,34 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P173" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>440492</v>
+        <v>440885</v>
       </c>
       <c r="R173" t="n">
-        <v>6815012</v>
+        <v>6814475</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19304,7 +19289,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -19314,12 +19299,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>14:08</t>
-        </is>
-      </c>
-      <c r="AC173" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19346,7 +19326,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>131195847</v>
+        <v>131195804</v>
       </c>
       <c r="B174" t="n">
         <v>79254</v>
@@ -19381,10 +19361,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>440465</v>
+        <v>441158</v>
       </c>
       <c r="R174" t="n">
-        <v>6815075</v>
+        <v>6815289</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19416,7 +19396,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -19426,7 +19406,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19453,7 +19433,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>131195788</v>
+        <v>131195708</v>
       </c>
       <c r="B175" t="n">
         <v>79254</v>
@@ -19482,16 +19462,21 @@
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P175" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>440795</v>
+        <v>440774</v>
       </c>
       <c r="R175" t="n">
-        <v>6815104</v>
+        <v>6814546</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19523,7 +19508,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -19533,7 +19518,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19560,7 +19545,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>131195901</v>
+        <v>131195793</v>
       </c>
       <c r="B176" t="n">
         <v>79254</v>
@@ -19595,10 +19580,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>440885</v>
+        <v>440758</v>
       </c>
       <c r="R176" t="n">
-        <v>6814475</v>
+        <v>6815261</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19630,7 +19615,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -19640,7 +19625,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19667,7 +19652,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>131195804</v>
+        <v>131195849</v>
       </c>
       <c r="B177" t="n">
         <v>79254</v>
@@ -19702,10 +19687,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>441158</v>
+        <v>440438</v>
       </c>
       <c r="R177" t="n">
-        <v>6815289</v>
+        <v>6815100</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19737,7 +19722,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -19747,7 +19732,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19774,7 +19759,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>131195708</v>
+        <v>131195783</v>
       </c>
       <c r="B178" t="n">
         <v>79254</v>
@@ -19803,21 +19788,16 @@
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P178" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>440774</v>
+        <v>440881</v>
       </c>
       <c r="R178" t="n">
-        <v>6814546</v>
+        <v>6815052</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19849,7 +19829,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -19859,7 +19839,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19886,7 +19866,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>131195793</v>
+        <v>131195744</v>
       </c>
       <c r="B179" t="n">
         <v>79254</v>
@@ -19921,10 +19901,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>440758</v>
+        <v>441179</v>
       </c>
       <c r="R179" t="n">
-        <v>6815261</v>
+        <v>6814681</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19956,7 +19936,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -19966,7 +19946,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19993,10 +19973,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>131195849</v>
+        <v>131195914</v>
       </c>
       <c r="B180" t="n">
-        <v>79254</v>
+        <v>89207</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20004,21 +19984,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -20028,10 +20008,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>440438</v>
+        <v>440856</v>
       </c>
       <c r="R180" t="n">
-        <v>6815100</v>
+        <v>6814840</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20063,7 +20043,7 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -20073,7 +20053,7 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -20100,10 +20080,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>131195783</v>
+        <v>131195636</v>
       </c>
       <c r="B181" t="n">
-        <v>79254</v>
+        <v>57892</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20111,34 +20091,39 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
       <c r="P181" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>440881</v>
+        <v>440969</v>
       </c>
       <c r="R181" t="n">
-        <v>6815052</v>
+        <v>6814838</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20170,7 +20155,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -20180,7 +20165,12 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>Äldre påbörjat bobygge</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20207,10 +20197,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>131195744</v>
+        <v>131195588</v>
       </c>
       <c r="B182" t="n">
-        <v>79254</v>
+        <v>57892</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20218,34 +20208,39 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P182" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>441179</v>
+        <v>440492</v>
       </c>
       <c r="R182" t="n">
-        <v>6814681</v>
+        <v>6815012</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20277,7 +20272,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -20287,7 +20282,12 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -25818,10 +25818,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>131197390</v>
+        <v>131197406</v>
       </c>
       <c r="B234" t="n">
-        <v>57892</v>
+        <v>79254</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -25829,42 +25829,34 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
-      <c r="K234" t="inlineStr"/>
-      <c r="L234" t="inlineStr"/>
-      <c r="M234" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>440857</v>
+        <v>441114</v>
       </c>
       <c r="R234" t="n">
-        <v>6815078</v>
+        <v>6814652</v>
       </c>
       <c r="S234" t="n">
         <v>25</v>
@@ -25923,10 +25915,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>131197406</v>
+        <v>131197390</v>
       </c>
       <c r="B235" t="n">
-        <v>79254</v>
+        <v>57892</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -25934,34 +25926,42 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
+      <c r="K235" t="inlineStr"/>
+      <c r="L235" t="inlineStr"/>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
           <t>Navardalsgnupen östra, Dlr</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>441114</v>
+        <v>440857</v>
       </c>
       <c r="R235" t="n">
-        <v>6814652</v>
+        <v>6815078</v>
       </c>
       <c r="S235" t="n">
         <v>25</v>
@@ -26722,10 +26722,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>131197391</v>
+        <v>131197393</v>
       </c>
       <c r="B243" t="n">
-        <v>57892</v>
+        <v>57889</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -26733,16 +26733,16 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -26765,10 +26765,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>440926</v>
+        <v>440751</v>
       </c>
       <c r="R243" t="n">
-        <v>6814891</v>
+        <v>6815273</v>
       </c>
       <c r="S243" t="n">
         <v>25</v>
@@ -26827,10 +26827,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>131197393</v>
+        <v>131197391</v>
       </c>
       <c r="B244" t="n">
-        <v>57889</v>
+        <v>57892</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -26838,16 +26838,16 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -26870,10 +26870,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>440751</v>
+        <v>440926</v>
       </c>
       <c r="R244" t="n">
-        <v>6815273</v>
+        <v>6814891</v>
       </c>
       <c r="S244" t="n">
         <v>25</v>
@@ -27829,10 +27829,10 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>131180073</v>
+        <v>131180228</v>
       </c>
       <c r="B254" t="n">
-        <v>57889</v>
+        <v>79254</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -27840,39 +27840,34 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
-      <c r="M254" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P254" t="inlineStr">
         <is>
           <t>Navarnäsberget, Dlr</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>440948</v>
+        <v>441009</v>
       </c>
       <c r="R254" t="n">
-        <v>6815355</v>
+        <v>6815390</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -27915,11 +27910,6 @@
       <c r="AB254" t="inlineStr">
         <is>
           <t>09:13</t>
-        </is>
-      </c>
-      <c r="AC254" t="inlineStr">
-        <is>
-          <t>1 bild</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -27946,10 +27936,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>131180228</v>
+        <v>131180073</v>
       </c>
       <c r="B255" t="n">
-        <v>79254</v>
+        <v>57889</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -27957,34 +27947,39 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P255" t="inlineStr">
         <is>
           <t>Navarnäsberget, Dlr</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>441009</v>
+        <v>440948</v>
       </c>
       <c r="R255" t="n">
-        <v>6815390</v>
+        <v>6815355</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -28027,6 +28022,11 @@
       <c r="AB255" t="inlineStr">
         <is>
           <t>09:13</t>
+        </is>
+      </c>
+      <c r="AC255" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -28981,7 +28981,7 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>131175193</v>
+        <v>131176226</v>
       </c>
       <c r="B265" t="n">
         <v>79254</v>
@@ -29016,10 +29016,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>440948</v>
+        <v>440926</v>
       </c>
       <c r="R265" t="n">
-        <v>6814948</v>
+        <v>6815004</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -29062,11 +29062,6 @@
       <c r="AB265" t="inlineStr">
         <is>
           <t>09:13</t>
-        </is>
-      </c>
-      <c r="AC265" t="inlineStr">
-        <is>
-          <t>1 bild gran</t>
         </is>
       </c>
       <c r="AD265" t="b">
@@ -29093,7 +29088,7 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>131176226</v>
+        <v>131175193</v>
       </c>
       <c r="B266" t="n">
         <v>79254</v>
@@ -29128,10 +29123,10 @@
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>440926</v>
+        <v>440948</v>
       </c>
       <c r="R266" t="n">
-        <v>6815004</v>
+        <v>6814948</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -29174,6 +29169,11 @@
       <c r="AB266" t="inlineStr">
         <is>
           <t>09:13</t>
+        </is>
+      </c>
+      <c r="AC266" t="inlineStr">
+        <is>
+          <t>1 bild gran</t>
         </is>
       </c>
       <c r="AD266" t="b">
@@ -29929,10 +29929,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>131180289</v>
+        <v>131170517</v>
       </c>
       <c r="B274" t="n">
-        <v>79254</v>
+        <v>57892</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -29940,37 +29940,39 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
-      <c r="J274" t="inlineStr"/>
-      <c r="K274" t="inlineStr"/>
-      <c r="N274" t="inlineStr"/>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P274" t="inlineStr">
         <is>
-          <t>Navarnäsberget, Dlr</t>
+          <t>Ytter-Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>441013</v>
+        <v>441106</v>
       </c>
       <c r="R274" t="n">
-        <v>6815402</v>
+        <v>6814655</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -30017,7 +30019,7 @@
       </c>
       <c r="AC274" t="inlineStr">
         <is>
-          <t>1 bild, garn vid källa</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD274" t="b">
@@ -30026,7 +30028,6 @@
       <c r="AE274" t="b">
         <v>0</v>
       </c>
-      <c r="AF274" t="inlineStr"/>
       <c r="AG274" t="b">
         <v>0</v>
       </c>
@@ -30045,7 +30046,7 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>131187704</v>
+        <v>131180289</v>
       </c>
       <c r="B275" t="n">
         <v>79254</v>
@@ -30074,16 +30075,19 @@
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
+      <c r="J275" t="inlineStr"/>
+      <c r="K275" t="inlineStr"/>
+      <c r="N275" t="inlineStr"/>
       <c r="P275" t="inlineStr">
         <is>
           <t>Navarnäsberget, Dlr</t>
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>440434</v>
+        <v>441013</v>
       </c>
       <c r="R275" t="n">
-        <v>6815187</v>
+        <v>6815402</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -30113,17 +30117,33 @@
           <t>2026-02-16</t>
         </is>
       </c>
+      <c r="Z275" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AA275" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
+      <c r="AB275" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
+      <c r="AC275" t="inlineStr">
+        <is>
+          <t>1 bild, garn vid källa</t>
+        </is>
+      </c>
       <c r="AD275" t="b">
         <v>0</v>
       </c>
       <c r="AE275" t="b">
         <v>0</v>
       </c>
+      <c r="AF275" t="inlineStr"/>
       <c r="AG275" t="b">
         <v>0</v>
       </c>
@@ -30142,10 +30162,10 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>131170517</v>
+        <v>131187704</v>
       </c>
       <c r="B276" t="n">
-        <v>57892</v>
+        <v>79254</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -30153,39 +30173,34 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
-      <c r="M276" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P276" t="inlineStr">
         <is>
-          <t>Ytter-Navardalen, Dlr</t>
+          <t>Navarnäsberget, Dlr</t>
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>441106</v>
+        <v>440434</v>
       </c>
       <c r="R276" t="n">
-        <v>6814655</v>
+        <v>6815187</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -30215,24 +30230,9 @@
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="Z276" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AA276" t="inlineStr">
         <is>
           <t>2026-02-16</t>
-        </is>
-      </c>
-      <c r="AB276" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
-      <c r="AC276" t="inlineStr">
-        <is>
-          <t>1 bild</t>
         </is>
       </c>
       <c r="AD276" t="b">
@@ -32637,10 +32637,10 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>131192073</v>
+        <v>131180074</v>
       </c>
       <c r="B299" t="n">
-        <v>57892</v>
+        <v>79254</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -32648,39 +32648,34 @@
         </is>
       </c>
       <c r="E299" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I299" t="inlineStr"/>
-      <c r="M299" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P299" t="inlineStr">
         <is>
-          <t>Ytter-Navardalen, Dlr</t>
+          <t>Navarnäsberget, Dlr</t>
         </is>
       </c>
       <c r="Q299" t="n">
-        <v>440917</v>
+        <v>440948</v>
       </c>
       <c r="R299" t="n">
-        <v>6814603</v>
+        <v>6815355</v>
       </c>
       <c r="S299" t="n">
         <v>10</v>
@@ -32710,14 +32705,19 @@
           <t>2026-02-16</t>
         </is>
       </c>
+      <c r="Z299" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AA299" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="AC299" t="inlineStr">
-        <is>
-          <t>3 bilder med person</t>
+      <c r="AB299" t="inlineStr">
+        <is>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD299" t="b">
@@ -32744,7 +32744,7 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>131180074</v>
+        <v>131180739</v>
       </c>
       <c r="B300" t="n">
         <v>79254</v>
@@ -32779,10 +32779,10 @@
         </is>
       </c>
       <c r="Q300" t="n">
-        <v>440948</v>
+        <v>441163</v>
       </c>
       <c r="R300" t="n">
-        <v>6815355</v>
+        <v>6815248</v>
       </c>
       <c r="S300" t="n">
         <v>10</v>
@@ -32851,10 +32851,10 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>131180739</v>
+        <v>131192073</v>
       </c>
       <c r="B301" t="n">
-        <v>79254</v>
+        <v>57892</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -32862,34 +32862,39 @@
         </is>
       </c>
       <c r="E301" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I301" t="inlineStr"/>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P301" t="inlineStr">
         <is>
-          <t>Navarnäsberget, Dlr</t>
+          <t>Ytter-Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>441163</v>
+        <v>440917</v>
       </c>
       <c r="R301" t="n">
-        <v>6815248</v>
+        <v>6814603</v>
       </c>
       <c r="S301" t="n">
         <v>10</v>
@@ -32919,19 +32924,14 @@
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="Z301" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AA301" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="AB301" t="inlineStr">
-        <is>
-          <t>09:13</t>
+      <c r="AC301" t="inlineStr">
+        <is>
+          <t>3 bilder med person</t>
         </is>
       </c>
       <c r="AD301" t="b">
